--- a/Reports/Registration-Setup-Test-Report.xlsx
+++ b/Reports/Registration-Setup-Test-Report.xlsx
@@ -454,7 +454,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Full suite on branch registration-setup (commit dfbc9fa, before this report), run 27 October 2026: web integration tests on the local Docker database, app and package unit tests. Features only a phone can confirm are marked Not yet done (phone) in Other Checks.</t>
+          <t>Full suite on branch registration-setup (after the final fix wave), run 27 October 2026: web integration tests on the local Docker database, app and package unit tests. Features only a phone can confirm are marked Not yet done (phone) in Other Checks.</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTA('Test Results'!C2:C374)</f>
+        <f>COUNTA('Test Results'!C2:C383)</f>
         <v/>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Test Results'!E2:E374,"Passed")</f>
+        <f>COUNTIF('Test Results'!E2:E383,"Passed")</f>
         <v/>
       </c>
     </row>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Test Results'!E2:E374,"Failed")</f>
+        <f>COUNTIF('Test Results'!E2:E383,"Failed")</f>
         <v/>
       </c>
     </row>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF('Test Results'!E2:E374,"Skipped")</f>
+        <f>COUNTIF('Test Results'!E2:E383,"Skipped")</f>
         <v/>
       </c>
     </row>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E374"/>
+  <dimension ref="A1:E383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -728,7 +728,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>a user suspended before having a profile cannot create one and publish it (409)</t>
+          <t>suspension emails: none for a customer without a profile, none for a lift of a user who was not suspended</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>lists users with pagination and a text filter on email or name</t>
+          <t>a user suspended before having a profile cannot create one and publish it (409)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>creates and updates a category per language</t>
+          <t>lists users with pagination and a text filter on email or name</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>creates a page and publishes it</t>
+          <t>creates and updates a category per language</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>sets a staff role by email; an unknown email is 404</t>
+          <t>creates a page and publishes it</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>providers are readable; a Reviewer deletes a photo (object removed, published profile photo unpublishes)</t>
+          <t>sets a staff role by email; an unknown email is 404</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>GET /me returns the staff user; unknown resources are 404</t>
+          <t>providers are readable; a Reviewer deletes a photo (object removed, published profile photo unpublishes)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>a Reviewer cannot decide their own document</t>
+          <t>staff see a person's picture on the provider page and the user page, and delete it</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>an expired suspension is not counted by the suspended filter</t>
+          <t>GET /me returns the staff user; unknown resources are 404</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>GET users/[id] carries names, the private address and the picture; the list shows them too</t>
+          <t>a Reviewer cannot decide their own document</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -988,17 +988,17 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Admin lang</t>
+          <t>Admin back office API</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>admin-lang.int.spec.ts</t>
+          <t>admin-api.int.spec.ts</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>adminLang {"cookie":"en"} -&gt; en</t>
+          <t>an expired suspension is not counted by the suspended filter</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1015,17 +1015,17 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Admin lang</t>
+          <t>Admin back office API</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>admin-lang.int.spec.ts</t>
+          <t>admin-api.int.spec.ts</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>adminLang {"cookie":"fr"} -&gt; de</t>
+          <t>GET users/[id] carries names, the private address and the picture; the list shows them too</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>adminLang {"cookie":"xx","acceptLanguage":"en"} -&gt; en</t>
+          <t>{"cookie":"en"} -&gt; en</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>adminLang {"acceptLanguage":"en-GB,en;q=0.9,de;q=0.8"} -&gt; en</t>
+          <t>{"cookie":"fr"} -&gt; de</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>adminLang {"acceptLanguage":"fr-FR"} -&gt; de</t>
+          <t>{"cookie":"xx","acceptLanguage":"en"} -&gt; en</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>adminLang {} -&gt; de</t>
+          <t>{"acceptLanguage":"en-GB,en;q=0.9,de;q=0.8"} -&gt; en</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>adminLangCookie lasts a year for the whole site</t>
+          <t>{"acceptLanguage":"fr-FR"} -&gt; de</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>useAt renders en</t>
+          <t>{} -&gt; de</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>useAt renders de</t>
+          <t>lasts a year for the whole site</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>admin layout follows the cookie, then Accept-Language, then German</t>
+          <t>renders en</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1258,17 +1258,17 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Staff roles</t>
+          <t>Admin lang</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>admin-roles.int.spec.ts</t>
+          <t>admin-lang.int.spec.ts</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>a Reviewer cannot do Administrator actions, and nothing changes</t>
+          <t>renders de</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1285,17 +1285,17 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Staff roles</t>
+          <t>Admin lang</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>admin-roles.int.spec.ts</t>
+          <t>admin-lang.int.spec.ts</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>a Reviewer cannot change or delete an existing category or page</t>
+          <t>follows the cookie, then Accept-Language, then German</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>a Reviewer can read users and documents</t>
+          <t>a Reviewer cannot do Administrator actions, and nothing changes</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>a customer with no staff role gets 403 on every admin route; no session gets 401</t>
+          <t>a Reviewer cannot change or delete an existing category or page</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>the last Administrator cannot be demoted</t>
+          <t>a Reviewer can read users and documents</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>every route file under app/api/admin exports handlers built with adminRequest</t>
+          <t>a customer with no staff role gets 403 on every admin route; no session gets 401</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1420,17 +1420,17 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Security rule check</t>
+          <t>Staff roles</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>app-endpoints-wrapped.int.spec.ts</t>
+          <t>admin-roles.int.spec.ts</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>the owner-connection check catches a bypass (negative fixture)</t>
+          <t>the last Administrator cannot be demoted</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1447,17 +1447,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Security rule check</t>
+          <t>Staff roles</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>app-endpoints-wrapped.int.spec.ts</t>
+          <t>admin-roles.int.spec.ts</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>every route file under app/app-api exports handlers built with appRequest</t>
+          <t>every route file under app/api/admin exports handlers built with adminRequest</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1474,17 +1474,17 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>App request wrapper</t>
+          <t>Security rule check</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>app-request.int.spec.ts</t>
+          <t>app-endpoints-wrapped.int.spec.ts</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>first contact creates the users row</t>
+          <t>the owner-connection check catches a bypass (negative fixture)</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1501,17 +1501,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>App request wrapper</t>
+          <t>Security rule check</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>app-request.int.spec.ts</t>
+          <t>app-endpoints-wrapped.int.spec.ts</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>a forged cookie is 401 and touches nothing</t>
+          <t>every route file under app/app-api exports handlers built with appRequest</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>required auth without a cookie is 401</t>
+          <t>first contact creates the users row</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>optional auth without a cookie runs with no user</t>
+          <t>a forged cookie is 401 and touches nothing</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>an unconfirmed email: 403 where auth is required, signed out where optional; never a users row</t>
+          <t>required auth without a cookie is 401</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>a handler error rolls back and returns 500</t>
+          <t>optional auth without a cookie runs with no user</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>a body over maxBodyBytes is 413 before the handler runs</t>
+          <t>an unconfirmed email: 403 where auth is required, signed out where optional; never a users row</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>user A cannot read user B through the wrapper</t>
+          <t>a handler error rolls back and returns 500</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>app_user cannot write staff columns of its own row</t>
+          <t>a body over maxBodyBytes is 413 before the handler runs</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>first contact with a changed email updates the row</t>
+          <t>user A cannot read user B through the wrapper</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>a second id with the same email gets 409 and no row is written</t>
+          <t>app_user cannot write staff columns of its own row</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>a thrown 400 Response is returned unchanged</t>
+          <t>first contact with a changed email updates the row</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1798,17 +1798,17 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Sign-up and session</t>
+          <t>App request wrapper</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>auth-cookie-flow.int.spec.ts</t>
+          <t>app-request.int.spec.ts</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>auth cookie flow signs up by REST, captures the cookie; /app-api/v1/me knows the session but refuses it until the email is confirmed</t>
+          <t>a second id with the same email gets 409 and no row is written</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1825,17 +1825,17 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Categories</t>
+          <t>App request wrapper</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>categories.int.spec.ts</t>
+          <t>app-request.int.spec.ts</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>ordered by sort, "other services" always last, names in the requested language, anonymous allowed</t>
+          <t>a thrown 400 Response is returned unchanged</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>an unknown language is 400</t>
+          <t>ordered by sort, "other services" always last, names in the requested language, anonymous allowed</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1879,17 +1879,17 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Concurrency</t>
+          <t>Categories</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>concurrency.int.spec.ts</t>
+          <t>categories.int.spec.ts</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>12 concurrent searches and 12 concurrent public pages all complete</t>
+          <t>an unknown language is 400</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1906,17 +1906,17 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Cron suspensions</t>
+          <t>Concurrency</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>cron-suspensions.int.spec.ts</t>
+          <t>concurrency.int.spec.ts</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>401 without the right secret, and when CRON_SECRET is unset</t>
+          <t>12 concurrent searches and 12 concurrent public pages all complete</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>ends a past suspension once: both columns cleared, one email; a future one is left alone</t>
+          <t>401 without the right secret, and when CRON_SECRET is unset</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1960,17 +1960,17 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Database migrations</t>
+          <t>Cron suspensions</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>db-migrations.int.spec.ts</t>
+          <t>cron-suspensions.int.spec.ts</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>migrates an empty database and classifies every table</t>
+          <t>ends a past suspension once: both columns cleared, one email; a future one is left alone</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>0008: person fields on users, suspensions by date, drafts allowed, notifications; applyRls succeeds</t>
+          <t>migrates an empty database and classifies every table</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>photos: a profile photo has no provider, a portfolio photo has one, one profile photo per person</t>
+          <t>0008: person fields on users, suspensions by date, drafts allowed, notifications; applyRls succeeds</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2041,17 +2041,17 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Emails</t>
+          <t>Database migrations</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>email.int.spec.ts</t>
+          <t>db-migrations.int.spec.ts</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>approval: one email in the user language with the document name and the deep link</t>
+          <t>photos: a profile photo has no provider, a portfolio photo has one, one profile photo per person</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>rejection in German includes the note verbatim, escaped in the HTML</t>
+          <t>approval: one email in the user language with the document name and the deep link</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>without a key it only logs and records, and never throws</t>
+          <t>rejection in German includes the note verbatim, escaped in the HTML</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>outside tests without a key: one log line without recipient or body, and nothing kept in memory</t>
+          <t>without a key it only logs and records, and never throws</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>with a key it calls Resend with the full message; an { error } and a throw are logged, not thrown</t>
+          <t>outside tests without a key: one log line without recipient or body, and nothing kept in memory</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>an unexpected stored language falls back to German</t>
+          <t>with a key it calls Resend with the full message; an { error } and a throw are logged, not thrown</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -2203,17 +2203,17 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Uploads and document review</t>
+          <t>Emails</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>files-review.int.spec.ts</t>
+          <t>email.int.spec.ts</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>afterCommit: a handler that deletes a photo and then throws rolls back, the object stays</t>
+          <t>an unexpected stored language falls back to German</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>afterCommit: the object is deleted only after the commit</t>
+          <t>afterCommit: a handler that deletes a photo and then throws rolls back, the object stays</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>private_files and documents are isolated (RLS)</t>
+          <t>afterCommit: the object is deleted only after the commit</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>at most 10 unsubmitted uploads per user (409)</t>
+          <t>private_files and documents are isolated (RLS)</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>a decompression bomb and a header followed by garbage are 400; a later upload is accepted</t>
+          <t>at most 10 unsubmitted uploads per user (409)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>EXIF is stripped from the stored JPEG</t>
+          <t>a decompression bomb and a header followed by garbage are 400; a later upload is accepted</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>alt over 200 characters is 400</t>
+          <t>EXIF is stripped from the stored JPEG</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>an unauthenticated upload is refused before the body is read</t>
+          <t>alt over 200 characters is 400</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>the body is read before the first-contact user row and the transaction exist</t>
+          <t>an unauthenticated upload is refused before the body is read</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>photos of a published provider are public, and unreadable once suspended</t>
+          <t>the body is read before the first-contact user row and the transaction exist</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>replacing the profile photo of a published profile works</t>
+          <t>photos of a published provider are public, and unreadable once suspended</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>deleting the profile photo while publishing never leaves a published profile without a photo</t>
+          <t>replacing the profile photo of a published profile works</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>two simultaneous submits for one requirement give one 201 and one 409</t>
+          <t>deleting the profile photo while publishing never leaves a published profile without a photo</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>the database refuses a second pending check for a requirement</t>
+          <t>two simultaneous submits for one requirement give one 201 and one 409</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>approval (staff SQL) makes a service with required documents offerable</t>
+          <t>the database refuses a second pending check for a requirement</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>the signed link carries X-Amz-Expires=300 and the public URL needs AWS_ENDPOINT</t>
+          <t>approval (staff SQL) makes a service with required documents offerable</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -2635,17 +2635,17 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Uploads</t>
+          <t>Uploads and document review</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>files.int.spec.ts</t>
+          <t>files-review.int.spec.ts</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>a profile photo is re-encoded to JPEG at most 1600 px and returned in contract shape</t>
+          <t>the signed link carries X-Amz-Expires=300 and the public URL needs AWS_ENDPOINT</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>a new profile photo replaces the old one and deletes its object</t>
+          <t>a profile photo is re-encoded to JPEG at most 1600 px and returned in contract shape</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>portfolio is limited to 12 (409), a non-image is 400, a missing kind is 400</t>
+          <t>a new profile photo replaces the old one and deletes its object</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>a portfolio photo needs a profile first (409); anonymous is 401; an oversize body is 413</t>
+          <t>portfolio is limited to 12 (409), a non-image is 400, a missing kind is 400</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>deleting a photo: another user gets 404, the owner 204 and the object and row are gone</t>
+          <t>a portfolio photo needs a profile first (409); anonymous is 401; an oversize body is 413</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>the profile photo of a published profile cannot be deleted (409)</t>
+          <t>deleting a photo: another user gets 404, the owner 204 and the object and row are gone</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>suspended_until is domain-only and photos are isolated</t>
+          <t>the profile photo of a published profile cannot be deleted (409)</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>files: a PDF goes to the private bucket, a non-PDF is 400, another user gets 404, the owner a signed link</t>
+          <t>suspended_until is domain-only and photos are isolated</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>documents also take JPEG, PNG and WEBP photos: re-encoded without metadata, at most 2400 px, stored with their type</t>
+          <t>files: a PDF goes to the private bucket, a non-PDF is 400, another user gets 404, the owner a signed link</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>a GIF and a text file renamed to .pdf are refused as documents</t>
+          <t>documents also take JPEG, PNG and WEBP photos: re-encoded without metadata, at most 2400 px, stored with their type</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>staff open an image document through the same signed link; it is served as an image</t>
+          <t>a GIF and a text file renamed to .pdf are refused as documents</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>a failed file insert removes the uploaded object</t>
+          <t>staff open an image document through the same signed link; it is served as an image</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>verifications: one pending check per requirement (409 removes the second file), bad input is 400</t>
+          <t>a failed file insert removes the uploaded object</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>the profile photo is private to its owner: another user cannot see it and gets 404 on delete; listPhotos puts it first</t>
+          <t>verifications: one pending check per requirement (409 removes the second file), bad input is 400</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -3013,17 +3013,17 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Website home page</t>
+          <t>Uploads</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>home-page.int.spec.ts</t>
+          <t>files.int.spec.ts</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>home page is German by default: headline, categories, store badges without links, no forbidden words</t>
+          <t>the profile photo is private to its owner: another user cannot see it and gets 404 on delete; listPhotos puts it first</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>home page switches to English with ?lang=en and falls back to German for unknown values</t>
+          <t>is German by default: headline, categories, store badges without links, no forbidden words</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>home page has per-language metadata with canonical and hreflang for every language</t>
+          <t>switches to English with ?lang=en and falls back to German for unknown values</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>site layout metadataBase makes canonical and hreflang absolute on the site url</t>
+          <t>has per-language metadata with canonical and hreflang for every language</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>site layout html lang follows the request language; unknown falls back to de</t>
+          <t>metadataBase makes canonical and hreflang absolute on the site url</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>site layout footer links the four legal pages with catalogue labels in both languages</t>
+          <t>html lang follows the request language; unknown falls back to de</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -3175,17 +3175,17 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Website home page</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>notifications.int.spec.ts</t>
+          <t>home-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>live and nothing else pending: "profile is live" email with the link, and one notification</t>
+          <t>footer links the four legal pages with catalogue labels in both languages</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>the link of a German provider has no lang parameter</t>
+          <t>live and nothing else pending: "profile is live" email with the link, and one notification</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>live but another document is still missing: says the category service is visible, no notification</t>
+          <t>the link of a German provider has no lang parameter</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>the approved requirement is not enough for any service: plain approval, no notification</t>
+          <t>live but another document is still missing: says the category service is visible, no notification</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>draft profile: offline text, no notification</t>
+          <t>the approved requirement is not enough for any service: plain approval, no notification</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>suspended profile: suspended text with the date, no notification</t>
+          <t>draft profile: offline text, no notification</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>a requirement that was already approved: plain approval, no notification</t>
+          <t>suspended profile: suspended text with the date, no notification</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>rejection is unchanged</t>
+          <t>a requirement that was already approved: plain approval, no notification</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>GET /me lists the notification; PATCH dismissed hides it; another user gets 404</t>
+          <t>rejection is unchanged</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -3418,17 +3418,17 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>Database connection</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>owner-connection.int.spec.ts</t>
+          <t>notifications.int.spec.ts</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>inside a request transaction the owner connection `db` is a different connection (not app_user)</t>
+          <t>GET /me lists the notification; PATCH dismissed hides it; another user gets 404</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>two interleaved requests keep their own user id and role</t>
+          <t>inside a request transaction the owner connection `db` is a different connection (not app_user)</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -3472,17 +3472,17 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>Legal and info pages</t>
+          <t>Database connection</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>pages.int.spec.ts</t>
+          <t>owner-connection.int.spec.ts</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>pages tables every table is classified (pages and page_texts are public reference tables)</t>
+          <t>two interleaved requests keep their own user id and role</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>pages tables anonymous app requests read pages but cannot write them</t>
+          <t>every table is classified (pages and page_texts are public reference tables)</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>getPage returns the text in the language, falls back to de, hides drafts and unknown slugs</t>
+          <t>anonymous app requests read pages but cannot write them</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>getPage publishedPages lists published pages only</t>
+          <t>returns the text in the language, falls back to de, hides drafts and unknown slugs</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>legal page by slug renders the Markdown body in both languages with the de fallback</t>
+          <t>publishedPages lists published pages only</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>legal page by slug 404 for unknown and unpublished slugs</t>
+          <t>renders the Markdown body in both languages with the de fallback</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>legal page by slug metadata: title, canonical and hreflang for every language</t>
+          <t>404 for unknown and unpublished slugs</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>legal page by slug escapes HTML in a body and drops unsafe links</t>
+          <t>metadata: title, canonical and hreflang for every language</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>renderMarkdown escapes raw html and keeps Markdown</t>
+          <t>escapes HTML in a body and drops unsafe links</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>renderMarkdown external links get rel="nofollow ugc"; protocol-relative and backslash paths are dropped</t>
+          <t>escapes raw html and keeps Markdown</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -3742,17 +3742,17 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>Postcodes</t>
+          <t>Legal and info pages</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>postcodes.int.spec.ts</t>
+          <t>pages.int.spec.ts</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>imports the German file and looks up 01053 Dresden</t>
+          <t>external links get rel="nofollow ugc"; protocol-relative and backslash paths are dropped</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>rejects a four-digit German code and an unknown one</t>
+          <t>imports the German file and looks up 01053 Dresden</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Berlin to Munich is about 504 km</t>
+          <t>rejects a four-digit German code and an unknown one</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -3823,17 +3823,17 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>Website provider page</t>
+          <t>Postcodes</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>provider-page.int.spec.ts</t>
+          <t>postcodes.int.spec.ts</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>public provider page German default: public name heading, category, price "ab 80,00 â‚¬", on request, place</t>
+          <t>Berlin to Munich is about 504 km</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>public provider page English with ?lang=en: "from â‚¬80.00"</t>
+          <t>German default: public name heading, category, price "ab 80,00 â‚¬", on request, place</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>public provider page escapes user content</t>
+          <t>English with ?lang=en: "from â‚¬80.00"</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>public provider page 404 for a hidden provider (draft) and an unknown slug</t>
+          <t>escapes user content</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>public provider page metadata: title, description, canonical and hreflang for every language</t>
+          <t>404 for a hidden provider (draft) and an unknown slug</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>translate link is shown only when the texts are not in the page language</t>
+          <t>metadata: title, description, canonical and hreflang for every language</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>translate link ?translate=1 shows the translation with the AI label, noindex, canonical unchanged</t>
+          <t>is shown only when the texts are not in the page language</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>translate link ?translate=1 without a key shows the original texts and the unavailable copy</t>
+          <t>?translate=1 shows the translation with the AI label, noindex, canonical unchanged</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>translate link translate=1 on texts already in the viewer language: original, no label, no model call</t>
+          <t>?translate=1 without a key shows the original texts and the unavailable copy</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -4066,17 +4066,17 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>Provider profile</t>
+          <t>Website provider page</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>provider-profile.int.spec.ts</t>
+          <t>provider-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>GET is null when there is no profile</t>
+          <t>translate=1 on texts already in the viewer language: original, no label, no model call</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>PUT creates (201) and a later PUT edits (200); responses fit the contract</t>
+          <t>GET is null when there is no profile</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>an unknown postcode is 400 and changes nothing</t>
+          <t>PUT creates (201) and a later PUT edits (200); responses fit the contract</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>a partial first save never fails on business rules</t>
+          <t>an unknown postcode is 400 and changes nothing</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>status, slug and suspended in the body are ignored</t>
+          <t>a partial first save never fails on business rules</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>one user's profile is not visible to another</t>
+          <t>status, slug and suspended in the body are ignored</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>an invalid body is 400 with the contract error</t>
+          <t>one user's profile is not visible to another</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>an unconfirmed email gets 403 EMAIL_NOT_VERIFIED from PUT provider-profile and GET /me, and no users row</t>
+          <t>an invalid body is 400 with the contract error</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>PATCH /me checks its body with the contract: 400 Invalid input names the field; a valid patch saves</t>
+          <t>an unconfirmed email gets 403 EMAIL_NOT_VERIFIED from PUT provider-profile and GET /me, and no users row</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>updateMe stores country DE when the address carries none (the HTTP contract always sends one)</t>
+          <t>PATCH /me checks its body with the contract: 400 Invalid input names the field; a valid patch saves</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>PATCH /me stores names and a private address (country stored as sent); GET /me returns them; null clears the address</t>
+          <t>updateMe stores country DE when the address carries none (the HTTP contract always sends one)</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>POST creates a draft with the postcode prefilled; again returns the same id; GET /me is fine</t>
+          <t>PATCH /me stores names and a private address (country stored as sent); GET /me returns them; null clears the address</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>missing: the empty draft lists the person-independent items, business adds two, saves shrink it, PUT carries it</t>
+          <t>POST creates a draft with the postcode prefilled; again returns the same id; GET /me is fine</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>publish of an incomplete draft is 409 with the list; complete publishes with public name Lena F.</t>
+          <t>missing: the empty draft lists the person-independent items, business adds two, saves shrink it, PUT carries it</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>a draft with every nullable field null is invisible in search and the sitemap</t>
+          <t>publish of an incomplete draft is 409 with the list; complete publishes with public name Lena F.</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>a draft created during a suspension cannot be published</t>
+          <t>a draft with every nullable field null is invisible in search and the sitemap</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>the draft prefills the postcode only when it is a known one</t>
+          <t>a draft created during a suspension cannot be published</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -4525,17 +4525,17 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>Public provider data</t>
+          <t>Provider profile</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>provider-public.int.spec.ts</t>
+          <t>provider-profile.int.spec.ts</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>a published provider page: contract shape, place, photo urls, only offerable services</t>
+          <t>the draft prefills the postcode only when it is a known one</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -4552,17 +4552,17 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>Public provider data</t>
+          <t>Provider profile</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>provider-public.int.spec.ts</t>
+          <t>provider-profile.int.spec.ts</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>404 when not visible: unknown, draft, or no offerable service</t>
+          <t>a live profile cannot be emptied by a save: 409 with the missing list, nothing changed</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -4579,17 +4579,17 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>Public provider data</t>
+          <t>Provider profile</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>provider-public.int.spec.ts</t>
+          <t>provider-profile.int.spec.ts</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>a draft page is a 404 for its own owner too</t>
+          <t>a provider whose names are missing cannot publish: missing lists name</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -4606,17 +4606,17 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>Public provider data</t>
+          <t>Provider profile</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>provider-public.int.spec.ts</t>
+          <t>provider-profile.int.spec.ts</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>unknown language is 400</t>
+          <t>the draft's postcode lookup uses the owner's stored country</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>anonymous: the page carries the owner's profile photo and the public name, no display name</t>
+          <t>a published provider page: contract shape, place, photo urls, only offerable services</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -4660,17 +4660,17 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>Translate endpoint</t>
+          <t>Public provider data</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>provider-translation.int.spec.ts</t>
+          <t>provider-public.int.spec.ts</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>returns translated texts in the page shape</t>
+          <t>404 when not visible: unknown, draft, or no offerable service</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -4687,17 +4687,17 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>Translate endpoint</t>
+          <t>Public provider data</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>provider-translation.int.spec.ts</t>
+          <t>provider-public.int.spec.ts</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>a draft or suspended provider -&gt; 404, no call</t>
+          <t>a draft page is a 404 for its own owner too</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -4714,17 +4714,17 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>Translate endpoint</t>
+          <t>Public provider data</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>provider-translation.int.spec.ts</t>
+          <t>provider-public.int.spec.ts</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>unknown lang -&gt; 400</t>
+          <t>unknown language is 400</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -4741,17 +4741,17 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>Translate endpoint</t>
+          <t>Public provider data</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>provider-translation.int.spec.ts</t>
+          <t>provider-public.int.spec.ts</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>service failure -&gt; 503 and nothing stored</t>
+          <t>anonymous: the page carries the owner's profile photo and the public name, no display name</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>a logged-in caller is counted under the user id</t>
+          <t>returns translated texts in the page shape</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>the provider endpoint reports translatable per viewer language</t>
+          <t>a draft or suspended provider -&gt; 404, no call</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>accepts no text from the client</t>
+          <t>unknown lang -&gt; 400</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>fails closed without a usable secret: 503, no counter row, no model call</t>
+          <t>service failure -&gt; 503 and nothing stored</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -4876,17 +4876,17 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>Site and admin routing</t>
+          <t>Translate endpoint</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>proxy.int.spec.ts</t>
+          <t>provider-translation.int.spec.ts</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>/admin and below go through the auth middleware</t>
+          <t>a logged-in caller is counted under the user id</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -4903,17 +4903,17 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>Site and admin routing</t>
+          <t>Translate endpoint</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>proxy.int.spec.ts</t>
+          <t>provider-translation.int.spec.ts</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>/administrator or a page slug starting with admin is a site path with x-lang</t>
+          <t>the provider endpoint reports translatable per viewer language</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -4930,17 +4930,17 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>Public name</t>
+          <t>Translate endpoint</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>public-name.int.spec.ts</t>
+          <t>provider-translation.int.spec.ts</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>publicNameFor: business name, else first name and surname initial</t>
+          <t>accepts no text from the client</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -4957,17 +4957,17 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>Public name</t>
+          <t>Translate endpoint</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>public-name.int.spec.ts</t>
+          <t>provider-translation.int.spec.ts</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>slugify transliterates umlauts and strips the rest</t>
+          <t>fails closed without a usable secret: 503, no counter row, no model call</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -4984,17 +4984,17 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>Public name</t>
+          <t>Site and admin routing</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>public-name.int.spec.ts</t>
+          <t>proxy.int.spec.ts</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>public name and slug are unique and stable</t>
+          <t>/admin and below go through the auth middleware</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
@@ -5011,17 +5011,17 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>Public name</t>
+          <t>Site and admin routing</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>public-name.int.spec.ts</t>
+          <t>proxy.int.spec.ts</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>an individual without names has an empty public name and the fallback slug</t>
+          <t>/administrator or a page slug starting with admin is a site path with x-lang</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>first contact does not copy the session name: the person sets their own names</t>
+          <t>publicNameFor: business name, else first name and surname initial</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>a rename of the person changes the public name of their provider profile</t>
+          <t>slugify transliterates umlauts and strips the rest</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -5092,17 +5092,17 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>Publish and unpublish</t>
+          <t>Public name</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>publish-flow.int.spec.ts</t>
+          <t>public-name.int.spec.ts</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>the first-time flow: refused until photo and service exist, then published, then unpublished</t>
+          <t>public name and slug are unique and stable</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -5119,17 +5119,17 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>Publish and unpublish</t>
+          <t>Public name</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>publish-flow.int.spec.ts</t>
+          <t>public-name.int.spec.ts</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>a postcode-less profile is refused until a postcode is saved</t>
+          <t>an individual without names cannot publish; with names the public name follows</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -5146,17 +5146,17 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>Publish and unpublish</t>
+          <t>Public name</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>publish-flow.int.spec.ts</t>
+          <t>public-name.int.spec.ts</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>a suspended profile cannot publish (409)</t>
+          <t>first contact does not copy the session name: the person sets their own names</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -5173,17 +5173,17 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>Publish and unpublish</t>
+          <t>Public name</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>publish-flow.int.spec.ts</t>
+          <t>public-name.int.spec.ts</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>RLS: published and not suspended is public, drafts and suspended are not</t>
+          <t>a rename of the person changes the public name of their provider profile</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>RLS: another user cannot change or add to a provider; domain-only columns are closed</t>
+          <t>the first-time flow: refused until photo and service exist, then published, then unpublished</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>RLS: set_provider_* touch only the caller's own profile</t>
+          <t>a postcode-less profile is refused until a postcode is saved</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>RLS: documents are private and the verdict is staff-only</t>
+          <t>a suspended profile cannot publish (409)</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>offerableServiceIds: services whose required documents are all approved</t>
+          <t>RLS: published and not suspended is public, drafts and suspended are not</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>a user suspension that has ended no longer blocks publishing; a running one does</t>
+          <t>RLS: another user cannot change or add to a provider; domain-only columns are closed</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
@@ -5335,17 +5335,17 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>Staff check</t>
+          <t>Publish and unpublish</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>require-staff.int.spec.ts</t>
+          <t>publish-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>an active admin passes</t>
+          <t>RLS: set_provider_* touch only the caller's own profile</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
@@ -5362,17 +5362,17 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>Staff check</t>
+          <t>Publish and unpublish</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>require-staff.int.spec.ts</t>
+          <t>publish-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>a suspended admin gets 403</t>
+          <t>RLS: documents are private and the verdict is staff-only</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
@@ -5389,17 +5389,17 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>Staff check</t>
+          <t>Publish and unpublish</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>require-staff.int.spec.ts</t>
+          <t>publish-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>an expired suspension no longer blocks</t>
+          <t>offerableServiceIds: services whose required documents are all approved</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
@@ -5416,17 +5416,17 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>Row-level security</t>
+          <t>Publish and unpublish</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>rls-providers.int.spec.ts</t>
+          <t>publish-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>another user cannot update or delete a service or a reference (rowCount 0, rows unchanged)</t>
+          <t>a user suspension that has ended no longer blocks publishing; a running one does</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -5443,17 +5443,17 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>Row-level security</t>
+          <t>Staff check</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>rls-providers.int.spec.ts</t>
+          <t>require-staff.int.spec.ts</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>another user cannot insert a service or a reference for my provider</t>
+          <t>an active admin passes</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -5470,17 +5470,17 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>Row-level security</t>
+          <t>Staff check</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>rls-providers.int.spec.ts</t>
+          <t>require-staff.int.spec.ts</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>the owner cannot move a service to another provider</t>
+          <t>a suspended admin gets 403</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
@@ -5497,17 +5497,17 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>Row-level security</t>
+          <t>Staff check</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>rls-providers.int.spec.ts</t>
+          <t>require-staff.int.spec.ts</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>offerableServiceIds and missingRequirements are identical through tx and the owner db</t>
+          <t>an expired suspension no longer blocks</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>a stranger asking about a draft provider gets empty answers; the owner still gets the full ones</t>
+          <t>another user cannot update or delete a service or a reference (rowCount 0, rows unchanged)</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>a service with a category alone (no price type yet) is never offerable, not even to its owner</t>
+          <t>another user cannot insert a service or a reference for my provider</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>slugify strips accents</t>
+          <t>the owner cannot move a service to another provider</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>rls.int.spec.ts</t>
+          <t>rls-providers.int.spec.ts</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>app_user cannot read a private table row of another user</t>
+          <t>offerableServiceIds and missingRequirements are identical through tx and the owner db</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
@@ -5637,12 +5637,12 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>rls.int.spec.ts</t>
+          <t>rls-providers.int.spec.ts</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>public reference tables are readable by app_user and not writable</t>
+          <t>a stranger asking about a draft provider gets empty answers; the owner still gets the full ones</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>rls.int.spec.ts</t>
+          <t>rls-providers.int.spec.ts</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>a person's picture is private until the owner's provider is published and not suspended</t>
+          <t>a service with a category alone (no price type yet) is never offerable, not even to its owner</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>rls.int.spec.ts</t>
+          <t>rls-providers.int.spec.ts</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>notifications: the owner reads and marks own rows; another user sees none, cannot insert or change kind</t>
+          <t>slugify strips accents</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
@@ -5713,17 +5713,17 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Row-level security</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>search.int.spec.ts</t>
+          <t>rls.int.spec.ts</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>radius edge and remote providers</t>
+          <t>app_user cannot read a private table row of another user</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
@@ -5740,17 +5740,17 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Row-level security</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>search.int.spec.ts</t>
+          <t>rls.int.spec.ts</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>a remote provider more than 200 km away is found, without a distance</t>
+          <t>public reference tables are readable by app_user and not writable</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
@@ -5767,17 +5767,17 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Row-level security</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>search.int.spec.ts</t>
+          <t>rls.int.spec.ts</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>a draft is invisible to its owner too</t>
+          <t>a person's picture is private until the owner's provider is published and not suspended</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
@@ -5794,17 +5794,17 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Row-level security</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>search.int.spec.ts</t>
+          <t>rls.int.spec.ts</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>distance is whole km, at least 1, hidden for remote providers outside the radius</t>
+          <t>notifications: the owner reads and marks own rows; another user sees none, cannot insert or change kind</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>a draft, a suspended or a provider without an offerable service never appears</t>
+          <t>radius edge and remote providers</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>category filter and q (public name and skills, case-insensitive)</t>
+          <t>a remote provider more than 200 km away is found, without a distance</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>bad input is 400: unknown postcode, bad format, unknown country, unknown language, bad page</t>
+          <t>a draft is invisible to its owner too</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>paging: 20 per page and hasMore</t>
+          <t>distance is whole km, at least 1, hidden for remote providers outside the radius</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>anonymous: the card carries the owner's profile photo and the public name, no display name</t>
+          <t>a draft, a suspended or a provider without an offerable service never appears</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>a provider whose only service has no price type is neither found nor has a public page</t>
+          <t>category filter and q (public name and skills, case-insensitive)</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
@@ -5983,17 +5983,17 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>search.int.spec.ts</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>categories seed is idempotent: 14 categories, both names, babysitting needs a police certificate</t>
+          <t>bad input is 400: unknown postcode, bad format, unknown country, unknown language, bad page</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
@@ -6010,17 +6010,17 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>search.int.spec.ts</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>postcode import upserts: a second run leaves the same count</t>
+          <t>paging: 20 per page and hasMore</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
@@ -6037,17 +6037,17 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>search.int.spec.ts</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>the dev guard needs the dev branch AND the dev database host</t>
+          <t>anonymous: the card carries the owner's profile photo and the public name, no display name</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
@@ -6064,17 +6064,17 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>search.int.spec.ts</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>loadSeedData reads the git-ignored list or the committed example, and rejects a broken file</t>
+          <t>a provider whose only service has no price type is neither found nor has a public page</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
@@ -6091,17 +6091,17 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>search.int.spec.ts</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>seedTestUsers itself refuses outside dev, before touching anything</t>
+          <t>a fixed service without a price is not found in its category</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>builds the test users through the domain: published providers with photo, services, public names, verified; a rerun adds nothing</t>
+          <t>categories seed is idempotent: 14 categories, both names, babysitting needs a police certificate</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>a run that crashed after the services (no photo, not published) resumes without adding the services twice</t>
+          <t>postcode import upserts: a second run leaves the same count</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>placeholder photos: gives a published profile without a photo one; elsewhere needs the typed yes</t>
+          <t>the dev guard needs the dev branch AND the dev database host</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>neonAuth retries a 429, then succeeds</t>
+          <t>loadSeedData reads the git-ignored list or the committed example, and rejects a broken file</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>neonAuth signs in when the email already exists</t>
+          <t>seedTestUsers itself refuses outside dev, before touching anything</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>neonAuth surfaces any other sign-up failure without falling back to sign-in</t>
+          <t>builds the test users through the domain: published providers with photo, services, public names, verified; a rerun adds nothing</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
@@ -6280,17 +6280,17 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>Services and references</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>services-references.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>a service needs a profile first (409)</t>
+          <t>a run that crashed after the services (no photo, not published) resumes without adding the services twice</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
@@ -6307,17 +6307,17 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>Services and references</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>services-references.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>create, list and patch a service; shapes fit the contract</t>
+          <t>placeholder photos: gives a published profile without a photo one; elsewhere needs the typed yes</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
@@ -6334,17 +6334,17 @@
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>Services and references</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>services-references.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>on-request has no price, even when one is sent</t>
+          <t>neonAuth retries a 429, then succeeds</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
@@ -6361,17 +6361,17 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>Services and references</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>services-references.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>bad service input: no price, three decimals, unknown category are 400</t>
+          <t>neonAuth signs in when the email already exists</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
@@ -6388,17 +6388,17 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>Services and references</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>services-references.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>a service in a category with required documents waits for approval</t>
+          <t>neonAuth surfaces any other sign-up failure without falling back to sign-in</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>user A cannot edit or delete user B's service</t>
+          <t>a service needs a profile first (409)</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>references are capped at 2 (409), can be patched and deleted</t>
+          <t>create, list and patch a service; shapes fit the contract</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>a service with a category alone is saved, not offerable, and a patch accepts the partial shape</t>
+          <t>on-request has no price, even when one is sent</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
@@ -6496,17 +6496,17 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>Sitemaps</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>sitemaps.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>providers sitemap lists only visible providers</t>
+          <t>bad service input: no price, three decimals, unknown category are 400</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
@@ -6523,17 +6523,17 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>Sitemaps</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>sitemaps.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>pages sitemap lists the home page and published pages only</t>
+          <t>a service in a category with required documents waits for approval</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
@@ -6550,17 +6550,17 @@
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>Sitemaps</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>sitemaps.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>robots.txt allows the site, keeps the admin out and points at both sitemaps</t>
+          <t>user A cannot edit or delete user B's service</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
@@ -6577,17 +6577,17 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>Smoke test</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>smoke.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>connects to the test database and sees PostGIS</t>
+          <t>references are capped at 2 (409), can be patched and deleted</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
@@ -6604,17 +6604,17 @@
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>Test database guard</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>test-guard.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>the test guard refuses a non-local or non-test URL</t>
+          <t>a service with a category alone is saved, not offerable, and a patch accepts the partial shape</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
@@ -6631,17 +6631,17 @@
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>translate stores translations and serves the second request from the store without a call</t>
+          <t>the price type and the price save in either order, each as its own one-field save</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
@@ -6658,17 +6658,17 @@
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>translate an edited text is re-translated, the rest comes from the store</t>
+          <t>a fixed service without a price is not offerable, with a price it is; on-request clears the price</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
@@ -6685,17 +6685,17 @@
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Sitemaps</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>sitemaps.int.spec.ts</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>translate texts already in the target language are returned unchanged without a call</t>
+          <t>providers sitemap lists only visible providers</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
@@ -6712,17 +6712,17 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Sitemaps</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>sitemaps.int.spec.ts</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>translate a malformed or incomplete model answer stores nothing and throws TranslationUnavailable</t>
+          <t>pages sitemap lists the home page and published pages only</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
@@ -6739,17 +6739,17 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Sitemaps</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>sitemaps.int.spec.ts</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>translate a non-2xx answer throws TranslationUnavailable</t>
+          <t>robots.txt allows the site, keeps the admin out and points at both sitemaps</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
@@ -6766,17 +6766,17 @@
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Smoke test</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>smoke.int.spec.ts</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>translate line breaks survive</t>
+          <t>connects to the test database and sees PostGIS</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
@@ -6793,17 +6793,17 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Test database guard</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>test-guard.int.spec.ts</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>translate no key -&gt; TranslationUnavailable without a call</t>
+          <t>the test guard refuses a non-local or non-test URL</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>translate the 31st AI call within an hour for one client key -&gt; TranslationUnavailable</t>
+          <t>stores translations and serves the second request from the store without a call</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>translate the limit boundary: the 30th call passes, the 31st is refused</t>
+          <t>an edited text is re-translated, the rest comes from the store</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>translate a timeout -&gt; TranslationUnavailable</t>
+          <t>texts already in the target language are returned unchanged without a call</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>translate concurrent translations of the same page store one row per text</t>
+          <t>a malformed or incomplete model answer stores nothing and throws TranslationUnavailable</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>translate writes through the request transaction and commits with it</t>
+          <t>a non-2xx answer throws TranslationUnavailable</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>translate the default timeout is 12 seconds</t>
+          <t>line breaks survive</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>translate French and Afrikaans texts are flagged and sent to the model, in either viewer language</t>
+          <t>no key -&gt; TranslationUnavailable without a call</t>
         </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>translate a page the detector cannot classify is translated when long enough, left alone when short</t>
+          <t>the 31st AI call within an hour for one client key -&gt; TranslationUnavailable</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>translate a German profile of short skills and titles needs no translation for de but does for en</t>
+          <t>the limit boundary: the 30th call passes, the 31st is refused</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>translate a Markdown-fenced answer parses; the request carries max_tokens</t>
+          <t>a timeout -&gt; TranslationUnavailable</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>translate an empty string from the model stores nothing</t>
+          <t>concurrent translations of the same page store one row per text</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>translate counter rows older than 24 hours are deleted; recent ones stay</t>
+          <t>writes through the request transaction and commits with it</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>translate anonymous client keys are salted hashes, never the raw IP</t>
+          <t>the default timeout is 12 seconds</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>translate textsOf picks the translatable fields of a profile</t>
+          <t>French and Afrikaans texts are flagged and sent to the model, in either viewer language</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>translate needsTranslation is false for a page entirely in the viewer language and true for a mixed page</t>
+          <t>a page the detector cannot classify is translated when long enough, left alone when short</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>translation tables are insert-only for app_user anonymous callers can insert and read, never update or delete</t>
+          <t>a German profile of short skills and titles needs no translation for de but does for en</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
@@ -7252,22 +7252,22 @@
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>Share profile</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>share-profile.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>the provider page url carries the language only when it is not the default</t>
+          <t>a Markdown-fenced answer parses; the request carries max_tokens</t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E248" s="4" t="inlineStr">
@@ -7279,22 +7279,22 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>Share profile</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>share-profile.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>shareProfile passes the url and the text in the given language</t>
+          <t>an empty string from the model stores nothing</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E249" s="4" t="inlineStr">
@@ -7306,22 +7306,22 @@
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>server errors land on the right field</t>
+          <t>counter rows older than 24 hours are deleted; recent ones stay</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E250" s="4" t="inlineStr">
@@ -7333,22 +7333,22 @@
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>withItem adds a trimmed new skill or strength once and ignores blanks</t>
+          <t>anonymous client keys are salted hashes, never the raw IP</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E251" s="4" t="inlineStr">
@@ -7360,22 +7360,22 @@
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>the form-level error shows unless every server error has an inline slot</t>
+          <t>textsOf picks the translatable fields of a profile</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E252" s="4" t="inlineStr">
@@ -7387,22 +7387,22 @@
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>service and reference validation</t>
+          <t>needsTranslation is false for a page entirely in the viewer language and true for a mixed page</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E253" s="4" t="inlineStr">
@@ -7414,22 +7414,22 @@
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>every missing item the publish route can return has de and en text</t>
+          <t>anonymous callers can insert and read, never update or delete</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E254" s="4" t="inlineStr">
@@ -7441,22 +7441,22 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Sign-up and session</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>auth-cookie-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>the service body names the category by id and the currency, as the server expects</t>
+          <t>signs up by REST, captures the cookie; /app-api/v1/me knows the session but refuses it until the email is confirmed</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E255" s="4" t="inlineStr">
@@ -7468,17 +7468,17 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Address fields</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>address-fields.test.ts</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>a 400 "Invalid input" marks each named field</t>
+          <t>toAddress: empty is null (clears), complete is DE, partial is undefined</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
@@ -7495,17 +7495,17 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>Address fields</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>address-fields.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>toAddress: empty is null (clears), complete is DE, partial is undefined</t>
+          <t>server errors land on the right field</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>texts come from the shared catalogue, in the chosen language, with placeholders filled</t>
+          <t>withItem adds a trimmed new skill or strength once and ignores blanks</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
@@ -7554,12 +7554,12 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>the translate button texts exist in both languages</t>
+          <t>the form-level error shows unless every server error has an inline slot</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>errorText maps the auth server codes to catalogue messages</t>
+          <t>service and reference validation</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>errorText maps the app API strings</t>
+          <t>every missing item the publish route can return has de and en text</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>docText maps known document codes and passes unknown ones through</t>
+          <t>the service body names the category by id and the currency, as the server expects</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>a failed check after the upload deletes the uploaded file and reports the original error</t>
+          <t>a 400 "Invalid input" marks each named field</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>a successful submit deletes nothing</t>
+          <t>live means published and not suspended now (the server rule of listServices)</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
@@ -7711,17 +7711,17 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Share profile</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>share-profile.test.ts</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>a failing clean-up does not hide the original error</t>
+          <t>the provider page url carries the language only when it is not the default</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
@@ -7738,17 +7738,17 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Share profile</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>share-profile.test.ts</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>loading -&gt; signed in -&gt; signed out</t>
+          <t>shareProfile passes the url and the text in the given language</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>an unverified email never counts as signed in: sign-in sends a code and asks for it</t>
+          <t>signUp posts email, password and name and stores the session cookie</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
@@ -7797,12 +7797,12 @@
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>a server that refuses unverified sign-ins (EMAIL_NOT_VERIFIED) also leads to the code screen</t>
+          <t>signIn posts email and password and returns the user</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>sign-up creates the account and sends the code; the right code signs in and saves the account name</t>
+          <t>a refused sign-in throws the server code, which maps to a catalogue message</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>a wrong code throws and keeps signed out</t>
+          <t>signOut forgets the session at once and tells the server with the old cookie</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>a failed login rejects and keeps signed out; a server error on load means signed out</t>
+          <t>signOut offline still signs out</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>a network error on load sets offline (not signed out); retry recovers</t>
+          <t>session reads get-session with the cookie; no cookie means null without a request</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>onUnauthorized from the API client signs the user out</t>
+          <t>session throws on a network error (the app offers a retry, not the login)</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>updateName saves the account name in both places and updates the session user; a failure keeps the old one</t>
+          <t>sendVerificationCode asks for an email-verification code</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>switching the language also saves it for emails, but only while signed in</t>
+          <t>verifyEmail sends the code as otp, stores the new session and returns the user</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>verify finishes the sign-up: names and address, then the picture, then the record is cleared; returns the tick</t>
+          <t>requestPasswordReset asks for a reset code</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>a failed upload keeps the record; loadSession retries it once and clears it</t>
+          <t>resetPassword sends email, code and the new password</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>loadSession without a record or while signed out does not finish a sign-up</t>
+          <t>a wrong code throws INVALID_OTP, shown as the code message</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>a record for another email is dropped and applies nothing</t>
+          <t>updateUserName changes the name on the auth account</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>a failed PATCH keeps the full record</t>
+          <t>signUp and signIn start without an old stored session</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>after the PATCH succeeded, a failed upload keeps only email, tick and picture; the retry does not PATCH again</t>
+          <t>prices follow the website rules in German and English</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>a picture whose cached file is gone is dropped and the record cleared</t>
+          <t>distance shows km, remote or nothing</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
@@ -8202,12 +8202,12 @@
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>sign-up keeps the record for the code step; a failed sign-up leaves none</t>
+          <t>search path leaves out empty filters and trims text</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>prices follow the website rules in German and English</t>
+          <t>photoSrc loads only absolute http(s) URLs, never a server-relative /api path</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>distance shows km, remote or nothing</t>
+          <t>a failed check after the upload deletes the uploaded file and reports the original error</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>search path leaves out empty filters and trims text</t>
+          <t>a successful submit deletes nothing</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>photoSrc loads only absolute http(s) URLs, never a server-relative /api path</t>
+          <t>a failing clean-up does not hide the original error</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>preparePhoto keeps the long side at 1600 px</t>
+          <t>texts come from the shared catalogue, in the chosen language, with placeholders filled</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
@@ -8364,12 +8364,12 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>tooLarge is true above 4_434_464 bytes</t>
+          <t>the translate button texts exist in both languages</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>pickPhoto cancelled is null</t>
+          <t>errorText maps the auth server codes to catalogue messages</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>pickPhoto a refused permission is denied, not cancelled</t>
+          <t>errorText maps the app API strings</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>pickDocument offers PDFs and the image types the server accepts, from any file source</t>
+          <t>docText maps known document codes and passes unknown ones through</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>pickDocument cancelled is null</t>
+          <t>preparePhoto keeps the long side at 1600 px</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
@@ -8499,12 +8499,12 @@
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>sends the stored cookie and stores a new set-cookie</t>
+          <t>tooLarge is true above 4_434_464 bytes</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>a single joined set-cookie header (no getSetCookie) is split into its cookies</t>
+          <t>cancelled is null</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>clears the session on 401</t>
+          <t>a refused permission is denied, not cancelled</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>a 401 without a stored session does not call onUnauthorized</t>
+          <t>offers PDFs and the image types the server accepts, from any file source</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>every request names the app origin and leaves the platform cookie store out</t>
+          <t>cancelled is null</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
@@ -8634,12 +8634,12 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>a 409 with error and missing throws ApiError with code and missing</t>
+          <t>loading -&gt; signed in -&gt; signed out</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>a 400 "Invalid input" lists the fields named by its issues</t>
+          <t>an unverified email never counts as signed in: sign-in sends a code and asks for it</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>a network failure throws ApiError(0, network)</t>
+          <t>a server that refuses unverified sign-ins (EMAIL_NOT_VERIFIED) also leads to the code screen</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -8715,12 +8715,12 @@
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>a server that never answers fails as network after the time limit</t>
+          <t>sign-up creates the account and sends the code; the right code signs in and saves the account name</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>saves have no time limit: a slow save that succeeds is not reported as a failure</t>
+          <t>a wrong code throws and keeps signed out</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>updateMe PATCHes the account name</t>
+          <t>a failed login rejects and keeps signed out; a server error on load means signed out</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
@@ -8796,12 +8796,12 @@
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>upload sends multipart with the cookie and no time limit</t>
+          <t>a network error on load sets offline (not signed out); retry recovers</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>upload sends the file bytes with its name and type, not a bare { uri } object</t>
+          <t>onUnauthorized from the API client signs the user out</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>a file the phone cannot open is "File unreadable", not a network error, and nothing is sent</t>
+          <t>updateName saves the account name in both places and updates the session user; a failure keeps the old one</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>upload maps a 413 to ApiError "File too large"</t>
+          <t>switching the language also saves it for emails, but only while signed in</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>upload maps a network failure to ApiError network and does not retry</t>
+          <t>verify finishes the sign-up: names and address, then the picture, then the record is cleared; returns the tick</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>a store that cannot be read (Keystore failure) sends the request without a cookie</t>
+          <t>a failed upload keeps the record; loadSession retries it once and clears it</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>a cookie that cannot be saved does not fail a request the server already carried out</t>
+          <t>loadSession without a record or while signed out does not finish a sign-up</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>a malformed Set-Cookie line without "=" is skipped</t>
+          <t>a record for another email is dropped and applies nothing</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
@@ -9012,12 +9012,12 @@
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>updateMe sends the one-field name as first and last name, split at the last space</t>
+          <t>a failed PATCH keeps the full record</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>no rows when no service needs a document</t>
+          <t>after the PATCH succeeded, a failed upload keeps only email, tick and picture; the retry does not PATCH again</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>a babysitting service with nothing uploaded â†’ police-certificate none</t>
+          <t>a picture whose cached file is gone is dropped and the record cleared</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -9093,12 +9093,12 @@
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>the most recently reviewed check decides, like the server</t>
+          <t>sign-up keeps the record for the code step; a failed sign-up leaves none</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>a pending check shows pending even after an approval</t>
+          <t>sends the stored cookie and stores a new set-cookie</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -9147,12 +9147,12 @@
       </c>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>a requirement code the app does not know still gets a row, after the known ones</t>
+          <t>a single joined set-cookie header (no getSetCookie) is split into its cookies</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>two services needing the same document give one row</t>
+          <t>clears the session on 401</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>two different categories needing the same document give one row with the latest status</t>
+          <t>a 401 without a stored session does not call onUnauthorized</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>a hidden service says a document is needed until it is uploaded, then that it waits for the check</t>
+          <t>every request names the app origin and leaves the platform cookie store out</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>sharing is allowed only while no service waits for a document</t>
+          <t>a 409 with error and missing throws ApiError with code and missing</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
@@ -9282,12 +9282,12 @@
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>signUp posts email, password and name and stores the session cookie</t>
+          <t>a 400 "Invalid input" lists the fields named by its issues</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>signIn posts email and password and returns the user</t>
+          <t>a network failure throws ApiError(0, network)</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
@@ -9336,12 +9336,12 @@
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>a refused sign-in throws the server code, which maps to a catalogue message</t>
+          <t>a server that never answers fails as network after the time limit</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>signOut forgets the session at once and tells the server with the old cookie</t>
+          <t>saves have no time limit: a slow save that succeeds is not reported as a failure</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>signOut offline still signs out</t>
+          <t>updateMe PATCHes the account name</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -9417,12 +9417,12 @@
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>session reads get-session with the cookie; no cookie means null without a request</t>
+          <t>upload sends multipart with the cookie and no time limit</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>session throws on a network error (the app offers a retry, not the login)</t>
+          <t>upload sends the file bytes with its name and type, not a bare { uri } object</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>sendVerificationCode asks for an email-verification code</t>
+          <t>a file the phone cannot open is "File unreadable", not a network error, and nothing is sent</t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>verifyEmail sends the code as otp, stores the new session and returns the user</t>
+          <t>upload maps a 413 to ApiError "File too large"</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>requestPasswordReset asks for a reset code</t>
+          <t>upload maps a network failure to ApiError network and does not retry</t>
         </is>
       </c>
       <c r="D332" s="4" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>resetPassword sends email, code and the new password</t>
+          <t>a store that cannot be read (Keystore failure) sends the request without a cookie</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>a wrong code throws INVALID_OTP, shown as the code message</t>
+          <t>a cookie that cannot be saved does not fail a request the server already carried out</t>
         </is>
       </c>
       <c r="D334" s="4" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>updateUserName changes the name on the auth account</t>
+          <t>a malformed Set-Cookie line without "=" is skipped</t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>signUp and signIn start without an old stored session</t>
+          <t>updateMe sends the one-field name as first and last name, split at the last space</t>
         </is>
       </c>
       <c r="D336" s="4" t="inlineStr">
@@ -9655,17 +9655,17 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Pending signup</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>pending-signup.test.ts</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>applyTexts swaps only the translatable fields and keeps names, prices and photos</t>
+          <t>the pending record round-trips and clears</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="B338" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C338" s="4" t="inlineStr">
         <is>
-          <t>applyTexts matches services and references by id and leaves unknown ones untouched</t>
+          <t>no rows when no service needs a document</t>
         </is>
       </c>
       <c r="D338" s="4" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="B339" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>applyTexts keeps line breaks</t>
+          <t>a babysitting service with nothing uploaded â†’ police-certificate none</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
@@ -9736,17 +9736,17 @@
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B340" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C340" s="4" t="inlineStr">
         <is>
-          <t>two quick changes become one request with the last value</t>
+          <t>the most recently reviewed check decides, like the server</t>
         </is>
       </c>
       <c r="D340" s="4" t="inlineStr">
@@ -9763,17 +9763,17 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>flush saves immediately and nothing is sent twice</t>
+          <t>a pending check shows pending even after an approval</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
@@ -9790,17 +9790,17 @@
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B342" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>a rejected save marks error and retry resends the same value</t>
+          <t>a requirement code the app does not know still gets a row, after the known ones</t>
         </is>
       </c>
       <c r="D342" s="4" t="inlineStr">
@@ -9817,17 +9817,17 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>a change typed while a save is in flight is sent after it, in order</t>
+          <t>two services needing the same document give one row</t>
         </is>
       </c>
       <c r="D343" s="4" t="inlineStr">
@@ -9844,17 +9844,17 @@
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B344" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>dispose sends a pending change so nothing typed is lost</t>
+          <t>two different categories needing the same document give one row with the latest status</t>
         </is>
       </c>
       <c r="D344" s="4" t="inlineStr">
@@ -9876,12 +9876,12 @@
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>auth-layout.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C345" s="4" t="inlineStr">
         <is>
-          <t>logged-out landing route is login</t>
+          <t>a hidden service says a document is needed until it is uploaded, then that it waits for the check</t>
         </is>
       </c>
       <c r="D345" s="4" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="B346" s="4" t="inlineStr">
         <is>
-          <t>auth-layout.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C346" s="4" t="inlineStr">
         <is>
-          <t>no test files inside src/app (each file there becomes a screen)</t>
+          <t>sharing is allowed only while no service waits for a document</t>
         </is>
       </c>
       <c r="D346" s="4" t="inlineStr">
@@ -9925,17 +9925,17 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>Use me</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>use-me.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>a loadMe in flight at sign-out never fills the store for the next account</t>
+          <t>applyTexts swaps only the translatable fields and keeps names, prices and photos</t>
         </is>
       </c>
       <c r="D347" s="4" t="inlineStr">
@@ -9952,17 +9952,17 @@
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>Pending signup</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B348" s="4" t="inlineStr">
         <is>
-          <t>pending-signup.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C348" s="4" t="inlineStr">
         <is>
-          <t>the pending record round-trips and clears</t>
+          <t>applyTexts matches services and references by id and leaves unknown ones untouched</t>
         </is>
       </c>
       <c r="D348" s="4" t="inlineStr">
@@ -9979,17 +9979,17 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>Serial create</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>serial-create.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>choosing twice before the create returns creates once, then updates</t>
+          <t>applyTexts keeps line breaks</t>
         </is>
       </c>
       <c r="D349" s="4" t="inlineStr">
@@ -10006,17 +10006,17 @@
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>Serial create</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B350" s="4" t="inlineStr">
         <is>
-          <t>serial-create.test.ts</t>
+          <t>auth-layout.test.ts</t>
         </is>
       </c>
       <c r="C350" s="4" t="inlineStr">
         <is>
-          <t>an existing id is only updated</t>
+          <t>logged-out landing route is login</t>
         </is>
       </c>
       <c r="D350" s="4" t="inlineStr">
@@ -10033,17 +10033,17 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>Stale guard</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
         <is>
-          <t>stale-guard.test.ts</t>
+          <t>auth-layout.test.ts</t>
         </is>
       </c>
       <c r="C351" s="4" t="inlineStr">
         <is>
-          <t>a response older than one already applied is ignored</t>
+          <t>no test files inside src/app (each file there becomes a screen)</t>
         </is>
       </c>
       <c r="D351" s="4" t="inlineStr">
@@ -10060,17 +10060,17 @@
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>Stale guard</t>
+          <t>Serial create</t>
         </is>
       </c>
       <c r="B352" s="4" t="inlineStr">
         <is>
-          <t>stale-guard.test.ts</t>
+          <t>serial-create.test.ts</t>
         </is>
       </c>
       <c r="C352" s="4" t="inlineStr">
         <is>
-          <t>answers arriving in order are all applied</t>
+          <t>choosing twice before the create returns creates once, then updates</t>
         </is>
       </c>
       <c r="D352" s="4" t="inlineStr">
@@ -10087,17 +10087,17 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Serial create</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>match.test.ts</t>
+          <t>serial-create.test.ts</t>
         </is>
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>matches ignores case and accents, and an empty query matches everything</t>
+          <t>an existing id is only updated</t>
         </is>
       </c>
       <c r="D353" s="4" t="inlineStr">
@@ -10114,22 +10114,22 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>match.test.ts</t>
         </is>
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>ServiceInputSchema rejects three decimals and negative prices</t>
+          <t>matches ignores case and accents, and an empty query matches everything</t>
         </is>
       </c>
       <c r="D354" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E354" s="4" t="inlineStr">
@@ -10141,22 +10141,22 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>ServiceInputSchema needs no price on request</t>
+          <t>two quick changes become one request with the last value</t>
         </is>
       </c>
       <c r="D355" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E355" s="4" t="inlineStr">
@@ -10168,22 +10168,22 @@
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B356" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>AdminListQuerySchema caps pageSize at 100</t>
+          <t>flush saves immediately and nothing is sent twice</t>
         </is>
       </c>
       <c r="D356" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E356" s="4" t="inlineStr">
@@ -10195,22 +10195,22 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>parse helpers parseBody answers 400 with the issues</t>
+          <t>a rejected save marks error and retry resends the same value</t>
         </is>
       </c>
       <c r="D357" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E357" s="4" t="inlineStr">
@@ -10222,22 +10222,22 @@
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B358" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C358" s="4" t="inlineStr">
         <is>
-          <t>parse helpers parseQuery reads the search params</t>
+          <t>a change typed while a save is in flight is sent after it, in order</t>
         </is>
       </c>
       <c r="D358" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E358" s="4" t="inlineStr">
@@ -10249,22 +10249,22 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>list envelopes lists are { docs: [...] }</t>
+          <t>dispose sends a pending change so nothing typed is lost</t>
         </is>
       </c>
       <c r="D359" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E359" s="4" t="inlineStr">
@@ -10276,22 +10276,22 @@
     <row r="360">
       <c r="A360" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Stale guard</t>
         </is>
       </c>
       <c r="B360" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>stale-guard.test.ts</t>
         </is>
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>list envelopes reference year is checked against the current year at parse time</t>
+          <t>a response older than one already applied is ignored</t>
         </is>
       </c>
       <c r="D360" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E360" s="4" t="inlineStr">
@@ -10303,22 +10303,22 @@
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Stale guard</t>
         </is>
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>stale-guard.test.ts</t>
         </is>
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>catalogue de and en have the same keys</t>
+          <t>answers arriving in order are all applied</t>
         </is>
       </c>
       <c r="D361" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E361" s="4" t="inlineStr">
@@ -10330,22 +10330,22 @@
     <row r="362">
       <c r="A362" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Use me</t>
         </is>
       </c>
       <c r="B362" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>use-me.test.ts</t>
         </is>
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>catalogue no text is empty and no two keys of one namespace carry the same text</t>
+          <t>a loadMe in flight at sign-out never fills the store for the next account</t>
         </is>
       </c>
       <c r="D362" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E362" s="4" t="inlineStr">
@@ -10357,7 +10357,7 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
@@ -10367,7 +10367,7 @@
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>catalogue no text contains Treuhand, Escrow, garantiert or a competitor name</t>
+          <t>rejects three decimals and negative prices</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
@@ -10384,7 +10384,7 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
@@ -10394,7 +10394,7 @@
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>catalogue the product name is only written in brand.name</t>
+          <t>needs no price on request</t>
         </is>
       </c>
       <c r="D364" s="4" t="inlineStr">
@@ -10411,7 +10411,7 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>t replaces placeholders and falls back to the key when missing</t>
+          <t>caps pageSize at 100</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr">
@@ -10438,7 +10438,7 @@
     <row r="366">
       <c r="A366" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B366" s="4" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="C366" s="4" t="inlineStr">
         <is>
-          <t>t fills the brand name without a parameter</t>
+          <t>parseBody answers 400 with the issues</t>
         </is>
       </c>
       <c r="D366" s="4" t="inlineStr">
@@ -10465,7 +10465,7 @@
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B367" s="4" t="inlineStr">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="C367" s="4" t="inlineStr">
         <is>
-          <t>t knows its languages</t>
+          <t>parseQuery reads the search params</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
@@ -10492,7 +10492,7 @@
     <row r="368">
       <c r="A368" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B368" s="4" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="C368" s="4" t="inlineStr">
         <is>
-          <t>money formats per language</t>
+          <t>lists are { docs: [...] }</t>
         </is>
       </c>
       <c r="D368" s="4" t="inlineStr">
@@ -10519,7 +10519,7 @@
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B369" s="4" t="inlineStr">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="C369" s="4" t="inlineStr">
         <is>
-          <t>money formats price labels from the catalogue</t>
+          <t>reference year is checked against the current year at parse time</t>
         </is>
       </c>
       <c r="D369" s="4" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="C370" s="4" t="inlineStr">
         <is>
-          <t>acceptLang en-GB,en;q=0.9,de;q=0.8 -&gt; en</t>
+          <t>de and en have the same keys</t>
         </is>
       </c>
       <c r="D370" s="4" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="C371" s="4" t="inlineStr">
         <is>
-          <t>acceptLang * -&gt; undefined</t>
+          <t>no text is empty and no two keys of one namespace carry the same text</t>
         </is>
       </c>
       <c r="D371" s="4" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="C372" s="4" t="inlineStr">
         <is>
-          <t>acceptLang fr-FR -&gt; undefined</t>
+          <t>no text contains Treuhand, Escrow, garantiert or a competitor name</t>
         </is>
       </c>
       <c r="D372" s="4" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>acceptLang  -&gt; undefined</t>
+          <t>the product name is only written in brand.name</t>
         </is>
       </c>
       <c r="D373" s="4" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>acceptLang undefined -&gt; undefined</t>
+          <t>replaces placeholders and falls back to the key when missing</t>
         </is>
       </c>
       <c r="D374" s="4" t="inlineStr">
@@ -10673,6 +10673,249 @@
         </is>
       </c>
       <c r="E374" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B375" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C375" s="4" t="inlineStr">
+        <is>
+          <t>fills the brand name without a parameter</t>
+        </is>
+      </c>
+      <c r="D375" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E375" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B376" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C376" s="4" t="inlineStr">
+        <is>
+          <t>knows its languages</t>
+        </is>
+      </c>
+      <c r="D376" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E376" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B377" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C377" s="4" t="inlineStr">
+        <is>
+          <t>formats per language</t>
+        </is>
+      </c>
+      <c r="D377" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E377" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B378" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C378" s="4" t="inlineStr">
+        <is>
+          <t>formats price labels from the catalogue</t>
+        </is>
+      </c>
+      <c r="D378" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E378" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B379" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C379" s="4" t="inlineStr">
+        <is>
+          <t>en-GB,en;q=0.9,de;q=0.8 -&gt; en</t>
+        </is>
+      </c>
+      <c r="D379" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E379" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B380" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C380" s="4" t="inlineStr">
+        <is>
+          <t>* -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D380" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E380" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B381" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C381" s="4" t="inlineStr">
+        <is>
+          <t>fr-FR -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D381" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E381" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B382" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C382" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D382" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E382" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B383" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C383" s="4" t="inlineStr">
+        <is>
+          <t>undefined -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D383" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E383" s="4" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
@@ -10782,7 +11025,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>35 files, 246 tests.</t>
+          <t>35 files, 254 tests (the root run); the Neon Auth cookie-flow spec timed out once at 5 s and passed alone on the rerun.</t>
         </is>
       </c>
     </row>
@@ -10826,7 +11069,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>246 tests. The Neon Auth cookie-flow spec (real service, 5 s limit) passed on the first run; no rerun was needed.</t>
+          <t>254 tests. The Neon Auth cookie-flow spec (real service, 5 s limit) timed out once in the full run and passed when run alone.</t>
         </is>
       </c>
     </row>
@@ -10848,7 +11091,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>106 tests.</t>
+          <t>107 tests.</t>
         </is>
       </c>
     </row>
@@ -11413,7 +11656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -11526,17 +11769,17 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Parked: lift on a non-suspended user</t>
+          <t>Fixed: emails on suspension and lift</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Lifting a suspension on a user who is not suspended still sends "published again".</t>
+          <t>Suspension and "published again" emails go only to a person who has a profile; a lift sends only when the user was suspended; the cron only emails people with a profile (a294569).</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Parked (minor)</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -11769,12 +12012,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Still to come before the pull request is merged.</t>
+          <t>Done. One Critical (service price could not be saved), two Important and the Minor points were fixed in a final fix wave; a scoped re-review follows.</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed, re-review pending</t>
         </is>
       </c>
     </row>
@@ -11786,7 +12029,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Add it to Production and Preview, or the daily check answers 401 and suspensions never end by date.</t>
+          <t>Add it to Production (Vercel runs crons on Production only), or the daily check answers 401 and suspensions never end by date.</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11809,6 +12052,176 @@
       <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Owner, before ship</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (final review 1, Critical): service price</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>The price type and the price save in either order; a service counts only with a type and, unless on request, a price (completeness, offerable ids, search) (fd98b0b).</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (final review 2): live profile cannot be emptied</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>A save that would leave a published profile incomplete is refused with 409 and the missing list (eb614ff).</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (final review 3): staff and the picture</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>The provider page lists the person's picture and the user page has a Delete button for it (167b75d).</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (final review 5): country in the UI</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Postcode lookup uses the owner's stored country, the setup postcode field is plain text, the Account save keeps the stored country (7616177).</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (final review 6): publish bar</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>A suspended profile shows the suspension, not Live (d815883).</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (final review 7): name required to publish</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>The missing list has "name" when first or last name is empty (eb614ff).</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (final review 8): picture key</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>The public picture key has a random folder, not the account id (d815883).</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (final review 9): Account screen</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Changing the picture no longer resets unsaved name and address edits (7616177).</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (final review 10): docs</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>CRON_SECRET in .env.example; crons run on Production only; orphaned photo objects after migration 0008 are noted (585f274).</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Parked: one shared "not suspended" SQL constant</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>The "not suspended" test is written out in about eight SQL places (rls.ts, search.ts, public-profile.ts, sitemap) plus TypeScript variants; they agree today, one shared constant would keep it so.</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Parked (minor)</t>
         </is>
       </c>
     </row>

--- a/Reports/Registration-Setup-Test-Report.xlsx
+++ b/Reports/Registration-Setup-Test-Report.xlsx
@@ -454,7 +454,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Full suite on branch registration-setup (after the final fix wave), run 27 October 2026: web integration tests on the local Docker database, app and package unit tests. Features only a phone can confirm are marked Not yet done (phone) in Other Checks.</t>
+          <t>Full suite on branch registration-setup (after fix wave 2 of the independent review), run 27 October 2026: web integration tests on the local Docker database, app and package unit tests. Features only a phone can confirm are marked Not yet done (phone) in Other Checks.</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTA('Test Results'!C2:C383)</f>
+        <f>COUNTA('Test Results'!C2:C389)</f>
         <v/>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Test Results'!E2:E383,"Passed")</f>
+        <f>COUNTIF('Test Results'!E2:E389,"Passed")</f>
         <v/>
       </c>
     </row>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Test Results'!E2:E383,"Failed")</f>
+        <f>COUNTIF('Test Results'!E2:E389,"Failed")</f>
         <v/>
       </c>
     </row>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF('Test Results'!E2:E383,"Skipped")</f>
+        <f>COUNTIF('Test Results'!E2:E389,"Skipped")</f>
         <v/>
       </c>
     </row>
@@ -532,18 +532,18 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Package tests (contract 7, i18n 14)</t>
+          <t>Package tests (contract 9, i18n 14)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E383"/>
+  <dimension ref="A1:E389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1042,17 +1042,17 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Admin lang</t>
+          <t>Admin back office API</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>admin-lang.int.spec.ts</t>
+          <t>admin-api.int.spec.ts</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>{"cookie":"en"} -&gt; en</t>
+          <t>suspension and published-again emails go to published profiles only; the cron still clears every ended suspension</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>{"cookie":"fr"} -&gt; de</t>
+          <t>adminLang {"cookie":"en"} -&gt; en</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>{"cookie":"xx","acceptLanguage":"en"} -&gt; en</t>
+          <t>adminLang {"cookie":"fr"} -&gt; de</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>{"acceptLanguage":"en-GB,en;q=0.9,de;q=0.8"} -&gt; en</t>
+          <t>adminLang {"cookie":"xx","acceptLanguage":"en"} -&gt; en</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>{"acceptLanguage":"fr-FR"} -&gt; de</t>
+          <t>adminLang {"acceptLanguage":"en-GB,en;q=0.9,de;q=0.8"} -&gt; en</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>{} -&gt; de</t>
+          <t>adminLang {"acceptLanguage":"fr-FR"} -&gt; de</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>lasts a year for the whole site</t>
+          <t>adminLang {} -&gt; de</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>renders en</t>
+          <t>adminLangCookie lasts a year for the whole site</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>renders de</t>
+          <t>useAt renders en</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>follows the cookie, then Accept-Language, then German</t>
+          <t>useAt renders de</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1312,17 +1312,17 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Staff roles</t>
+          <t>Admin lang</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>admin-roles.int.spec.ts</t>
+          <t>admin-lang.int.spec.ts</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>a Reviewer cannot do Administrator actions, and nothing changes</t>
+          <t>admin layout follows the cookie, then Accept-Language, then German</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>a Reviewer cannot change or delete an existing category or page</t>
+          <t>a Reviewer cannot do Administrator actions, and nothing changes</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>a Reviewer can read users and documents</t>
+          <t>a Reviewer cannot change or delete an existing category or page</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>a customer with no staff role gets 403 on every admin route; no session gets 401</t>
+          <t>a Reviewer can read users and documents</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>the last Administrator cannot be demoted</t>
+          <t>a customer with no staff role gets 403 on every admin route; no session gets 401</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>every route file under app/api/admin exports handlers built with adminRequest</t>
+          <t>the last Administrator cannot be demoted</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1474,17 +1474,17 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Security rule check</t>
+          <t>Staff roles</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>app-endpoints-wrapped.int.spec.ts</t>
+          <t>admin-roles.int.spec.ts</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>the owner-connection check catches a bypass (negative fixture)</t>
+          <t>every route file under app/api/admin exports handlers built with adminRequest</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>every route file under app/app-api exports handlers built with appRequest</t>
+          <t>the owner-connection check catches a bypass (negative fixture)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1528,17 +1528,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>App request wrapper</t>
+          <t>Security rule check</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>app-request.int.spec.ts</t>
+          <t>app-endpoints-wrapped.int.spec.ts</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>first contact creates the users row</t>
+          <t>every route file under app/app-api exports handlers built with appRequest</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>a forged cookie is 401 and touches nothing</t>
+          <t>first contact creates the users row</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>required auth without a cookie is 401</t>
+          <t>a forged cookie is 401 and touches nothing</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>optional auth without a cookie runs with no user</t>
+          <t>required auth without a cookie is 401</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>an unconfirmed email: 403 where auth is required, signed out where optional; never a users row</t>
+          <t>optional auth without a cookie runs with no user</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>a handler error rolls back and returns 500</t>
+          <t>an unconfirmed email: 403 where auth is required, signed out where optional; never a users row</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>a body over maxBodyBytes is 413 before the handler runs</t>
+          <t>a handler error rolls back and returns 500</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>user A cannot read user B through the wrapper</t>
+          <t>a body over maxBodyBytes is 413 before the handler runs</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>app_user cannot write staff columns of its own row</t>
+          <t>user A cannot read user B through the wrapper</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>first contact with a changed email updates the row</t>
+          <t>app_user cannot write staff columns of its own row</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>a second id with the same email gets 409 and no row is written</t>
+          <t>first contact with a changed email updates the row</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>a thrown 400 Response is returned unchanged</t>
+          <t>a second id with the same email gets 409 and no row is written</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1852,17 +1852,17 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Categories</t>
+          <t>App request wrapper</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>categories.int.spec.ts</t>
+          <t>app-request.int.spec.ts</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>ordered by sort, "other services" always last, names in the requested language, anonymous allowed</t>
+          <t>a thrown 400 Response is returned unchanged</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1879,17 +1879,17 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Categories</t>
+          <t>Sign-up and session</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>categories.int.spec.ts</t>
+          <t>auth-cookie-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>an unknown language is 400</t>
+          <t>auth cookie flow signs up by REST, captures the cookie; /app-api/v1/me knows the session but refuses it until the email is confirmed</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1906,17 +1906,17 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Concurrency</t>
+          <t>Categories</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>concurrency.int.spec.ts</t>
+          <t>categories.int.spec.ts</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>12 concurrent searches and 12 concurrent public pages all complete</t>
+          <t>ordered by sort, "other services" always last, names in the requested language, anonymous allowed</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1933,17 +1933,17 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Cron suspensions</t>
+          <t>Categories</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>cron-suspensions.int.spec.ts</t>
+          <t>categories.int.spec.ts</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>401 without the right secret, and when CRON_SECRET is unset</t>
+          <t>an unknown language is 400</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1960,17 +1960,17 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Cron suspensions</t>
+          <t>Concurrency</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>cron-suspensions.int.spec.ts</t>
+          <t>concurrency.int.spec.ts</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>ends a past suspension once: both columns cleared, one email; a future one is left alone</t>
+          <t>12 concurrent searches and 12 concurrent public pages all complete</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Database migrations</t>
+          <t>Cron suspensions</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>db-migrations.int.spec.ts</t>
+          <t>cron-suspensions.int.spec.ts</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>migrates an empty database and classifies every table</t>
+          <t>401 without the right secret, and when CRON_SECRET is unset</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2014,17 +2014,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Database migrations</t>
+          <t>Cron suspensions</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>db-migrations.int.spec.ts</t>
+          <t>cron-suspensions.int.spec.ts</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>0008: person fields on users, suspensions by date, drafts allowed, notifications; applyRls succeeds</t>
+          <t>ends a past suspension once: both columns cleared, one email; a future one is left alone</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>photos: a profile photo has no provider, a portfolio photo has one, one profile photo per person</t>
+          <t>migrates an empty database and classifies every table</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2068,17 +2068,17 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Emails</t>
+          <t>Database migrations</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>email.int.spec.ts</t>
+          <t>db-migrations.int.spec.ts</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>approval: one email in the user language with the document name and the deep link</t>
+          <t>0008: person fields on users, suspensions by date, drafts allowed, notifications; applyRls succeeds</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2095,17 +2095,17 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Emails</t>
+          <t>Database migrations</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>email.int.spec.ts</t>
+          <t>db-migrations.int.spec.ts</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>rejection in German includes the note verbatim, escaped in the HTML</t>
+          <t>photos: a profile photo has no provider, a portfolio photo has one, one profile photo per person</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2122,17 +2122,17 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Emails</t>
+          <t>Database migrations</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>email.int.spec.ts</t>
+          <t>db-migrations.int.spec.ts</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>without a key it only logs and records, and never throws</t>
+          <t>0008 on a database with data: a suspended provider stays hidden, a published one without names or picture goes back to draft</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>outside tests without a key: one log line without recipient or body, and nothing kept in memory</t>
+          <t>approval: one email in the user language with the document name and the deep link</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>with a key it calls Resend with the full message; an { error } and a throw are logged, not thrown</t>
+          <t>rejection in German includes the note verbatim, escaped in the HTML</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>an unexpected stored language falls back to German</t>
+          <t>without a key it only logs and records, and never throws</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -2230,17 +2230,17 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Uploads and document review</t>
+          <t>Emails</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>files-review.int.spec.ts</t>
+          <t>email.int.spec.ts</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>afterCommit: a handler that deletes a photo and then throws rolls back, the object stays</t>
+          <t>outside tests without a key: one log line without recipient or body, and nothing kept in memory</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -2257,17 +2257,17 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Uploads and document review</t>
+          <t>Emails</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>files-review.int.spec.ts</t>
+          <t>email.int.spec.ts</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>afterCommit: the object is deleted only after the commit</t>
+          <t>with a key it calls Resend with the full message; an { error } and a throw are logged, not thrown</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -2284,17 +2284,17 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Uploads and document review</t>
+          <t>Emails</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>files-review.int.spec.ts</t>
+          <t>email.int.spec.ts</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>private_files and documents are isolated (RLS)</t>
+          <t>an unexpected stored language falls back to German</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>at most 10 unsubmitted uploads per user (409)</t>
+          <t>afterCommit: a handler that deletes a photo and then throws rolls back, the object stays</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>a decompression bomb and a header followed by garbage are 400; a later upload is accepted</t>
+          <t>afterCommit: the object is deleted only after the commit</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>EXIF is stripped from the stored JPEG</t>
+          <t>private_files and documents are isolated (RLS)</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>alt over 200 characters is 400</t>
+          <t>at most 10 unsubmitted uploads per user (409)</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>an unauthenticated upload is refused before the body is read</t>
+          <t>a decompression bomb and a header followed by garbage are 400; a later upload is accepted</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>the body is read before the first-contact user row and the transaction exist</t>
+          <t>EXIF is stripped from the stored JPEG</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>photos of a published provider are public, and unreadable once suspended</t>
+          <t>alt over 200 characters is 400</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>replacing the profile photo of a published profile works</t>
+          <t>an unauthenticated upload is refused before the body is read</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>deleting the profile photo while publishing never leaves a published profile without a photo</t>
+          <t>the body is read before the first-contact user row and the transaction exist</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>two simultaneous submits for one requirement give one 201 and one 409</t>
+          <t>photos of a published provider are public, and unreadable once suspended</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>the database refuses a second pending check for a requirement</t>
+          <t>replacing the profile photo of a published profile works</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>approval (staff SQL) makes a service with required documents offerable</t>
+          <t>deleting the profile photo while publishing never leaves a published profile without a photo</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>the signed link carries X-Amz-Expires=300 and the public URL needs AWS_ENDPOINT</t>
+          <t>two simultaneous submits for one requirement give one 201 and one 409</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -2662,17 +2662,17 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Uploads</t>
+          <t>Uploads and document review</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>files.int.spec.ts</t>
+          <t>files-review.int.spec.ts</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>a profile photo is re-encoded to JPEG at most 1600 px and returned in contract shape</t>
+          <t>the database refuses a second pending check for a requirement</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -2689,17 +2689,17 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Uploads</t>
+          <t>Uploads and document review</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>files.int.spec.ts</t>
+          <t>files-review.int.spec.ts</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>a new profile photo replaces the old one and deletes its object</t>
+          <t>approval (staff SQL) makes a service with required documents offerable</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -2716,17 +2716,17 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Uploads</t>
+          <t>Uploads and document review</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>files.int.spec.ts</t>
+          <t>files-review.int.spec.ts</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>portfolio is limited to 12 (409), a non-image is 400, a missing kind is 400</t>
+          <t>the signed link carries X-Amz-Expires=300 and the public URL needs AWS_ENDPOINT</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>a portfolio photo needs a profile first (409); anonymous is 401; an oversize body is 413</t>
+          <t>a profile photo is re-encoded to JPEG at most 1600 px and returned in contract shape</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>deleting a photo: another user gets 404, the owner 204 and the object and row are gone</t>
+          <t>a new profile photo replaces the old one and deletes its object</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>the profile photo of a published profile cannot be deleted (409)</t>
+          <t>portfolio is limited to 12 (409), a non-image is 400, a missing kind is 400</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>suspended_until is domain-only and photos are isolated</t>
+          <t>a portfolio photo needs a profile first (409); anonymous is 401; an oversize body is 413</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>files: a PDF goes to the private bucket, a non-PDF is 400, another user gets 404, the owner a signed link</t>
+          <t>deleting a photo: another user gets 404, the owner 204 and the object and row are gone</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>documents also take JPEG, PNG and WEBP photos: re-encoded without metadata, at most 2400 px, stored with their type</t>
+          <t>the profile photo of a published profile cannot be deleted (409)</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>a GIF and a text file renamed to .pdf are refused as documents</t>
+          <t>suspended_until is domain-only and photos are isolated</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>staff open an image document through the same signed link; it is served as an image</t>
+          <t>files: a PDF goes to the private bucket, a non-PDF is 400, another user gets 404, the owner a signed link</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>a failed file insert removes the uploaded object</t>
+          <t>documents also take JPEG, PNG and WEBP photos: re-encoded without metadata, at most 2400 px, stored with their type</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>verifications: one pending check per requirement (409 removes the second file), bad input is 400</t>
+          <t>a GIF and a text file renamed to .pdf are refused as documents</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>the profile photo is private to its owner: another user cannot see it and gets 404 on delete; listPhotos puts it first</t>
+          <t>staff open an image document through the same signed link; it is served as an image</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -3040,17 +3040,17 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Website home page</t>
+          <t>Uploads</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>home-page.int.spec.ts</t>
+          <t>files.int.spec.ts</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>is German by default: headline, categories, store badges without links, no forbidden words</t>
+          <t>a failed file insert removes the uploaded object</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -3067,17 +3067,17 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Website home page</t>
+          <t>Uploads</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>home-page.int.spec.ts</t>
+          <t>files.int.spec.ts</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>switches to English with ?lang=en and falls back to German for unknown values</t>
+          <t>verifications: one pending check per requirement (409 removes the second file), bad input is 400</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -3094,17 +3094,17 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>Website home page</t>
+          <t>Uploads</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>home-page.int.spec.ts</t>
+          <t>files.int.spec.ts</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>has per-language metadata with canonical and hreflang for every language</t>
+          <t>the profile photo is private to its owner: another user cannot see it and gets 404 on delete; listPhotos puts it first</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>metadataBase makes canonical and hreflang absolute on the site url</t>
+          <t>home page is German by default: headline, categories, store badges without links, no forbidden words</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>html lang follows the request language; unknown falls back to de</t>
+          <t>home page switches to English with ?lang=en and falls back to German for unknown values</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>footer links the four legal pages with catalogue labels in both languages</t>
+          <t>home page has per-language metadata with canonical and hreflang for every language</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -3202,17 +3202,17 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Website home page</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>notifications.int.spec.ts</t>
+          <t>home-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>live and nothing else pending: "profile is live" email with the link, and one notification</t>
+          <t>site layout metadataBase makes canonical and hreflang absolute on the site url</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -3229,17 +3229,17 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Website home page</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>notifications.int.spec.ts</t>
+          <t>home-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>the link of a German provider has no lang parameter</t>
+          <t>site layout html lang follows the request language; unknown falls back to de</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -3256,17 +3256,17 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Website home page</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>notifications.int.spec.ts</t>
+          <t>home-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>live but another document is still missing: says the category service is visible, no notification</t>
+          <t>site layout footer links the four legal pages with catalogue labels in both languages</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>the approved requirement is not enough for any service: plain approval, no notification</t>
+          <t>live and nothing else pending: "profile is live" email with the link, and one notification</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>draft profile: offline text, no notification</t>
+          <t>the link of a German provider has no lang parameter</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>suspended profile: suspended text with the date, no notification</t>
+          <t>live but another document is still missing: says the category service is visible, no notification</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>a requirement that was already approved: plain approval, no notification</t>
+          <t>the approved requirement is not enough for any service: plain approval, no notification</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>rejection is unchanged</t>
+          <t>draft profile: offline text, no notification</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>GET /me lists the notification; PATCH dismissed hides it; another user gets 404</t>
+          <t>suspended profile: suspended text with the date, no notification</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -3445,17 +3445,17 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Database connection</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>owner-connection.int.spec.ts</t>
+          <t>notifications.int.spec.ts</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>inside a request transaction the owner connection `db` is a different connection (not app_user)</t>
+          <t>a requirement that was already approved: plain approval, no notification</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -3472,17 +3472,17 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>Database connection</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>owner-connection.int.spec.ts</t>
+          <t>notifications.int.spec.ts</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>two interleaved requests keep their own user id and role</t>
+          <t>rejection is unchanged</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -3499,17 +3499,17 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Legal and info pages</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>pages.int.spec.ts</t>
+          <t>notifications.int.spec.ts</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>every table is classified (pages and page_texts are public reference tables)</t>
+          <t>GET /me lists the notification; PATCH dismissed hides it; another user gets 404</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -3526,17 +3526,17 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>Legal and info pages</t>
+          <t>Database connection</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>pages.int.spec.ts</t>
+          <t>owner-connection.int.spec.ts</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>anonymous app requests read pages but cannot write them</t>
+          <t>inside a request transaction the owner connection `db` is a different connection (not app_user)</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -3553,17 +3553,17 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>Legal and info pages</t>
+          <t>Database connection</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>pages.int.spec.ts</t>
+          <t>owner-connection.int.spec.ts</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>returns the text in the language, falls back to de, hides drafts and unknown slugs</t>
+          <t>two interleaved requests keep their own user id and role</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>publishedPages lists published pages only</t>
+          <t>pages tables every table is classified (pages and page_texts are public reference tables)</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>renders the Markdown body in both languages with the de fallback</t>
+          <t>pages tables anonymous app requests read pages but cannot write them</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>404 for unknown and unpublished slugs</t>
+          <t>getPage returns the text in the language, falls back to de, hides drafts and unknown slugs</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>metadata: title, canonical and hreflang for every language</t>
+          <t>getPage publishedPages lists published pages only</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>escapes HTML in a body and drops unsafe links</t>
+          <t>legal page by slug renders the Markdown body in both languages with the de fallback</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>escapes raw html and keeps Markdown</t>
+          <t>legal page by slug 404 for unknown and unpublished slugs</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>external links get rel="nofollow ugc"; protocol-relative and backslash paths are dropped</t>
+          <t>legal page by slug metadata: title, canonical and hreflang for every language</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -3769,17 +3769,17 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>Postcodes</t>
+          <t>Legal and info pages</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>postcodes.int.spec.ts</t>
+          <t>pages.int.spec.ts</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>imports the German file and looks up 01053 Dresden</t>
+          <t>legal page by slug escapes HTML in a body and drops unsafe links</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -3796,17 +3796,17 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>Postcodes</t>
+          <t>Legal and info pages</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>postcodes.int.spec.ts</t>
+          <t>pages.int.spec.ts</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>rejects a four-digit German code and an unknown one</t>
+          <t>renderMarkdown escapes raw html and keeps Markdown</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -3823,17 +3823,17 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>Postcodes</t>
+          <t>Legal and info pages</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>postcodes.int.spec.ts</t>
+          <t>pages.int.spec.ts</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Berlin to Munich is about 504 km</t>
+          <t>renderMarkdown external links get rel="nofollow ugc"; protocol-relative and backslash paths are dropped</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -3850,17 +3850,17 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>Website provider page</t>
+          <t>Postcodes</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>provider-page.int.spec.ts</t>
+          <t>postcodes.int.spec.ts</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>German default: public name heading, category, price "ab 80,00 â‚¬", on request, place</t>
+          <t>imports the German file and looks up 01053 Dresden</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -3877,17 +3877,17 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>Website provider page</t>
+          <t>Postcodes</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>provider-page.int.spec.ts</t>
+          <t>postcodes.int.spec.ts</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>English with ?lang=en: "from â‚¬80.00"</t>
+          <t>rejects a four-digit German code and an unknown one</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -3904,17 +3904,17 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>Website provider page</t>
+          <t>Postcodes</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>provider-page.int.spec.ts</t>
+          <t>postcodes.int.spec.ts</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>escapes user content</t>
+          <t>Berlin to Munich is about 504 km</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>404 for a hidden provider (draft) and an unknown slug</t>
+          <t>public provider page German default: public name heading, category, price "ab 80,00 â‚¬", on request, place</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>metadata: title, description, canonical and hreflang for every language</t>
+          <t>public provider page English with ?lang=en: "from â‚¬80.00"</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>is shown only when the texts are not in the page language</t>
+          <t>public provider page escapes user content</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>?translate=1 shows the translation with the AI label, noindex, canonical unchanged</t>
+          <t>public provider page 404 for a hidden provider (draft) and an unknown slug</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>?translate=1 without a key shows the original texts and the unavailable copy</t>
+          <t>public provider page metadata: title, description, canonical and hreflang for every language</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>translate=1 on texts already in the viewer language: original, no label, no model call</t>
+          <t>translate link is shown only when the texts are not in the page language</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -4093,17 +4093,17 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>Provider profile</t>
+          <t>Website provider page</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>provider-profile.int.spec.ts</t>
+          <t>provider-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>GET is null when there is no profile</t>
+          <t>translate link ?translate=1 shows the translation with the AI label, noindex, canonical unchanged</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -4120,17 +4120,17 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>Provider profile</t>
+          <t>Website provider page</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>provider-profile.int.spec.ts</t>
+          <t>provider-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>PUT creates (201) and a later PUT edits (200); responses fit the contract</t>
+          <t>translate link ?translate=1 without a key shows the original texts and the unavailable copy</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -4147,17 +4147,17 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>Provider profile</t>
+          <t>Website provider page</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>provider-profile.int.spec.ts</t>
+          <t>provider-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>an unknown postcode is 400 and changes nothing</t>
+          <t>translate link translate=1 on texts already in the viewer language: original, no label, no model call</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>a partial first save never fails on business rules</t>
+          <t>GET is null when there is no profile</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>status, slug and suspended in the body are ignored</t>
+          <t>PUT creates (201) and a later PUT edits (200); responses fit the contract</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>one user's profile is not visible to another</t>
+          <t>an unknown postcode is 400 and changes nothing</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>an invalid body is 400 with the contract error</t>
+          <t>a partial first save never fails on business rules</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>an unconfirmed email gets 403 EMAIL_NOT_VERIFIED from PUT provider-profile and GET /me, and no users row</t>
+          <t>status, slug and suspended in the body are ignored</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>PATCH /me checks its body with the contract: 400 Invalid input names the field; a valid patch saves</t>
+          <t>one user's profile is not visible to another</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>updateMe stores country DE when the address carries none (the HTTP contract always sends one)</t>
+          <t>an invalid body is 400 with the contract error</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>PATCH /me stores names and a private address (country stored as sent); GET /me returns them; null clears the address</t>
+          <t>an unconfirmed email gets 403 EMAIL_NOT_VERIFIED from PUT provider-profile and GET /me, and no users row</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>POST creates a draft with the postcode prefilled; again returns the same id; GET /me is fine</t>
+          <t>PATCH /me checks its body with the contract: 400 Invalid input names the field; a valid patch saves</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>missing: the empty draft lists the person-independent items, business adds two, saves shrink it, PUT carries it</t>
+          <t>a user without an address still gets a draft (the provider row default country applies)</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>publish of an incomplete draft is 409 with the list; complete publishes with public name Lena F.</t>
+          <t>POST creates a draft with the postcode prefilled; again returns the same id; GET /me is fine</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>a draft with every nullable field null is invisible in search and the sitemap</t>
+          <t>missing: the empty draft lists the person-independent items, business adds two, saves shrink it, PUT carries it</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>a draft created during a suspension cannot be published</t>
+          <t>publish of an incomplete draft is 409 with the list; complete publishes with public name Lena F.</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>the draft prefills the postcode only when it is a known one</t>
+          <t>a draft with every nullable field null is invisible in search and the sitemap</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>a live profile cannot be emptied by a save: 409 with the missing list, nothing changed</t>
+          <t>a draft created during a suspension cannot be published</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>a provider whose names are missing cannot publish: missing lists name</t>
+          <t>the draft prefills the postcode only when it is a known one</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>the draft's postcode lookup uses the owner's stored country</t>
+          <t>a live profile cannot be emptied by a save: 409 with the missing list, nothing changed</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -4633,17 +4633,17 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>Public provider data</t>
+          <t>Provider profile</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>provider-public.int.spec.ts</t>
+          <t>provider-profile.int.spec.ts</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>a published provider page: contract shape, place, photo urls, only offerable services</t>
+          <t>a provider whose names are missing cannot publish: missing lists name</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -4660,17 +4660,17 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>Public provider data</t>
+          <t>Provider profile</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>provider-public.int.spec.ts</t>
+          <t>provider-profile.int.spec.ts</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>404 when not visible: unknown, draft, or no offerable service</t>
+          <t>the draft's postcode lookup uses the owner's stored country</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>a draft page is a 404 for its own owner too</t>
+          <t>a published provider page: contract shape, place, photo urls, only offerable services</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>unknown language is 400</t>
+          <t>404 when not visible: unknown, draft, or no offerable service</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>anonymous: the page carries the owner's profile photo and the public name, no display name</t>
+          <t>a draft page is a 404 for its own owner too</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -4768,17 +4768,17 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>Translate endpoint</t>
+          <t>Public provider data</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>provider-translation.int.spec.ts</t>
+          <t>provider-public.int.spec.ts</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>returns translated texts in the page shape</t>
+          <t>unknown language is 400</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
@@ -4795,17 +4795,17 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>Translate endpoint</t>
+          <t>Public provider data</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>provider-translation.int.spec.ts</t>
+          <t>provider-public.int.spec.ts</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>a draft or suspended provider -&gt; 404, no call</t>
+          <t>anonymous: the page carries the owner's profile photo and the public name, no display name</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>unknown lang -&gt; 400</t>
+          <t>returns translated texts in the page shape</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>service failure -&gt; 503 and nothing stored</t>
+          <t>a draft or suspended provider -&gt; 404, no call</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>a logged-in caller is counted under the user id</t>
+          <t>unknown lang -&gt; 400</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>the provider endpoint reports translatable per viewer language</t>
+          <t>service failure -&gt; 503 and nothing stored</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>accepts no text from the client</t>
+          <t>a logged-in caller is counted under the user id</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>fails closed without a usable secret: 503, no counter row, no model call</t>
+          <t>the provider endpoint reports translatable per viewer language</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -4984,17 +4984,17 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>Site and admin routing</t>
+          <t>Translate endpoint</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>proxy.int.spec.ts</t>
+          <t>provider-translation.int.spec.ts</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>/admin and below go through the auth middleware</t>
+          <t>accepts no text from the client</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
@@ -5011,17 +5011,17 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>Site and admin routing</t>
+          <t>Translate endpoint</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>proxy.int.spec.ts</t>
+          <t>provider-translation.int.spec.ts</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>/administrator or a page slug starting with admin is a site path with x-lang</t>
+          <t>fails closed without a usable secret: 503, no counter row, no model call</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -5038,17 +5038,17 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>Public name</t>
+          <t>Site and admin routing</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>public-name.int.spec.ts</t>
+          <t>proxy.int.spec.ts</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>publicNameFor: business name, else first name and surname initial</t>
+          <t>/admin and below go through the auth middleware</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
@@ -5065,17 +5065,17 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>Public name</t>
+          <t>Site and admin routing</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>public-name.int.spec.ts</t>
+          <t>proxy.int.spec.ts</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>slugify transliterates umlauts and strips the rest</t>
+          <t>/administrator or a page slug starting with admin is a site path with x-lang</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>public name and slug are unique and stable</t>
+          <t>publicNameFor: business name, else first name and surname initial</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>an individual without names cannot publish; with names the public name follows</t>
+          <t>slugify transliterates umlauts and strips the rest</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>first contact does not copy the session name: the person sets their own names</t>
+          <t>public name and slug are unique and stable</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>a rename of the person changes the public name of their provider profile</t>
+          <t>an individual without names cannot publish; with names the public name follows</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -5200,17 +5200,17 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>Publish and unpublish</t>
+          <t>Public name</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>publish-flow.int.spec.ts</t>
+          <t>public-name.int.spec.ts</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>the first-time flow: refused until photo and service exist, then published, then unpublished</t>
+          <t>first contact does not copy the session name: the person sets their own names</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -5227,17 +5227,17 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>Publish and unpublish</t>
+          <t>Public name</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>publish-flow.int.spec.ts</t>
+          <t>public-name.int.spec.ts</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>a postcode-less profile is refused until a postcode is saved</t>
+          <t>a rename of the person changes the public name of their provider profile</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>a suspended profile cannot publish (409)</t>
+          <t>the first-time flow: refused until photo and service exist, then published, then unpublished</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>RLS: published and not suspended is public, drafts and suspended are not</t>
+          <t>a postcode-less profile is refused until a postcode is saved</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>RLS: another user cannot change or add to a provider; domain-only columns are closed</t>
+          <t>a suspended profile cannot publish (409)</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>RLS: set_provider_* touch only the caller's own profile</t>
+          <t>RLS: published and not suspended is public, drafts and suspended are not</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>RLS: documents are private and the verdict is staff-only</t>
+          <t>RLS: another user cannot change or add to a provider; domain-only columns are closed</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>offerableServiceIds: services whose required documents are all approved</t>
+          <t>RLS: set_provider_* touch only the caller's own profile</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>a user suspension that has ended no longer blocks publishing; a running one does</t>
+          <t>RLS: documents are private and the verdict is staff-only</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -5443,17 +5443,17 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>Staff check</t>
+          <t>Publish and unpublish</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>require-staff.int.spec.ts</t>
+          <t>publish-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>an active admin passes</t>
+          <t>offerableServiceIds: services whose required documents are all approved</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -5470,17 +5470,17 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>Staff check</t>
+          <t>Publish and unpublish</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>require-staff.int.spec.ts</t>
+          <t>publish-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>a suspended admin gets 403</t>
+          <t>a user suspension that has ended no longer blocks publishing; a running one does</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>an expired suspension no longer blocks</t>
+          <t>an active admin passes</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -5524,17 +5524,17 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>Row-level security</t>
+          <t>Staff check</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>rls-providers.int.spec.ts</t>
+          <t>require-staff.int.spec.ts</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>another user cannot update or delete a service or a reference (rowCount 0, rows unchanged)</t>
+          <t>a suspended admin gets 403</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
@@ -5551,17 +5551,17 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>Row-level security</t>
+          <t>Staff check</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>rls-providers.int.spec.ts</t>
+          <t>require-staff.int.spec.ts</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>another user cannot insert a service or a reference for my provider</t>
+          <t>an expired suspension no longer blocks</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>the owner cannot move a service to another provider</t>
+          <t>another user cannot update or delete a service or a reference (rowCount 0, rows unchanged)</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>offerableServiceIds and missingRequirements are identical through tx and the owner db</t>
+          <t>another user cannot insert a service or a reference for my provider</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>a stranger asking about a draft provider gets empty answers; the owner still gets the full ones</t>
+          <t>the owner cannot move a service to another provider</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>a service with a category alone (no price type yet) is never offerable, not even to its owner</t>
+          <t>offerableServiceIds and missingRequirements are identical through tx and the owner db</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>slugify strips accents</t>
+          <t>a stranger asking about a draft provider gets empty answers; the owner still gets the full ones</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
@@ -5718,12 +5718,12 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>rls.int.spec.ts</t>
+          <t>rls-providers.int.spec.ts</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>app_user cannot read a private table row of another user</t>
+          <t>a service with a category alone (no price type yet) is never offerable, not even to its owner</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>rls.int.spec.ts</t>
+          <t>rls-providers.int.spec.ts</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>public reference tables are readable by app_user and not writable</t>
+          <t>slugify strips accents</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>a person's picture is private until the owner's provider is published and not suspended</t>
+          <t>app_user cannot read a private table row of another user</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>notifications: the owner reads and marks own rows; another user sees none, cannot insert or change kind</t>
+          <t>public reference tables are readable by app_user and not writable</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
@@ -5821,17 +5821,17 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Row-level security</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>search.int.spec.ts</t>
+          <t>rls.int.spec.ts</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>radius edge and remote providers</t>
+          <t>a person's picture is private until the owner's provider is published and not suspended</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
@@ -5848,17 +5848,17 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Row-level security</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>search.int.spec.ts</t>
+          <t>rls.int.spec.ts</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>a remote provider more than 200 km away is found, without a distance</t>
+          <t>notifications: the owner reads and marks own rows; another user sees none, cannot insert or change kind</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>a draft is invisible to its owner too</t>
+          <t>radius edge and remote providers</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>distance is whole km, at least 1, hidden for remote providers outside the radius</t>
+          <t>a remote provider more than 200 km away is found, without a distance</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>a draft, a suspended or a provider without an offerable service never appears</t>
+          <t>a draft is invisible to its owner too</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>category filter and q (public name and skills, case-insensitive)</t>
+          <t>distance is whole km, at least 1, hidden for remote providers outside the radius</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>bad input is 400: unknown postcode, bad format, unknown country, unknown language, bad page</t>
+          <t>a draft, a suspended or a provider without an offerable service never appears</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>paging: 20 per page and hasMore</t>
+          <t>category filter and q (public name and skills, case-insensitive)</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>anonymous: the card carries the owner's profile photo and the public name, no display name</t>
+          <t>bad input is 400: unknown postcode, bad format, unknown country, unknown language, bad page</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>a provider whose only service has no price type is neither found nor has a public page</t>
+          <t>paging: 20 per page and hasMore</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>a fixed service without a price is not found in its category</t>
+          <t>anonymous: the card carries the owner's profile photo and the public name, no display name</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -6118,17 +6118,17 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>search.int.spec.ts</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>categories seed is idempotent: 14 categories, both names, babysitting needs a police certificate</t>
+          <t>a provider whose only service has no price type is neither found nor has a public page</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
@@ -6145,17 +6145,17 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>search.int.spec.ts</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>postcode import upserts: a second run leaves the same count</t>
+          <t>a fixed service without a price is not found in its category</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>the dev guard needs the dev branch AND the dev database host</t>
+          <t>categories seed is idempotent: 14 categories, both names, babysitting needs a police certificate</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>loadSeedData reads the git-ignored list or the committed example, and rejects a broken file</t>
+          <t>postcode import upserts: a second run leaves the same count</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>seedTestUsers itself refuses outside dev, before touching anything</t>
+          <t>the dev guard needs the dev branch AND the dev database host</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>builds the test users through the domain: published providers with photo, services, public names, verified; a rerun adds nothing</t>
+          <t>loadSeedData reads the git-ignored list or the committed example, and rejects a broken file</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>a run that crashed after the services (no photo, not published) resumes without adding the services twice</t>
+          <t>seedTestUsers itself refuses outside dev, before touching anything</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>placeholder photos: gives a published profile without a photo one; elsewhere needs the typed yes</t>
+          <t>builds the test users through the domain: published providers with photo, services, public names, verified; a rerun adds nothing</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>neonAuth retries a 429, then succeeds</t>
+          <t>a run that crashed after the services (no photo, not published) resumes without adding the services twice</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>neonAuth signs in when the email already exists</t>
+          <t>placeholder photos: gives a published profile without a photo one; elsewhere needs the typed yes</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>neonAuth surfaces any other sign-up failure without falling back to sign-in</t>
+          <t>neonAuth retries a 429, then succeeds</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
@@ -6415,17 +6415,17 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>Services and references</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>services-references.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>a service needs a profile first (409)</t>
+          <t>neonAuth signs in when the email already exists</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -6442,17 +6442,17 @@
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>Services and references</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>services-references.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>create, list and patch a service; shapes fit the contract</t>
+          <t>neonAuth surfaces any other sign-up failure without falling back to sign-in</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>on-request has no price, even when one is sent</t>
+          <t>a service needs a profile first (409)</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>bad service input: no price, three decimals, unknown category are 400</t>
+          <t>create, list and patch a service; shapes fit the contract</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>a service in a category with required documents waits for approval</t>
+          <t>on-request has no price, even when one is sent</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>user A cannot edit or delete user B's service</t>
+          <t>bad service input: no price, three decimals, unknown category are 400</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>references are capped at 2 (409), can be patched and deleted</t>
+          <t>a service in a category with required documents waits for approval</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>a service with a category alone is saved, not offerable, and a patch accepts the partial shape</t>
+          <t>user A cannot edit or delete user B's service</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>the price type and the price save in either order, each as its own one-field save</t>
+          <t>references are capped at 2 (409), can be patched and deleted</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>a fixed service without a price is not offerable, with a price it is; on-request clears the price</t>
+          <t>a service with a category alone is saved, not offerable, and a patch accepts the partial shape</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
@@ -6685,17 +6685,17 @@
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>Sitemaps</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>sitemaps.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>providers sitemap lists only visible providers</t>
+          <t>the price type and the price save in either order, each as its own one-field save</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
@@ -6712,17 +6712,17 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>Sitemaps</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>sitemaps.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>pages sitemap lists the home page and published pages only</t>
+          <t>a fixed service without a price is not offerable, with a price it is; on-request clears the price</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
@@ -6739,17 +6739,17 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>Sitemaps</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>sitemaps.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>robots.txt allows the site, keeps the admin out and points at both sitemaps</t>
+          <t>the app sends a category alone, then one field per save: currency defaults to EUR, title to the category name</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
@@ -6766,17 +6766,17 @@
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>Smoke test</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>smoke.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>connects to the test database and sees PostGIS</t>
+          <t>add and update answer with waitingFor and visibleInSearch, like the list</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
@@ -6793,17 +6793,17 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>Test database guard</t>
+          <t>Sitemaps</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>test-guard.int.spec.ts</t>
+          <t>sitemaps.int.spec.ts</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>the test guard refuses a non-local or non-test URL</t>
+          <t>providers sitemap lists only visible providers</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
@@ -6820,17 +6820,17 @@
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Sitemaps</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>sitemaps.int.spec.ts</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>stores translations and serves the second request from the store without a call</t>
+          <t>pages sitemap lists the home page and published pages only</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
@@ -6847,17 +6847,17 @@
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Sitemaps</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>sitemaps.int.spec.ts</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>an edited text is re-translated, the rest comes from the store</t>
+          <t>robots.txt allows the site, keeps the admin out and points at both sitemaps</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
@@ -6874,17 +6874,17 @@
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Smoke test</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>smoke.int.spec.ts</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>texts already in the target language are returned unchanged without a call</t>
+          <t>connects to the test database and sees PostGIS</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
@@ -6901,17 +6901,17 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Test database guard</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>test-guard.int.spec.ts</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>a malformed or incomplete model answer stores nothing and throws TranslationUnavailable</t>
+          <t>the test guard refuses a non-local or non-test URL</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>a non-2xx answer throws TranslationUnavailable</t>
+          <t>translate stores translations and serves the second request from the store without a call</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>line breaks survive</t>
+          <t>translate an edited text is re-translated, the rest comes from the store</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>no key -&gt; TranslationUnavailable without a call</t>
+          <t>translate texts already in the target language are returned unchanged without a call</t>
         </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>the 31st AI call within an hour for one client key -&gt; TranslationUnavailable</t>
+          <t>translate a malformed or incomplete model answer stores nothing and throws TranslationUnavailable</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>the limit boundary: the 30th call passes, the 31st is refused</t>
+          <t>translate a non-2xx answer throws TranslationUnavailable</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>a timeout -&gt; TranslationUnavailable</t>
+          <t>translate line breaks survive</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>concurrent translations of the same page store one row per text</t>
+          <t>translate no key -&gt; TranslationUnavailable without a call</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>writes through the request transaction and commits with it</t>
+          <t>translate the 31st AI call within an hour for one client key -&gt; TranslationUnavailable</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>the default timeout is 12 seconds</t>
+          <t>translate the limit boundary: the 30th call passes, the 31st is refused</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>French and Afrikaans texts are flagged and sent to the model, in either viewer language</t>
+          <t>translate a timeout -&gt; TranslationUnavailable</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>a page the detector cannot classify is translated when long enough, left alone when short</t>
+          <t>translate concurrent translations of the same page store one row per text</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>a German profile of short skills and titles needs no translation for de but does for en</t>
+          <t>translate writes through the request transaction and commits with it</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>a Markdown-fenced answer parses; the request carries max_tokens</t>
+          <t>translate the default timeout is 12 seconds</t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>an empty string from the model stores nothing</t>
+          <t>translate French and Afrikaans texts are flagged and sent to the model, in either viewer language</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>counter rows older than 24 hours are deleted; recent ones stay</t>
+          <t>translate a page the detector cannot classify is translated when long enough, left alone when short</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>anonymous client keys are salted hashes, never the raw IP</t>
+          <t>translate a German profile of short skills and titles needs no translation for de but does for en</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>textsOf picks the translatable fields of a profile</t>
+          <t>translate a Markdown-fenced answer parses; the request carries max_tokens</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>needsTranslation is false for a page entirely in the viewer language and true for a mixed page</t>
+          <t>translate an empty string from the model stores nothing</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>anonymous callers can insert and read, never update or delete</t>
+          <t>translate counter rows older than 24 hours are deleted; recent ones stay</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
@@ -7441,17 +7441,17 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>Sign-up and session</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>auth-cookie-flow.int.spec.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>signs up by REST, captures the cookie; /app-api/v1/me knows the session but refuses it until the email is confirmed</t>
+          <t>translate anonymous client keys are salted hashes, never the raw IP</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
@@ -7468,22 +7468,22 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>Address fields</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>address-fields.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>toAddress: empty is null (clears), complete is DE, partial is undefined</t>
+          <t>translate textsOf picks the translatable fields of a profile</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E256" s="4" t="inlineStr">
@@ -7495,22 +7495,22 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>server errors land on the right field</t>
+          <t>translate needsTranslation is false for a page entirely in the viewer language and true for a mixed page</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E257" s="4" t="inlineStr">
@@ -7522,22 +7522,22 @@
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>withItem adds a trimmed new skill or strength once and ignores blanks</t>
+          <t>translation tables are insert-only for app_user anonymous callers can insert and read, never update or delete</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E258" s="4" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>the form-level error shows unless every server error has an inline slot</t>
+          <t>server errors land on the right field</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>service and reference validation</t>
+          <t>withItem adds a trimmed new skill or strength once and ignores blanks</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>every missing item the publish route can return has de and en text</t>
+          <t>the form-level error shows unless every server error has an inline slot</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>the service body names the category by id and the currency, as the server expects</t>
+          <t>service and reference validation</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>a 400 "Invalid input" marks each named field</t>
+          <t>every missing item the publish route can return has de and en text</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>live means published and not suspended now (the server rule of listServices)</t>
+          <t>the service body names the category by id and the currency, as the server expects</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
@@ -7711,17 +7711,17 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>Share profile</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>share-profile.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>the provider page url carries the language only when it is not the default</t>
+          <t>a 400 "Invalid input" marks each named field</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
@@ -7738,17 +7738,17 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>Share profile</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>share-profile.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>shareProfile passes the url and the text in the given language</t>
+          <t>live means published and not suspended now (the server rule of listServices)</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
@@ -7765,17 +7765,17 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Share profile</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>share-profile.test.ts</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>signUp posts email, password and name and stores the session cookie</t>
+          <t>the provider page url carries the language only when it is not the default</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
@@ -7792,17 +7792,17 @@
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Share profile</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>share-profile.test.ts</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>signIn posts email and password and returns the user</t>
+          <t>shareProfile passes the url and the text in the given language</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
@@ -7819,17 +7819,17 @@
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Address fields</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>address-fields.test.ts</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>a refused sign-in throws the server code, which maps to a catalogue message</t>
+          <t>toAddress: empty is null (clears), complete is DE, partial is undefined</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>signOut forgets the session at once and tells the server with the old cookie</t>
+          <t>texts come from the shared catalogue, in the chosen language, with placeholders filled</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>signOut offline still signs out</t>
+          <t>the translate button texts exist in both languages</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>session reads get-session with the cookie; no cookie means null without a request</t>
+          <t>errorText maps the auth server codes to catalogue messages</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>session throws on a network error (the app offers a retry, not the login)</t>
+          <t>errorText maps the app API strings</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>sendVerificationCode asks for an email-verification code</t>
+          <t>docText maps known document codes and passes unknown ones through</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>verifyEmail sends the code as otp, stores the new session and returns the user</t>
+          <t>prices follow the website rules in German and English</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>requestPasswordReset asks for a reset code</t>
+          <t>distance shows km, remote or nothing</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>resetPassword sends email, code and the new password</t>
+          <t>search path leaves out empty filters and trims text</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>a wrong code throws INVALID_OTP, shown as the code message</t>
+          <t>photoSrc loads only absolute http(s) URLs, never a server-relative /api path</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>updateUserName changes the name on the auth account</t>
+          <t>signUp posts email, password and name and stores the session cookie</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>signUp and signIn start without an old stored session</t>
+          <t>signIn posts email and password and returns the user</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>prices follow the website rules in German and English</t>
+          <t>a refused sign-in throws the server code, which maps to a catalogue message</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>distance shows km, remote or nothing</t>
+          <t>signOut forgets the session at once and tells the server with the old cookie</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
@@ -8202,12 +8202,12 @@
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>search path leaves out empty filters and trims text</t>
+          <t>signOut offline still signs out</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
@@ -8229,12 +8229,12 @@
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>photoSrc loads only absolute http(s) URLs, never a server-relative /api path</t>
+          <t>session reads get-session with the cookie; no cookie means null without a request</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>a failed check after the upload deletes the uploaded file and reports the original error</t>
+          <t>session throws on a network error (the app offers a retry, not the login)</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>a successful submit deletes nothing</t>
+          <t>sendVerificationCode asks for an email-verification code</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>a failing clean-up does not hide the original error</t>
+          <t>verifyEmail sends the code as otp, stores the new session and returns the user</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>texts come from the shared catalogue, in the chosen language, with placeholders filled</t>
+          <t>requestPasswordReset asks for a reset code</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
@@ -8364,12 +8364,12 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>the translate button texts exist in both languages</t>
+          <t>resetPassword sends email, code and the new password</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>errorText maps the auth server codes to catalogue messages</t>
+          <t>a wrong code throws INVALID_OTP, shown as the code message</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>errorText maps the app API strings</t>
+          <t>signUp and signIn start without an old stored session</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>docText maps known document codes and passes unknown ones through</t>
+          <t>a failed check after the upload deletes the uploaded file and reports the original error</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
@@ -8472,12 +8472,12 @@
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>preparePhoto keeps the long side at 1600 px</t>
+          <t>a successful submit deletes nothing</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
@@ -8499,12 +8499,12 @@
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>tooLarge is true above 4_434_464 bytes</t>
+          <t>a failing clean-up does not hide the original error</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>cancelled is null</t>
+          <t>preparePhoto keeps the long side at 1600 px</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>a refused permission is denied, not cancelled</t>
+          <t>tooLarge is true above 4_434_464 bytes</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>offers PDFs and the image types the server accepts, from any file source</t>
+          <t>pickPhoto cancelled is null</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>cancelled is null</t>
+          <t>pickPhoto a refused permission is denied, not cancelled</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
@@ -8634,12 +8634,12 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>loading -&gt; signed in -&gt; signed out</t>
+          <t>pickDocument offers PDFs and the image types the server accepts, from any file source</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>an unverified email never counts as signed in: sign-in sends a code and asks for it</t>
+          <t>pickDocument cancelled is null</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
@@ -8683,17 +8683,17 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Pending signup</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>pending-signup.test.ts</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>a server that refuses unverified sign-ins (EMAIL_NOT_VERIFIED) also leads to the code screen</t>
+          <t>the pending record round-trips and clears</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -8715,12 +8715,12 @@
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>sign-up creates the account and sends the code; the right code signs in and saves the account name</t>
+          <t>applyTexts swaps only the translatable fields and keeps names, prices and photos</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>a wrong code throws and keeps signed out</t>
+          <t>applyTexts matches services and references by id and leaves unknown ones untouched</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>a failed login rejects and keeps signed out; a server error on load means signed out</t>
+          <t>applyTexts keeps line breaks</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
@@ -8796,12 +8796,12 @@
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>a network error on load sets offline (not signed out); retry recovers</t>
+          <t>sends the stored cookie and stores a new set-cookie</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>onUnauthorized from the API client signs the user out</t>
+          <t>a single joined set-cookie header (no getSetCookie) is split into its cookies</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>updateName saves the account name in both places and updates the session user; a failure keeps the old one</t>
+          <t>clears the session on 401</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>switching the language also saves it for emails, but only while signed in</t>
+          <t>a 401 without a stored session does not call onUnauthorized</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>verify finishes the sign-up: names and address, then the picture, then the record is cleared; returns the tick</t>
+          <t>every request names the app origin and leaves the platform cookie store out</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>a failed upload keeps the record; loadSession retries it once and clears it</t>
+          <t>a 409 with error and missing throws ApiError with code and missing</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>loadSession without a record or while signed out does not finish a sign-up</t>
+          <t>a 400 "Invalid input" lists the fields named by its issues</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>a record for another email is dropped and applies nothing</t>
+          <t>a network failure throws ApiError(0, network)</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
@@ -9012,12 +9012,12 @@
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>a failed PATCH keeps the full record</t>
+          <t>a server that never answers fails as network after the time limit</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>after the PATCH succeeded, a failed upload keeps only email, tick and picture; the retry does not PATCH again</t>
+          <t>saves have no time limit: a slow save that succeeds is not reported as a failure</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>a picture whose cached file is gone is dropped and the record cleared</t>
+          <t>updateMe PATCHes the account name</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -9093,12 +9093,12 @@
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>sign-up keeps the record for the code step; a failed sign-up leaves none</t>
+          <t>upload sends multipart with the cookie and no time limit</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>sends the stored cookie and stores a new set-cookie</t>
+          <t>upload sends the file bytes with its name and type, not a bare { uri } object</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>a single joined set-cookie header (no getSetCookie) is split into its cookies</t>
+          <t>a file the phone cannot open is "File unreadable", not a network error, and nothing is sent</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>clears the session on 401</t>
+          <t>upload maps a 413 to ApiError "File too large"</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>a 401 without a stored session does not call onUnauthorized</t>
+          <t>upload maps a network failure to ApiError network and does not retry</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>every request names the app origin and leaves the platform cookie store out</t>
+          <t>a store that cannot be read (Keystore failure) sends the request without a cookie</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>a 409 with error and missing throws ApiError with code and missing</t>
+          <t>a cookie that cannot be saved does not fail a request the server already carried out</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>a 400 "Invalid input" lists the fields named by its issues</t>
+          <t>a malformed Set-Cookie line without "=" is skipped</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>a network failure throws ApiError(0, network)</t>
+          <t>updateMe sends the one-field name as first and last name, split at the last space</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
@@ -9336,12 +9336,12 @@
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>a server that never answers fails as network after the time limit</t>
+          <t>loading -&gt; signed in -&gt; signed out</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>saves have no time limit: a slow save that succeeds is not reported as a failure</t>
+          <t>an unverified email never counts as signed in: sign-in sends a code and asks for it</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>updateMe PATCHes the account name</t>
+          <t>a server that refuses unverified sign-ins (EMAIL_NOT_VERIFIED) also leads to the code screen</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -9417,12 +9417,12 @@
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>upload sends multipart with the cookie and no time limit</t>
+          <t>sign-up creates the account and sends the code; the right code signs in and saves the account name</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>upload sends the file bytes with its name and type, not a bare { uri } object</t>
+          <t>a wrong code throws and keeps signed out</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>a file the phone cannot open is "File unreadable", not a network error, and nothing is sent</t>
+          <t>a failed login rejects and keeps signed out; a server error on load means signed out</t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>upload maps a 413 to ApiError "File too large"</t>
+          <t>a network error on load sets offline (not signed out); retry recovers</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>upload maps a network failure to ApiError network and does not retry</t>
+          <t>onUnauthorized from the API client signs the user out</t>
         </is>
       </c>
       <c r="D332" s="4" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>a store that cannot be read (Keystore failure) sends the request without a cookie</t>
+          <t>switching the language also saves it for emails, but only while signed in</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>a cookie that cannot be saved does not fail a request the server already carried out</t>
+          <t>verify finishes the sign-up: names and address, then the picture, then the record is cleared; returns the tick</t>
         </is>
       </c>
       <c r="D334" s="4" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>a malformed Set-Cookie line without "=" is skipped</t>
+          <t>a failed upload keeps the record; loadSession retries it once and clears it</t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>updateMe sends the one-field name as first and last name, split at the last space</t>
+          <t>loadSession without a record or while signed out does not finish a sign-up</t>
         </is>
       </c>
       <c r="D336" s="4" t="inlineStr">
@@ -9655,17 +9655,17 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>Pending signup</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>pending-signup.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>the pending record round-trips and clears</t>
+          <t>a record for another email is dropped and applies nothing</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="B338" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C338" s="4" t="inlineStr">
         <is>
-          <t>no rows when no service needs a document</t>
+          <t>a failed PATCH keeps the full record</t>
         </is>
       </c>
       <c r="D338" s="4" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="B339" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>a babysitting service with nothing uploaded â†’ police-certificate none</t>
+          <t>after the PATCH succeeded, a failed upload keeps only email, tick and picture; the retry does not PATCH again</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="B340" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C340" s="4" t="inlineStr">
         <is>
-          <t>the most recently reviewed check decides, like the server</t>
+          <t>a picture whose cached file is gone is dropped and the record cleared</t>
         </is>
       </c>
       <c r="D340" s="4" t="inlineStr">
@@ -9768,12 +9768,12 @@
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>a pending check shows pending even after an approval</t>
+          <t>sign-up keeps the record for the code step; a failed sign-up leaves none</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="B342" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>a requirement code the app does not know still gets a row, after the known ones</t>
+          <t>finishing a sign-up reloads /me so the home nudge sees the new picture; nothing to finish, nothing to reload</t>
         </is>
       </c>
       <c r="D342" s="4" t="inlineStr">
@@ -9817,17 +9817,17 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Picture nudge</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>picture-nudge.test.ts</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>two services needing the same document give one row</t>
+          <t>the dismissed-nudge key is per user, so a second account on the device still sees it</t>
         </is>
       </c>
       <c r="D343" s="4" t="inlineStr">
@@ -9844,17 +9844,17 @@
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B344" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>two different categories needing the same document give one row with the latest status</t>
+          <t>two quick changes become one request with the last value</t>
         </is>
       </c>
       <c r="D344" s="4" t="inlineStr">
@@ -9871,17 +9871,17 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C345" s="4" t="inlineStr">
         <is>
-          <t>a hidden service says a document is needed until it is uploaded, then that it waits for the check</t>
+          <t>flush saves immediately and nothing is sent twice</t>
         </is>
       </c>
       <c r="D345" s="4" t="inlineStr">
@@ -9898,17 +9898,17 @@
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B346" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C346" s="4" t="inlineStr">
         <is>
-          <t>sharing is allowed only while no service waits for a document</t>
+          <t>a rejected save marks error and retry resends the same value</t>
         </is>
       </c>
       <c r="D346" s="4" t="inlineStr">
@@ -9925,17 +9925,17 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>applyTexts swaps only the translatable fields and keeps names, prices and photos</t>
+          <t>a change typed while a save is in flight is sent after it, in order</t>
         </is>
       </c>
       <c r="D347" s="4" t="inlineStr">
@@ -9952,17 +9952,17 @@
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B348" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C348" s="4" t="inlineStr">
         <is>
-          <t>applyTexts matches services and references by id and leaves unknown ones untouched</t>
+          <t>dispose sends a pending change so nothing typed is lost</t>
         </is>
       </c>
       <c r="D348" s="4" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>match.test.ts</t>
         </is>
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>applyTexts keeps line breaks</t>
+          <t>matches ignores case and accents, and an empty query matches everything</t>
         </is>
       </c>
       <c r="D349" s="4" t="inlineStr">
@@ -10060,17 +10060,17 @@
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>Serial create</t>
+          <t>Stale guard</t>
         </is>
       </c>
       <c r="B352" s="4" t="inlineStr">
         <is>
-          <t>serial-create.test.ts</t>
+          <t>stale-guard.test.ts</t>
         </is>
       </c>
       <c r="C352" s="4" t="inlineStr">
         <is>
-          <t>choosing twice before the create returns creates once, then updates</t>
+          <t>a response older than one already applied is ignored</t>
         </is>
       </c>
       <c r="D352" s="4" t="inlineStr">
@@ -10087,17 +10087,17 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>Serial create</t>
+          <t>Stale guard</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>serial-create.test.ts</t>
+          <t>stale-guard.test.ts</t>
         </is>
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>an existing id is only updated</t>
+          <t>answers arriving in order are all applied</t>
         </is>
       </c>
       <c r="D353" s="4" t="inlineStr">
@@ -10114,17 +10114,17 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Serial create</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>match.test.ts</t>
+          <t>serial-create.test.ts</t>
         </is>
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>matches ignores case and accents, and an empty query matches everything</t>
+          <t>choosing twice before the create returns creates once, then updates</t>
         </is>
       </c>
       <c r="D354" s="4" t="inlineStr">
@@ -10141,17 +10141,17 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Serial create</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>serial-create.test.ts</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>two quick changes become one request with the last value</t>
+          <t>an existing id is only updated</t>
         </is>
       </c>
       <c r="D355" s="4" t="inlineStr">
@@ -10168,17 +10168,17 @@
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B356" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>flush saves immediately and nothing is sent twice</t>
+          <t>no rows when no service needs a document</t>
         </is>
       </c>
       <c r="D356" s="4" t="inlineStr">
@@ -10195,17 +10195,17 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>a rejected save marks error and retry resends the same value</t>
+          <t>a babysitting service with nothing uploaded â†’ police-certificate none</t>
         </is>
       </c>
       <c r="D357" s="4" t="inlineStr">
@@ -10222,17 +10222,17 @@
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B358" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C358" s="4" t="inlineStr">
         <is>
-          <t>a change typed while a save is in flight is sent after it, in order</t>
+          <t>the most recently reviewed check decides, like the server</t>
         </is>
       </c>
       <c r="D358" s="4" t="inlineStr">
@@ -10249,17 +10249,17 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>dispose sends a pending change so nothing typed is lost</t>
+          <t>a pending check shows pending even after an approval</t>
         </is>
       </c>
       <c r="D359" s="4" t="inlineStr">
@@ -10276,17 +10276,17 @@
     <row r="360">
       <c r="A360" s="4" t="inlineStr">
         <is>
-          <t>Stale guard</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B360" s="4" t="inlineStr">
         <is>
-          <t>stale-guard.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>a response older than one already applied is ignored</t>
+          <t>a requirement code the app does not know still gets a row, after the known ones</t>
         </is>
       </c>
       <c r="D360" s="4" t="inlineStr">
@@ -10303,17 +10303,17 @@
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
         <is>
-          <t>Stale guard</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>stale-guard.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>answers arriving in order are all applied</t>
+          <t>two services needing the same document give one row</t>
         </is>
       </c>
       <c r="D361" s="4" t="inlineStr">
@@ -10330,17 +10330,17 @@
     <row r="362">
       <c r="A362" s="4" t="inlineStr">
         <is>
-          <t>Use me</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B362" s="4" t="inlineStr">
         <is>
-          <t>use-me.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>a loadMe in flight at sign-out never fills the store for the next account</t>
+          <t>two different categories needing the same document give one row with the latest status</t>
         </is>
       </c>
       <c r="D362" s="4" t="inlineStr">
@@ -10357,22 +10357,22 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>rejects three decimals and negative prices</t>
+          <t>a hidden service says a document is needed until it is uploaded, then that it waits for the check</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E363" s="4" t="inlineStr">
@@ -10384,22 +10384,22 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>needs no price on request</t>
+          <t>sharing is allowed only while no service waits for a document</t>
         </is>
       </c>
       <c r="D364" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E364" s="4" t="inlineStr">
@@ -10411,22 +10411,22 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>caps pageSize at 100</t>
+          <t>saving a waiting service keeps Share hidden: the server answer carries waitingFor</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E365" s="4" t="inlineStr">
@@ -10438,22 +10438,22 @@
     <row r="366">
       <c r="A366" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Use me</t>
         </is>
       </c>
       <c r="B366" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>use-me.test.ts</t>
         </is>
       </c>
       <c r="C366" s="4" t="inlineStr">
         <is>
-          <t>parseBody answers 400 with the issues</t>
+          <t>a loadMe in flight at sign-out never fills the store for the next account</t>
         </is>
       </c>
       <c r="D366" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E366" s="4" t="inlineStr">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="C367" s="4" t="inlineStr">
         <is>
-          <t>parseQuery reads the search params</t>
+          <t>ServiceInputSchema rejects three decimals and negative prices</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="C368" s="4" t="inlineStr">
         <is>
-          <t>lists are { docs: [...] }</t>
+          <t>ServiceInputSchema needs no price on request</t>
         </is>
       </c>
       <c r="D368" s="4" t="inlineStr">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="C369" s="4" t="inlineStr">
         <is>
-          <t>reference year is checked against the current year at parse time</t>
+          <t>AdminListQuerySchema caps pageSize at 100</t>
         </is>
       </c>
       <c r="D369" s="4" t="inlineStr">
@@ -10546,7 +10546,7 @@
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B370" s="4" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="C370" s="4" t="inlineStr">
         <is>
-          <t>de and en have the same keys</t>
+          <t>parse helpers parseBody answers 400 with the issues</t>
         </is>
       </c>
       <c r="D370" s="4" t="inlineStr">
@@ -10573,7 +10573,7 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="C371" s="4" t="inlineStr">
         <is>
-          <t>no text is empty and no two keys of one namespace carry the same text</t>
+          <t>parse helpers parseQuery reads the search params</t>
         </is>
       </c>
       <c r="D371" s="4" t="inlineStr">
@@ -10600,7 +10600,7 @@
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B372" s="4" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="C372" s="4" t="inlineStr">
         <is>
-          <t>no text contains Treuhand, Escrow, garantiert or a competitor name</t>
+          <t>list envelopes lists are { docs: [...] }</t>
         </is>
       </c>
       <c r="D372" s="4" t="inlineStr">
@@ -10627,7 +10627,7 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>the product name is only written in brand.name</t>
+          <t>list envelopes reference year is checked against the current year at parse time</t>
         </is>
       </c>
       <c r="D373" s="4" t="inlineStr">
@@ -10654,7 +10654,7 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>replaces placeholders and falls back to the key when missing</t>
+          <t>address street, postcode and city are required (no empty or blank parts)</t>
         </is>
       </c>
       <c r="D374" s="4" t="inlineStr">
@@ -10681,7 +10681,7 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B375" s="4" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>fills the brand name without a parameter</t>
+          <t>service input as the app sends it a category alone is valid (the server fills currency and title)</t>
         </is>
       </c>
       <c r="D375" s="4" t="inlineStr">
@@ -10718,7 +10718,7 @@
       </c>
       <c r="C376" s="4" t="inlineStr">
         <is>
-          <t>knows its languages</t>
+          <t>catalogue de and en have the same keys</t>
         </is>
       </c>
       <c r="D376" s="4" t="inlineStr">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>formats per language</t>
+          <t>catalogue no text is empty and no two keys of one namespace carry the same text</t>
         </is>
       </c>
       <c r="D377" s="4" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
-          <t>formats price labels from the catalogue</t>
+          <t>catalogue no text contains Treuhand, Escrow, garantiert or a competitor name</t>
         </is>
       </c>
       <c r="D378" s="4" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>en-GB,en;q=0.9,de;q=0.8 -&gt; en</t>
+          <t>catalogue the product name is only written in brand.name</t>
         </is>
       </c>
       <c r="D379" s="4" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="C380" s="4" t="inlineStr">
         <is>
-          <t>* -&gt; undefined</t>
+          <t>t replaces placeholders and falls back to the key when missing</t>
         </is>
       </c>
       <c r="D380" s="4" t="inlineStr">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="C381" s="4" t="inlineStr">
         <is>
-          <t>fr-FR -&gt; undefined</t>
+          <t>t fills the brand name without a parameter</t>
         </is>
       </c>
       <c r="D381" s="4" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="C382" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> -&gt; undefined</t>
+          <t>t knows its languages</t>
         </is>
       </c>
       <c r="D382" s="4" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>undefined -&gt; undefined</t>
+          <t>money formats per language</t>
         </is>
       </c>
       <c r="D383" s="4" t="inlineStr">
@@ -10916,6 +10916,168 @@
         </is>
       </c>
       <c r="E383" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B384" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C384" s="4" t="inlineStr">
+        <is>
+          <t>money formats price labels from the catalogue</t>
+        </is>
+      </c>
+      <c r="D384" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E384" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B385" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C385" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang en-GB,en;q=0.9,de;q=0.8 -&gt; en</t>
+        </is>
+      </c>
+      <c r="D385" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E385" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B386" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C386" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang * -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D386" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E386" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B387" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C387" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang fr-FR -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D387" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E387" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B388" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C388" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang  -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D388" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E388" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B389" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C389" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang undefined -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D389" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E389" s="4" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
@@ -10932,7 +11094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -11025,7 +11187,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>35 files, 254 tests (the root run); the Neon Auth cookie-flow spec timed out once at 5 s and passed alone on the rerun.</t>
+          <t>35 files, 257 tests (the root run).</t>
         </is>
       </c>
     </row>
@@ -11069,7 +11231,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>254 tests. The Neon Auth cookie-flow spec (real service, 5 s limit) timed out once in the full run and passed when run alone.</t>
+          <t>257 tests.</t>
         </is>
       </c>
     </row>
@@ -11081,7 +11243,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>19 suites.</t>
+          <t>20 suites.</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -11091,7 +11253,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>107 tests.</t>
+          <t>108 tests.</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11275,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>21 tests.</t>
+          <t>23 tests (contract 9, i18n 14).</t>
         </is>
       </c>
     </row>
@@ -11642,6 +11804,50 @@
       <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Migration 0008 on a database with data</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Migrated to 0007 with a suspended provider, one without a date, published providers without names and pictures, then to 0008.</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>db-migrations.int.spec.ts: suspensions carried over, published ones back to draft. Also applied by hand on kando-dev (0 rows changed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>The app request shapes (fix wave 2)</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Category-only service create, then one field per PATCH, with the exact bodies the app sends.</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>services-references.int.spec.ts (a category alone, one field per save; add and update answer with waitingFor).</t>
         </is>
       </c>
     </row>
@@ -11656,7 +11862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -11905,17 +12111,17 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Parked: nudge-dismissed flag is device-wide</t>
+          <t>Fixed (wave 2, minor 9): nudge-dismissed flag per user</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>A second account on the same phone does not see the nudge.</t>
+          <t>The key carries the user id (hash below).</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Parked (minor)</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -12017,7 +12223,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Fixed, re-review pending</t>
+          <t>Fixed, fix wave 2 done, re-review pending</t>
         </is>
       </c>
     </row>
@@ -12216,12 +12422,233 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>The "not suspended" test is written out in about eight SQL places (rls.ts, search.ts, public-profile.ts, sitemap) plus TypeScript variants; they agree today, one shared constant would keep it so.</t>
+          <t>rls.ts policies now use the constant (wave 2); the SQL functions, search.ts, public-profile.ts, sitemap and TypeScript variants still write it out.</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Parked (minor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (wave 2, Critical): service create from the app</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Currency is optional on create and defaults to EUR; the title defaults to the category name. Tested with the exact body { categoryId } then one-field PATCHes (af82e89).</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (wave 2, Important): add and update lose waitingFor</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>One helper gives waitingFor and visibleInSearch to list, add and update; Share stays hidden while a check is pending (af82e89).</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (wave 2, minor 4): suspension emails</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Only published profiles get the suspension and published-again emails; the cron still clears every ended suspension (c033602).</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (wave 2, minor 6): Germany fallbacks</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>No DE fallback in shared server code; the provider column default applies without an address (b015bd7).</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (wave 2, minor 7, 8, 9): app</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Sign-in sends only the language, sign-up ends with a /me reload, the nudge key is per user, dead updateName removed (107530c).</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (wave 2, minor 11): address</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Street, postcode and city are required (cdc0958).</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (wave 2, minor 10): email link</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>App link uses the skilled scheme (d72c36c).</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (wave 2, minor 12): migration 0008 on real data</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Suspended providers stay hidden; published ones without names or picture go back to draft; tested on a 0007 database with rows (5e965ac).</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (wave 2): simplification</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>rls.ts uses NOT_SUSPENDED; the price clause in search.ts is gone, offerable_service_ids covers it and the category search test proves it (34804f3).</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Parked: concurrent approvals</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Two approvals at once can send the "profile is live" email twice.</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Parked</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Parked: last complete service of a live profile</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Deleting or updating it is not blocked.</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Parked</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Parked: suspension check in TypeScript</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Duplicated next to the SQL.</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Parked</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Owner question: My profile tab for customers</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Should the tab be visible to customers?</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Open (owner)</t>
         </is>
       </c>
     </row>

--- a/Reports/Registration-Setup-Test-Report.xlsx
+++ b/Reports/Registration-Setup-Test-Report.xlsx
@@ -12116,7 +12116,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>The key carries the user id (hash below).</t>
+          <t>The key carries the user id (107530c).</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">

--- a/Reports/Registration-Setup-Test-Report.xlsx
+++ b/Reports/Registration-Setup-Test-Report.xlsx
@@ -11825,7 +11825,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>db-migrations.int.spec.ts: suspensions carried over, published ones back to draft. Also applied by hand on kando-dev (0 rows changed).</t>
+          <t>db-migrations.int.spec.ts: suspensions carried over, published ones back to draft. Also applied by hand on kando-dev (0 rows changed). Legacy rows are read through the domain mappers.</t>
         </is>
       </c>
     </row>
@@ -11862,7 +11862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -12652,6 +12652,23 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (re-review, Important): 0008 suspension without a date</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>The legacy flag now becomes 9999-12-31, not infinity (Node read infinity as Invalid Date and the profile and admin provider reads threw). The migration test reads legacy rows through getMyProfile and adminGet and checks they stay hidden (f7eb8ce). Dev database unaffected: no such row.</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Reports/Registration-Setup-Test-Report.xlsx
+++ b/Reports/Registration-Setup-Test-Report.xlsx
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTA('Test Results'!C2:C389)</f>
+        <f>COUNTA('Test Results'!C2:C391)</f>
         <v/>
       </c>
     </row>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E389"/>
+  <dimension ref="A1:E391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -11078,6 +11078,60 @@
         </is>
       </c>
       <c r="E389" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="4" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B390" s="4" t="inlineStr">
+        <is>
+          <t>profile-tab.test.ts</t>
+        </is>
+      </c>
+      <c r="C390" s="4" t="inlineStr">
+        <is>
+          <t>the My profile tab shows only for a known provider</t>
+        </is>
+      </c>
+      <c r="D390" s="4" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="E390" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="4" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B391" s="4" t="inlineStr">
+        <is>
+          <t>profile-tab.test.ts</t>
+        </is>
+      </c>
+      <c r="C391" s="4" t="inlineStr">
+        <is>
+          <t>after sign-out the next account does not inherit the provider tab</t>
+        </is>
+      </c>
+      <c r="D391" s="4" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="E391" s="4" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
@@ -11253,7 +11307,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>108 tests.</t>
+          <t>110 tests.</t>
         </is>
       </c>
     </row>
@@ -11862,7 +11916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -12669,6 +12723,23 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>My profile tab only for providers (PR #9)</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Owner decision: customers reach the profile page through Account &gt; Offer services; the tab appears once they are providers. Two jest tests added (110 app tests). Phone check: customer sees no tab; Offer services opens the page; tab appears after the draft exists.</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Not yet done (phone)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Reports/Registration-Setup-Test-Report.xlsx
+++ b/Reports/Registration-Setup-Test-Report.xlsx
@@ -454,7 +454,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Full suite on branch registration-setup (after fix wave 2 of the independent review), run 27 October 2026: web integration tests on the local Docker database, app and package unit tests. Features only a phone can confirm are marked Not yet done (phone) in Other Checks.</t>
+          <t>Full suite on branch account-address-saved (fixes from the owner phone test, on top of registration-setup), run 27 October 2026: web integration tests on the local Docker database, app and package unit tests. Features only a phone can confirm are marked Not yet done (phone) in Other Checks.</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTA('Test Results'!C2:C391)</f>
+        <f>COUNTA('Test Results'!C2:C398)</f>
         <v/>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Test Results'!E2:E389,"Passed")</f>
+        <f>COUNTIF('Test Results'!E2:E398,"Passed")</f>
         <v/>
       </c>
     </row>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Test Results'!E2:E389,"Failed")</f>
+        <f>COUNTIF('Test Results'!E2:E398,"Failed")</f>
         <v/>
       </c>
     </row>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF('Test Results'!E2:E389,"Skipped")</f>
+        <f>COUNTIF('Test Results'!E2:E398,"Skipped")</f>
         <v/>
       </c>
     </row>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E391"/>
+  <dimension ref="A1:E398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>suspension and published-again emails go to published profiles only; the cron still clears every ended suspension</t>
+          <t>GET users/[id] returns an address that has only a postcode</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1069,17 +1069,17 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Admin lang</t>
+          <t>Admin back office API</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>admin-lang.int.spec.ts</t>
+          <t>admin-api.int.spec.ts</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>adminLang {"cookie":"en"} -&gt; en</t>
+          <t>suspension and published-again emails go to published profiles only; the cron still clears every ended suspension</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>adminLang {"cookie":"fr"} -&gt; de</t>
+          <t>adminLang {"cookie":"en"} -&gt; en</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>adminLang {"cookie":"xx","acceptLanguage":"en"} -&gt; en</t>
+          <t>adminLang {"cookie":"fr"} -&gt; de</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>adminLang {"acceptLanguage":"en-GB,en;q=0.9,de;q=0.8"} -&gt; en</t>
+          <t>adminLang {"cookie":"xx","acceptLanguage":"en"} -&gt; en</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>adminLang {"acceptLanguage":"fr-FR"} -&gt; de</t>
+          <t>adminLang {"acceptLanguage":"en-GB,en;q=0.9,de;q=0.8"} -&gt; en</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>adminLang {} -&gt; de</t>
+          <t>adminLang {"acceptLanguage":"fr-FR"} -&gt; de</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>adminLangCookie lasts a year for the whole site</t>
+          <t>adminLang {} -&gt; de</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>useAt renders en</t>
+          <t>adminLangCookie lasts a year for the whole site</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>useAt renders de</t>
+          <t>useAt renders en</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>admin layout follows the cookie, then Accept-Language, then German</t>
+          <t>useAt renders de</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1339,17 +1339,17 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Staff roles</t>
+          <t>Admin lang</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>admin-roles.int.spec.ts</t>
+          <t>admin-lang.int.spec.ts</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>a Reviewer cannot do Administrator actions, and nothing changes</t>
+          <t>admin layout follows the cookie, then Accept-Language, then German</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>a Reviewer cannot change or delete an existing category or page</t>
+          <t>a Reviewer cannot do Administrator actions, and nothing changes</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>a Reviewer can read users and documents</t>
+          <t>a Reviewer cannot change or delete an existing category or page</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>a customer with no staff role gets 403 on every admin route; no session gets 401</t>
+          <t>a Reviewer can read users and documents</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>the last Administrator cannot be demoted</t>
+          <t>a customer with no staff role gets 403 on every admin route; no session gets 401</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>every route file under app/api/admin exports handlers built with adminRequest</t>
+          <t>the last Administrator cannot be demoted</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1501,17 +1501,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Security rule check</t>
+          <t>Staff roles</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>app-endpoints-wrapped.int.spec.ts</t>
+          <t>admin-roles.int.spec.ts</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>the owner-connection check catches a bypass (negative fixture)</t>
+          <t>every route file under app/api/admin exports handlers built with adminRequest</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>every route file under app/app-api exports handlers built with appRequest</t>
+          <t>the owner-connection check catches a bypass (negative fixture)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1555,17 +1555,17 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>App request wrapper</t>
+          <t>Security rule check</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>app-request.int.spec.ts</t>
+          <t>app-endpoints-wrapped.int.spec.ts</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>first contact creates the users row</t>
+          <t>every route file under app/app-api exports handlers built with appRequest</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>a forged cookie is 401 and touches nothing</t>
+          <t>first contact creates the users row</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>required auth without a cookie is 401</t>
+          <t>a forged cookie is 401 and touches nothing</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>optional auth without a cookie runs with no user</t>
+          <t>required auth without a cookie is 401</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>an unconfirmed email: 403 where auth is required, signed out where optional; never a users row</t>
+          <t>optional auth without a cookie runs with no user</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>a handler error rolls back and returns 500</t>
+          <t>an unconfirmed email: 403 where auth is required, signed out where optional; never a users row</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>a body over maxBodyBytes is 413 before the handler runs</t>
+          <t>a handler error rolls back and returns 500</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>user A cannot read user B through the wrapper</t>
+          <t>a body over maxBodyBytes is 413 before the handler runs</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>app_user cannot write staff columns of its own row</t>
+          <t>user A cannot read user B through the wrapper</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>first contact with a changed email updates the row</t>
+          <t>app_user cannot write staff columns of its own row</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>a second id with the same email gets 409 and no row is written</t>
+          <t>first contact with a changed email updates the row</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>a thrown 400 Response is returned unchanged</t>
+          <t>a second id with the same email gets 409 and no row is written</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1879,17 +1879,17 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Sign-up and session</t>
+          <t>App request wrapper</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>auth-cookie-flow.int.spec.ts</t>
+          <t>app-request.int.spec.ts</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>auth cookie flow signs up by REST, captures the cookie; /app-api/v1/me knows the session but refuses it until the email is confirmed</t>
+          <t>a thrown 400 Response is returned unchanged</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1906,17 +1906,17 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Categories</t>
+          <t>Sign-up and session</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>categories.int.spec.ts</t>
+          <t>auth-cookie-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>ordered by sort, "other services" always last, names in the requested language, anonymous allowed</t>
+          <t>auth cookie flow signs up by REST, captures the cookie; /app-api/v1/me knows the session but refuses it until the email is confirmed</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>an unknown language is 400</t>
+          <t>ordered by sort, "other services" always last, names in the requested language, anonymous allowed</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1960,17 +1960,17 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Concurrency</t>
+          <t>Categories</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>concurrency.int.spec.ts</t>
+          <t>categories.int.spec.ts</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>12 concurrent searches and 12 concurrent public pages all complete</t>
+          <t>an unknown language is 400</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Cron suspensions</t>
+          <t>Concurrency</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>cron-suspensions.int.spec.ts</t>
+          <t>concurrency.int.spec.ts</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>401 without the right secret, and when CRON_SECRET is unset</t>
+          <t>12 concurrent searches and 12 concurrent public pages all complete</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>ends a past suspension once: both columns cleared, one email; a future one is left alone</t>
+          <t>401 without the right secret, and when CRON_SECRET is unset</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2041,17 +2041,17 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Database migrations</t>
+          <t>Cron suspensions</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>db-migrations.int.spec.ts</t>
+          <t>cron-suspensions.int.spec.ts</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>migrates an empty database and classifies every table</t>
+          <t>ends a past suspension once: both columns cleared, one email; a future one is left alone</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>0008: person fields on users, suspensions by date, drafts allowed, notifications; applyRls succeeds</t>
+          <t>migrates an empty database and classifies every table</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>photos: a profile photo has no provider, a portfolio photo has one, one profile photo per person</t>
+          <t>0008: person fields on users, suspensions by date, drafts allowed, notifications; applyRls succeeds</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>0008 on a database with data: a suspended provider stays hidden, a published one without names or picture goes back to draft</t>
+          <t>photos: a profile photo has no provider, a portfolio photo has one, one profile photo per person</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -2149,17 +2149,17 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Emails</t>
+          <t>Database migrations</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>email.int.spec.ts</t>
+          <t>db-migrations.int.spec.ts</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>approval: one email in the user language with the document name and the deep link</t>
+          <t>0008 on a database with data: a suspended provider stays hidden, a published one without names or picture goes back to draft</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>rejection in German includes the note verbatim, escaped in the HTML</t>
+          <t>approval: one email in the user language with the document name and the deep link</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>without a key it only logs and records, and never throws</t>
+          <t>rejection in German includes the note verbatim, escaped in the HTML</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>outside tests without a key: one log line without recipient or body, and nothing kept in memory</t>
+          <t>without a key it only logs and records, and never throws</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>with a key it calls Resend with the full message; an { error } and a throw are logged, not thrown</t>
+          <t>outside tests without a key: one log line without recipient or body, and nothing kept in memory</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>an unexpected stored language falls back to German</t>
+          <t>with a key it calls Resend with the full message; an { error } and a throw are logged, not thrown</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -2311,17 +2311,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Uploads and document review</t>
+          <t>Emails</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>files-review.int.spec.ts</t>
+          <t>email.int.spec.ts</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>afterCommit: a handler that deletes a photo and then throws rolls back, the object stays</t>
+          <t>an unexpected stored language falls back to German</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>afterCommit: the object is deleted only after the commit</t>
+          <t>afterCommit: a handler that deletes a photo and then throws rolls back, the object stays</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>private_files and documents are isolated (RLS)</t>
+          <t>afterCommit: the object is deleted only after the commit</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>at most 10 unsubmitted uploads per user (409)</t>
+          <t>private_files and documents are isolated (RLS)</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>a decompression bomb and a header followed by garbage are 400; a later upload is accepted</t>
+          <t>at most 10 unsubmitted uploads per user (409)</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>EXIF is stripped from the stored JPEG</t>
+          <t>a decompression bomb and a header followed by garbage are 400; a later upload is accepted</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>alt over 200 characters is 400</t>
+          <t>EXIF is stripped from the stored JPEG</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>an unauthenticated upload is refused before the body is read</t>
+          <t>alt over 200 characters is 400</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>the body is read before the first-contact user row and the transaction exist</t>
+          <t>an unauthenticated upload is refused before the body is read</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>photos of a published provider are public, and unreadable once suspended</t>
+          <t>the body is read before the first-contact user row and the transaction exist</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>replacing the profile photo of a published profile works</t>
+          <t>photos of a published provider are public, and unreadable once suspended</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>deleting the profile photo while publishing never leaves a published profile without a photo</t>
+          <t>replacing the profile photo of a published profile works</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>two simultaneous submits for one requirement give one 201 and one 409</t>
+          <t>deleting the profile photo while publishing never leaves a published profile without a photo</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>the database refuses a second pending check for a requirement</t>
+          <t>two simultaneous submits for one requirement give one 201 and one 409</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>approval (staff SQL) makes a service with required documents offerable</t>
+          <t>the database refuses a second pending check for a requirement</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>the signed link carries X-Amz-Expires=300 and the public URL needs AWS_ENDPOINT</t>
+          <t>approval (staff SQL) makes a service with required documents offerable</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -2743,17 +2743,17 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Uploads</t>
+          <t>Uploads and document review</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>files.int.spec.ts</t>
+          <t>files-review.int.spec.ts</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>a profile photo is re-encoded to JPEG at most 1600 px and returned in contract shape</t>
+          <t>the signed link carries X-Amz-Expires=300 and the public URL needs AWS_ENDPOINT</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>a new profile photo replaces the old one and deletes its object</t>
+          <t>a profile photo is re-encoded to JPEG at most 1600 px and returned in contract shape</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>portfolio is limited to 12 (409), a non-image is 400, a missing kind is 400</t>
+          <t>a new profile photo replaces the old one and deletes its object</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>a portfolio photo needs a profile first (409); anonymous is 401; an oversize body is 413</t>
+          <t>portfolio is limited to 12 (409), a non-image is 400, a missing kind is 400</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>deleting a photo: another user gets 404, the owner 204 and the object and row are gone</t>
+          <t>a portfolio photo needs a profile first (409); anonymous is 401; an oversize body is 413</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>the profile photo of a published profile cannot be deleted (409)</t>
+          <t>deleting a photo: another user gets 404, the owner 204 and the object and row are gone</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>suspended_until is domain-only and photos are isolated</t>
+          <t>the profile photo of a published profile cannot be deleted (409)</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>files: a PDF goes to the private bucket, a non-PDF is 400, another user gets 404, the owner a signed link</t>
+          <t>suspended_until is domain-only and photos are isolated</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>documents also take JPEG, PNG and WEBP photos: re-encoded without metadata, at most 2400 px, stored with their type</t>
+          <t>files: a PDF goes to the private bucket, a non-PDF is 400, another user gets 404, the owner a signed link</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>a GIF and a text file renamed to .pdf are refused as documents</t>
+          <t>documents also take JPEG, PNG and WEBP photos: re-encoded without metadata, at most 2400 px, stored with their type</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>staff open an image document through the same signed link; it is served as an image</t>
+          <t>a GIF and a text file renamed to .pdf are refused as documents</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>a failed file insert removes the uploaded object</t>
+          <t>staff open an image document through the same signed link; it is served as an image</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>verifications: one pending check per requirement (409 removes the second file), bad input is 400</t>
+          <t>a failed file insert removes the uploaded object</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>the profile photo is private to its owner: another user cannot see it and gets 404 on delete; listPhotos puts it first</t>
+          <t>verifications: one pending check per requirement (409 removes the second file), bad input is 400</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -3121,17 +3121,17 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Website home page</t>
+          <t>Uploads</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>home-page.int.spec.ts</t>
+          <t>files.int.spec.ts</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>home page is German by default: headline, categories, store badges without links, no forbidden words</t>
+          <t>the profile photo is private to its owner: another user cannot see it and gets 404 on delete; listPhotos puts it first</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>home page switches to English with ?lang=en and falls back to German for unknown values</t>
+          <t>home page is German by default: headline, categories, store badges without links, no forbidden words</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>home page has per-language metadata with canonical and hreflang for every language</t>
+          <t>home page switches to English with ?lang=en and falls back to German for unknown values</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>site layout metadataBase makes canonical and hreflang absolute on the site url</t>
+          <t>home page has per-language metadata with canonical and hreflang for every language</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>site layout html lang follows the request language; unknown falls back to de</t>
+          <t>site layout metadataBase makes canonical and hreflang absolute on the site url</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>site layout footer links the four legal pages with catalogue labels in both languages</t>
+          <t>site layout html lang follows the request language; unknown falls back to de</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -3283,17 +3283,17 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Website home page</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>notifications.int.spec.ts</t>
+          <t>home-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>live and nothing else pending: "profile is live" email with the link, and one notification</t>
+          <t>site layout footer links the four legal pages with catalogue labels in both languages</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>the link of a German provider has no lang parameter</t>
+          <t>live and nothing else pending: "profile is live" email with the link, and one notification</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>live but another document is still missing: says the category service is visible, no notification</t>
+          <t>the link of a German provider has no lang parameter</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>the approved requirement is not enough for any service: plain approval, no notification</t>
+          <t>live but another document is still missing: says the category service is visible, no notification</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>draft profile: offline text, no notification</t>
+          <t>the approved requirement is not enough for any service: plain approval, no notification</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>suspended profile: suspended text with the date, no notification</t>
+          <t>draft profile: offline text, no notification</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>a requirement that was already approved: plain approval, no notification</t>
+          <t>suspended profile: suspended text with the date, no notification</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>rejection is unchanged</t>
+          <t>a requirement that was already approved: plain approval, no notification</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>GET /me lists the notification; PATCH dismissed hides it; another user gets 404</t>
+          <t>rejection is unchanged</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -3526,17 +3526,17 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>Database connection</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>owner-connection.int.spec.ts</t>
+          <t>notifications.int.spec.ts</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>inside a request transaction the owner connection `db` is a different connection (not app_user)</t>
+          <t>GET /me lists the notification; PATCH dismissed hides it; another user gets 404</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>two interleaved requests keep their own user id and role</t>
+          <t>inside a request transaction the owner connection `db` is a different connection (not app_user)</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -3580,17 +3580,17 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>Legal and info pages</t>
+          <t>Database connection</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>pages.int.spec.ts</t>
+          <t>owner-connection.int.spec.ts</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>pages tables every table is classified (pages and page_texts are public reference tables)</t>
+          <t>two interleaved requests keep their own user id and role</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>pages tables anonymous app requests read pages but cannot write them</t>
+          <t>pages tables every table is classified (pages and page_texts are public reference tables)</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>getPage returns the text in the language, falls back to de, hides drafts and unknown slugs</t>
+          <t>pages tables anonymous app requests read pages but cannot write them</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>getPage publishedPages lists published pages only</t>
+          <t>getPage returns the text in the language, falls back to de, hides drafts and unknown slugs</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>legal page by slug renders the Markdown body in both languages with the de fallback</t>
+          <t>getPage publishedPages lists published pages only</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>legal page by slug 404 for unknown and unpublished slugs</t>
+          <t>legal page by slug renders the Markdown body in both languages with the de fallback</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>legal page by slug metadata: title, canonical and hreflang for every language</t>
+          <t>legal page by slug 404 for unknown and unpublished slugs</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>legal page by slug escapes HTML in a body and drops unsafe links</t>
+          <t>legal page by slug metadata: title, canonical and hreflang for every language</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>renderMarkdown escapes raw html and keeps Markdown</t>
+          <t>legal page by slug escapes HTML in a body and drops unsafe links</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>renderMarkdown external links get rel="nofollow ugc"; protocol-relative and backslash paths are dropped</t>
+          <t>renderMarkdown escapes raw html and keeps Markdown</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -3850,17 +3850,17 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>Postcodes</t>
+          <t>Legal and info pages</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>postcodes.int.spec.ts</t>
+          <t>pages.int.spec.ts</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>imports the German file and looks up 01053 Dresden</t>
+          <t>renderMarkdown external links get rel="nofollow ugc"; protocol-relative and backslash paths are dropped</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>rejects a four-digit German code and an unknown one</t>
+          <t>imports the German file and looks up 01053 Dresden</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Berlin to Munich is about 504 km</t>
+          <t>rejects a four-digit German code and an unknown one</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -3931,17 +3931,17 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>Website provider page</t>
+          <t>Postcodes</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>provider-page.int.spec.ts</t>
+          <t>postcodes.int.spec.ts</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>public provider page German default: public name heading, category, price "ab 80,00 â‚¬", on request, place</t>
+          <t>Berlin to Munich is about 504 km</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>public provider page English with ?lang=en: "from â‚¬80.00"</t>
+          <t>public provider page German default: public name heading, category, price "ab 80,00 â‚¬", on request, place</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>public provider page escapes user content</t>
+          <t>public provider page English with ?lang=en: "from â‚¬80.00"</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>public provider page 404 for a hidden provider (draft) and an unknown slug</t>
+          <t>public provider page escapes user content</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>public provider page metadata: title, description, canonical and hreflang for every language</t>
+          <t>public provider page 404 for a hidden provider (draft) and an unknown slug</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>translate link is shown only when the texts are not in the page language</t>
+          <t>public provider page metadata: title, description, canonical and hreflang for every language</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>translate link ?translate=1 shows the translation with the AI label, noindex, canonical unchanged</t>
+          <t>translate link is shown only when the texts are not in the page language</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>translate link ?translate=1 without a key shows the original texts and the unavailable copy</t>
+          <t>translate link ?translate=1 shows the translation with the AI label, noindex, canonical unchanged</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>translate link translate=1 on texts already in the viewer language: original, no label, no model call</t>
+          <t>translate link ?translate=1 without a key shows the original texts and the unavailable copy</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -4174,17 +4174,17 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>Provider profile</t>
+          <t>Website provider page</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>provider-profile.int.spec.ts</t>
+          <t>provider-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>GET is null when there is no profile</t>
+          <t>translate link translate=1 on texts already in the viewer language: original, no label, no model call</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>PUT creates (201) and a later PUT edits (200); responses fit the contract</t>
+          <t>GET is null when there is no profile</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>an unknown postcode is 400 and changes nothing</t>
+          <t>PUT creates (201) and a later PUT edits (200); responses fit the contract</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>a partial first save never fails on business rules</t>
+          <t>an unknown postcode is 400 and changes nothing</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>status, slug and suspended in the body are ignored</t>
+          <t>a partial first save never fails on business rules</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>one user's profile is not visible to another</t>
+          <t>status, slug and suspended in the body are ignored</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>an invalid body is 400 with the contract error</t>
+          <t>one user's profile is not visible to another</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>an unconfirmed email gets 403 EMAIL_NOT_VERIFIED from PUT provider-profile and GET /me, and no users row</t>
+          <t>an invalid body is 400 with the contract error</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>PATCH /me checks its body with the contract: 400 Invalid input names the field; a valid patch saves</t>
+          <t>an unconfirmed email gets 403 EMAIL_NOT_VERIFIED from PUT provider-profile and GET /me, and no users row</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>a user without an address still gets a draft (the provider row default country applies)</t>
+          <t>PATCH /me checks its body with the contract: 400 Invalid input names the field; a valid patch saves</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>POST creates a draft with the postcode prefilled; again returns the same id; GET /me is fine</t>
+          <t>an address with only a postcode is stored and returned; a street without a postcode is refused; null clears it</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>missing: the empty draft lists the person-independent items, business adds two, saves shrink it, PUT carries it</t>
+          <t>a user without an address still gets a draft (the provider row default country applies)</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>publish of an incomplete draft is 409 with the list; complete publishes with public name Lena F.</t>
+          <t>POST creates a draft with the postcode prefilled; again returns the same id; GET /me is fine</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>a draft with every nullable field null is invisible in search and the sitemap</t>
+          <t>missing: the empty draft lists the person-independent items, business adds two, saves shrink it, PUT carries it</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>a draft created during a suspension cannot be published</t>
+          <t>publish of an incomplete draft is 409 with the list; complete publishes with public name Lena F.</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>the draft prefills the postcode only when it is a known one</t>
+          <t>a draft with every nullable field null is invisible in search and the sitemap</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>a live profile cannot be emptied by a save: 409 with the missing list, nothing changed</t>
+          <t>a draft created during a suspension cannot be published</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>a provider whose names are missing cannot publish: missing lists name</t>
+          <t>the draft prefills the postcode only when it is a known one</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>the draft's postcode lookup uses the owner's stored country</t>
+          <t>a live profile cannot be emptied by a save: 409 with the missing list, nothing changed</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -4687,17 +4687,17 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>Public provider data</t>
+          <t>Provider profile</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>provider-public.int.spec.ts</t>
+          <t>provider-profile.int.spec.ts</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>a published provider page: contract shape, place, photo urls, only offerable services</t>
+          <t>a provider whose names are missing cannot publish: missing lists name</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -4714,17 +4714,17 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>Public provider data</t>
+          <t>Provider profile</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>provider-public.int.spec.ts</t>
+          <t>provider-profile.int.spec.ts</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>404 when not visible: unknown, draft, or no offerable service</t>
+          <t>the draft's postcode lookup uses the owner's stored country</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>a draft page is a 404 for its own owner too</t>
+          <t>a published provider page: contract shape, place, photo urls, only offerable services</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>unknown language is 400</t>
+          <t>404 when not visible: unknown, draft, or no offerable service</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>anonymous: the page carries the owner's profile photo and the public name, no display name</t>
+          <t>a draft page is a 404 for its own owner too</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -4822,17 +4822,17 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>Translate endpoint</t>
+          <t>Public provider data</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>provider-translation.int.spec.ts</t>
+          <t>provider-public.int.spec.ts</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>returns translated texts in the page shape</t>
+          <t>unknown language is 400</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -4849,17 +4849,17 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>Translate endpoint</t>
+          <t>Public provider data</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>provider-translation.int.spec.ts</t>
+          <t>provider-public.int.spec.ts</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>a draft or suspended provider -&gt; 404, no call</t>
+          <t>anonymous: the page carries the owner's profile photo and the public name, no display name</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>unknown lang -&gt; 400</t>
+          <t>returns translated texts in the page shape</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>service failure -&gt; 503 and nothing stored</t>
+          <t>a draft or suspended provider -&gt; 404, no call</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>a logged-in caller is counted under the user id</t>
+          <t>unknown lang -&gt; 400</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>the provider endpoint reports translatable per viewer language</t>
+          <t>service failure -&gt; 503 and nothing stored</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>accepts no text from the client</t>
+          <t>a logged-in caller is counted under the user id</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>fails closed without a usable secret: 503, no counter row, no model call</t>
+          <t>the provider endpoint reports translatable per viewer language</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -5038,17 +5038,17 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>Site and admin routing</t>
+          <t>Translate endpoint</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>proxy.int.spec.ts</t>
+          <t>provider-translation.int.spec.ts</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>/admin and below go through the auth middleware</t>
+          <t>accepts no text from the client</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
@@ -5065,17 +5065,17 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>Site and admin routing</t>
+          <t>Translate endpoint</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>proxy.int.spec.ts</t>
+          <t>provider-translation.int.spec.ts</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>/administrator or a page slug starting with admin is a site path with x-lang</t>
+          <t>fails closed without a usable secret: 503, no counter row, no model call</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -5092,17 +5092,17 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>Public name</t>
+          <t>Site and admin routing</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>public-name.int.spec.ts</t>
+          <t>proxy.int.spec.ts</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>publicNameFor: business name, else first name and surname initial</t>
+          <t>/admin and below go through the auth middleware</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -5119,17 +5119,17 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>Public name</t>
+          <t>Site and admin routing</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>public-name.int.spec.ts</t>
+          <t>proxy.int.spec.ts</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>slugify transliterates umlauts and strips the rest</t>
+          <t>/administrator or a page slug starting with admin is a site path with x-lang</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>public name and slug are unique and stable</t>
+          <t>publicNameFor: business name, else first name and surname initial</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>an individual without names cannot publish; with names the public name follows</t>
+          <t>slugify transliterates umlauts and strips the rest</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>first contact does not copy the session name: the person sets their own names</t>
+          <t>public name and slug are unique and stable</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>a rename of the person changes the public name of their provider profile</t>
+          <t>an individual without names cannot publish; with names the public name follows</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -5254,17 +5254,17 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>Publish and unpublish</t>
+          <t>Public name</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>publish-flow.int.spec.ts</t>
+          <t>public-name.int.spec.ts</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>the first-time flow: refused until photo and service exist, then published, then unpublished</t>
+          <t>first contact does not copy the session name: the person sets their own names</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -5281,17 +5281,17 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>Publish and unpublish</t>
+          <t>Public name</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>publish-flow.int.spec.ts</t>
+          <t>public-name.int.spec.ts</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>a postcode-less profile is refused until a postcode is saved</t>
+          <t>a rename of the person changes the public name of their provider profile</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>a suspended profile cannot publish (409)</t>
+          <t>the first-time flow: refused until photo and service exist, then published, then unpublished</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>RLS: published and not suspended is public, drafts and suspended are not</t>
+          <t>a postcode-less profile is refused until a postcode is saved</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>RLS: another user cannot change or add to a provider; domain-only columns are closed</t>
+          <t>a suspended profile cannot publish (409)</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>RLS: set_provider_* touch only the caller's own profile</t>
+          <t>RLS: published and not suspended is public, drafts and suspended are not</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>RLS: documents are private and the verdict is staff-only</t>
+          <t>RLS: another user cannot change or add to a provider; domain-only columns are closed</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>offerableServiceIds: services whose required documents are all approved</t>
+          <t>RLS: set_provider_* touch only the caller's own profile</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>a user suspension that has ended no longer blocks publishing; a running one does</t>
+          <t>RLS: documents are private and the verdict is staff-only</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
@@ -5497,17 +5497,17 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>Staff check</t>
+          <t>Publish and unpublish</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>require-staff.int.spec.ts</t>
+          <t>publish-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>an active admin passes</t>
+          <t>offerableServiceIds: services whose required documents are all approved</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -5524,17 +5524,17 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>Staff check</t>
+          <t>Publish and unpublish</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>require-staff.int.spec.ts</t>
+          <t>publish-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>a suspended admin gets 403</t>
+          <t>a user suspension that has ended no longer blocks publishing; a running one does</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>an expired suspension no longer blocks</t>
+          <t>an active admin passes</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -5578,17 +5578,17 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>Row-level security</t>
+          <t>Staff check</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>rls-providers.int.spec.ts</t>
+          <t>require-staff.int.spec.ts</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>another user cannot update or delete a service or a reference (rowCount 0, rows unchanged)</t>
+          <t>a suspended admin gets 403</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
@@ -5605,17 +5605,17 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>Row-level security</t>
+          <t>Staff check</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>rls-providers.int.spec.ts</t>
+          <t>require-staff.int.spec.ts</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>another user cannot insert a service or a reference for my provider</t>
+          <t>an expired suspension no longer blocks</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>the owner cannot move a service to another provider</t>
+          <t>another user cannot update or delete a service or a reference (rowCount 0, rows unchanged)</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>offerableServiceIds and missingRequirements are identical through tx and the owner db</t>
+          <t>another user cannot insert a service or a reference for my provider</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>a stranger asking about a draft provider gets empty answers; the owner still gets the full ones</t>
+          <t>the owner cannot move a service to another provider</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>a service with a category alone (no price type yet) is never offerable, not even to its owner</t>
+          <t>offerableServiceIds and missingRequirements are identical through tx and the owner db</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>slugify strips accents</t>
+          <t>a stranger asking about a draft provider gets empty answers; the owner still gets the full ones</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>rls.int.spec.ts</t>
+          <t>rls-providers.int.spec.ts</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>app_user cannot read a private table row of another user</t>
+          <t>a service with a category alone (no price type yet) is never offerable, not even to its owner</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>rls.int.spec.ts</t>
+          <t>rls-providers.int.spec.ts</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>public reference tables are readable by app_user and not writable</t>
+          <t>slugify strips accents</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>a person's picture is private until the owner's provider is published and not suspended</t>
+          <t>app_user cannot read a private table row of another user</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>notifications: the owner reads and marks own rows; another user sees none, cannot insert or change kind</t>
+          <t>public reference tables are readable by app_user and not writable</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
@@ -5875,17 +5875,17 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Row-level security</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>search.int.spec.ts</t>
+          <t>rls.int.spec.ts</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>radius edge and remote providers</t>
+          <t>a person's picture is private until the owner's provider is published and not suspended</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
@@ -5902,17 +5902,17 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Row-level security</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>search.int.spec.ts</t>
+          <t>rls.int.spec.ts</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>a remote provider more than 200 km away is found, without a distance</t>
+          <t>notifications: the owner reads and marks own rows; another user sees none, cannot insert or change kind</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>a draft is invisible to its owner too</t>
+          <t>radius edge and remote providers</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>distance is whole km, at least 1, hidden for remote providers outside the radius</t>
+          <t>a remote provider more than 200 km away is found, without a distance</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>a draft, a suspended or a provider without an offerable service never appears</t>
+          <t>a draft is invisible to its owner too</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>category filter and q (public name and skills, case-insensitive)</t>
+          <t>distance is whole km, at least 1, hidden for remote providers outside the radius</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>bad input is 400: unknown postcode, bad format, unknown country, unknown language, bad page</t>
+          <t>a draft, a suspended or a provider without an offerable service never appears</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>paging: 20 per page and hasMore</t>
+          <t>category filter and q (public name and skills, case-insensitive)</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>anonymous: the card carries the owner's profile photo and the public name, no display name</t>
+          <t>bad input is 400: unknown postcode, bad format, unknown country, unknown language, bad page</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>a provider whose only service has no price type is neither found nor has a public page</t>
+          <t>paging: 20 per page and hasMore</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>a fixed service without a price is not found in its category</t>
+          <t>anonymous: the card carries the owner's profile photo and the public name, no display name</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
@@ -6172,17 +6172,17 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>search.int.spec.ts</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>categories seed is idempotent: 14 categories, both names, babysitting needs a police certificate</t>
+          <t>a provider whose only service has no price type is neither found nor has a public page</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
@@ -6199,17 +6199,17 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>search.int.spec.ts</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>postcode import upserts: a second run leaves the same count</t>
+          <t>a fixed service without a price is not found in its category</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>the dev guard needs the dev branch AND the dev database host</t>
+          <t>categories seed is idempotent: 14 categories, both names, babysitting needs a police certificate</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>loadSeedData reads the git-ignored list or the committed example, and rejects a broken file</t>
+          <t>postcode import upserts: a second run leaves the same count</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>seedTestUsers itself refuses outside dev, before touching anything</t>
+          <t>the dev guard needs the dev branch AND the dev database host</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>builds the test users through the domain: published providers with photo, services, public names, verified; a rerun adds nothing</t>
+          <t>loadSeedData reads the git-ignored list or the committed example, and rejects a broken file</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>a run that crashed after the services (no photo, not published) resumes without adding the services twice</t>
+          <t>seedTestUsers itself refuses outside dev, before touching anything</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>placeholder photos: gives a published profile without a photo one; elsewhere needs the typed yes</t>
+          <t>builds the test users through the domain: published providers with photo, services, public names, verified; a rerun adds nothing</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>neonAuth retries a 429, then succeeds</t>
+          <t>a run that crashed after the services (no photo, not published) resumes without adding the services twice</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>neonAuth signs in when the email already exists</t>
+          <t>placeholder photos: gives a published profile without a photo one; elsewhere needs the typed yes</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>neonAuth surfaces any other sign-up failure without falling back to sign-in</t>
+          <t>neonAuth retries a 429, then succeeds</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
@@ -6469,17 +6469,17 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>Services and references</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>services-references.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>a service needs a profile first (409)</t>
+          <t>neonAuth signs in when the email already exists</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
@@ -6496,17 +6496,17 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>Services and references</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>services-references.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>create, list and patch a service; shapes fit the contract</t>
+          <t>neonAuth surfaces any other sign-up failure without falling back to sign-in</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>on-request has no price, even when one is sent</t>
+          <t>a service needs a profile first (409)</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>bad service input: no price, three decimals, unknown category are 400</t>
+          <t>create, list and patch a service; shapes fit the contract</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>a service in a category with required documents waits for approval</t>
+          <t>on-request has no price, even when one is sent</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>user A cannot edit or delete user B's service</t>
+          <t>bad service input: no price, three decimals, unknown category are 400</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>references are capped at 2 (409), can be patched and deleted</t>
+          <t>a service in a category with required documents waits for approval</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>a service with a category alone is saved, not offerable, and a patch accepts the partial shape</t>
+          <t>user A cannot edit or delete user B's service</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>the price type and the price save in either order, each as its own one-field save</t>
+          <t>references are capped at 2 (409), can be patched and deleted</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>a fixed service without a price is not offerable, with a price it is; on-request clears the price</t>
+          <t>a service with a category alone is saved, not offerable, and a patch accepts the partial shape</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>the app sends a category alone, then one field per save: currency defaults to EUR, title to the category name</t>
+          <t>the price type and the price save in either order, each as its own one-field save</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>add and update answer with waitingFor and visibleInSearch, like the list</t>
+          <t>a fixed service without a price is not offerable, with a price it is; on-request clears the price</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
@@ -6793,17 +6793,17 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>Sitemaps</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>sitemaps.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>providers sitemap lists only visible providers</t>
+          <t>the app sends a category alone, then one field per save: currency defaults to EUR, title to the category name</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
@@ -6820,17 +6820,17 @@
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>Sitemaps</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>sitemaps.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>pages sitemap lists the home page and published pages only</t>
+          <t>add and update answer with waitingFor and visibleInSearch, like the list</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>robots.txt allows the site, keeps the admin out and points at both sitemaps</t>
+          <t>providers sitemap lists only visible providers</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
@@ -6874,17 +6874,17 @@
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>Smoke test</t>
+          <t>Sitemaps</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>smoke.int.spec.ts</t>
+          <t>sitemaps.int.spec.ts</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>connects to the test database and sees PostGIS</t>
+          <t>pages sitemap lists the home page and published pages only</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
@@ -6901,17 +6901,17 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>Test database guard</t>
+          <t>Sitemaps</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>test-guard.int.spec.ts</t>
+          <t>sitemaps.int.spec.ts</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>the test guard refuses a non-local or non-test URL</t>
+          <t>robots.txt allows the site, keeps the admin out and points at both sitemaps</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
@@ -6928,17 +6928,17 @@
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Smoke test</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>smoke.int.spec.ts</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>translate stores translations and serves the second request from the store without a call</t>
+          <t>connects to the test database and sees PostGIS</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
@@ -6955,17 +6955,17 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Test database guard</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>test-guard.int.spec.ts</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>translate an edited text is re-translated, the rest comes from the store</t>
+          <t>the test guard refuses a non-local or non-test URL</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>translate texts already in the target language are returned unchanged without a call</t>
+          <t>translate stores translations and serves the second request from the store without a call</t>
         </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>translate a malformed or incomplete model answer stores nothing and throws TranslationUnavailable</t>
+          <t>translate an edited text is re-translated, the rest comes from the store</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>translate a non-2xx answer throws TranslationUnavailable</t>
+          <t>translate texts already in the target language are returned unchanged without a call</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>translate line breaks survive</t>
+          <t>translate a malformed or incomplete model answer stores nothing and throws TranslationUnavailable</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>translate no key -&gt; TranslationUnavailable without a call</t>
+          <t>translate a non-2xx answer throws TranslationUnavailable</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>translate the 31st AI call within an hour for one client key -&gt; TranslationUnavailable</t>
+          <t>translate line breaks survive</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>translate the limit boundary: the 30th call passes, the 31st is refused</t>
+          <t>translate no key -&gt; TranslationUnavailable without a call</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>translate a timeout -&gt; TranslationUnavailable</t>
+          <t>translate the 31st AI call within an hour for one client key -&gt; TranslationUnavailable</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>translate concurrent translations of the same page store one row per text</t>
+          <t>translate the limit boundary: the 30th call passes, the 31st is refused</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>translate writes through the request transaction and commits with it</t>
+          <t>translate a timeout -&gt; TranslationUnavailable</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>translate the default timeout is 12 seconds</t>
+          <t>translate concurrent translations of the same page store one row per text</t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>translate French and Afrikaans texts are flagged and sent to the model, in either viewer language</t>
+          <t>translate writes through the request transaction and commits with it</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>translate a page the detector cannot classify is translated when long enough, left alone when short</t>
+          <t>translate the default timeout is 12 seconds</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>translate a German profile of short skills and titles needs no translation for de but does for en</t>
+          <t>translate French and Afrikaans texts are flagged and sent to the model, in either viewer language</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>translate a Markdown-fenced answer parses; the request carries max_tokens</t>
+          <t>translate a page the detector cannot classify is translated when long enough, left alone when short</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>translate an empty string from the model stores nothing</t>
+          <t>translate a German profile of short skills and titles needs no translation for de but does for en</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>translate counter rows older than 24 hours are deleted; recent ones stay</t>
+          <t>translate a Markdown-fenced answer parses; the request carries max_tokens</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>translate anonymous client keys are salted hashes, never the raw IP</t>
+          <t>translate an empty string from the model stores nothing</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>translate textsOf picks the translatable fields of a profile</t>
+          <t>translate counter rows older than 24 hours are deleted; recent ones stay</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>translate needsTranslation is false for a page entirely in the viewer language and true for a mixed page</t>
+          <t>translate anonymous client keys are salted hashes, never the raw IP</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>translation tables are insert-only for app_user anonymous callers can insert and read, never update or delete</t>
+          <t>translate textsOf picks the translatable fields of a profile</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
@@ -7549,22 +7549,22 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>server errors land on the right field</t>
+          <t>translate needsTranslation is false for a page entirely in the viewer language and true for a mixed page</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr">
@@ -7576,22 +7576,22 @@
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>withItem adds a trimmed new skill or strength once and ignores blanks</t>
+          <t>translation tables are insert-only for app_user anonymous callers can insert and read, never update or delete</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E260" s="4" t="inlineStr">
@@ -7603,17 +7603,17 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>the form-level error shows unless every server error has an inline slot</t>
+          <t>creates the draft, reloads /me, then opens the profile page, in that order</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
@@ -7630,17 +7630,17 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>service and reference validation</t>
+          <t>welcome passes through to the page</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
@@ -7657,17 +7657,17 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>every missing item the publish route can return has de and en text</t>
+          <t>a failure returns the error text and does not navigate</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -7684,17 +7684,17 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>the service body names the category by id and the currency, as the server expects</t>
+          <t>a second call while one runs does nothing extra</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>a 400 "Invalid input" marks each named field</t>
+          <t>texts come from the shared catalogue, in the chosen language, with placeholders filled</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>live means published and not suspended now (the server rule of listServices)</t>
+          <t>the translate button texts exist in both languages</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
@@ -7765,17 +7765,17 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>Share profile</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>share-profile.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>the provider page url carries the language only when it is not the default</t>
+          <t>errorText maps the auth server codes to catalogue messages</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
@@ -7792,17 +7792,17 @@
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>Share profile</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>share-profile.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>shareProfile passes the url and the text in the given language</t>
+          <t>errorText maps the app API strings</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
@@ -7819,17 +7819,17 @@
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>Address fields</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>address-fields.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>toAddress: empty is null (clears), complete is DE, partial is undefined</t>
+          <t>docText maps known document codes and passes unknown ones through</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
@@ -7846,17 +7846,17 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Share profile</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>share-profile.test.ts</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>texts come from the shared catalogue, in the chosen language, with placeholders filled</t>
+          <t>the provider page url carries the language only when it is not the default</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
@@ -7873,17 +7873,17 @@
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Share profile</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>share-profile.test.ts</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>the translate button texts exist in both languages</t>
+          <t>shareProfile passes the url and the text in the given language</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
@@ -7900,17 +7900,17 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Address fields</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>address-fields.test.ts</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>errorText maps the auth server codes to catalogue messages</t>
+          <t>toAddress: empty is null (clears), a postcode alone is enough, street or city without postcode is undefined</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>errorText maps the app API strings</t>
+          <t>signUp posts email, password and name and stores the session cookie</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>docText maps known document codes and passes unknown ones through</t>
+          <t>signIn posts email and password and returns the user</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>prices follow the website rules in German and English</t>
+          <t>a refused sign-in throws the server code, which maps to a catalogue message</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>distance shows km, remote or nothing</t>
+          <t>signOut forgets the session at once and tells the server with the old cookie</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>search path leaves out empty filters and trims text</t>
+          <t>signOut offline still signs out</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>photoSrc loads only absolute http(s) URLs, never a server-relative /api path</t>
+          <t>session reads get-session with the cookie; no cookie means null without a request</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>signUp posts email, password and name and stores the session cookie</t>
+          <t>session throws on a network error (the app offers a retry, not the login)</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>signIn posts email and password and returns the user</t>
+          <t>sendVerificationCode asks for an email-verification code</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>a refused sign-in throws the server code, which maps to a catalogue message</t>
+          <t>verifyEmail sends the code as otp, stores the new session and returns the user</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>signOut forgets the session at once and tells the server with the old cookie</t>
+          <t>requestPasswordReset asks for a reset code</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>signOut offline still signs out</t>
+          <t>resetPassword sends email, code and the new password</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>session reads get-session with the cookie; no cookie means null without a request</t>
+          <t>a wrong code throws INVALID_OTP, shown as the code message</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>session throws on a network error (the app offers a retry, not the login)</t>
+          <t>signUp and signIn start without an old stored session</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>sendVerificationCode asks for an email-verification code</t>
+          <t>preparePhoto keeps the long side at 1600 px</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>verifyEmail sends the code as otp, stores the new session and returns the user</t>
+          <t>tooLarge is true above 4_434_464 bytes</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>requestPasswordReset asks for a reset code</t>
+          <t>pickPhoto cancelled is null</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
@@ -8364,12 +8364,12 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>resetPassword sends email, code and the new password</t>
+          <t>pickPhoto a refused permission is denied, not cancelled</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>a wrong code throws INVALID_OTP, shown as the code message</t>
+          <t>pickDocument offers PDFs and the image types the server accepts, from any file source</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>signUp and signIn start without an old stored session</t>
+          <t>pickDocument cancelled is null</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>a failed check after the upload deletes the uploaded file and reports the original error</t>
+          <t>server errors land on the right field</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
@@ -8472,12 +8472,12 @@
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>a successful submit deletes nothing</t>
+          <t>withItem adds a trimmed new skill or strength once and ignores blanks</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
@@ -8499,12 +8499,12 @@
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>a failing clean-up does not hide the original error</t>
+          <t>the form-level error shows unless every server error has an inline slot</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>preparePhoto keeps the long side at 1600 px</t>
+          <t>service and reference validation</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>tooLarge is true above 4_434_464 bytes</t>
+          <t>every missing item the publish route can return has de and en text</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>pickPhoto cancelled is null</t>
+          <t>the service body names the category by id and the currency, as the server expects</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>pickPhoto a refused permission is denied, not cancelled</t>
+          <t>a 400 "Invalid input" marks each named field</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
@@ -8634,12 +8634,12 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>pickDocument offers PDFs and the image types the server accepts, from any file source</t>
+          <t>live means published and not suspended now (the server rule of listServices)</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>pickDocument cancelled is null</t>
+          <t>sends the stored cookie and stores a new set-cookie</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
@@ -8683,17 +8683,17 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>Pending signup</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>pending-signup.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>the pending record round-trips and clears</t>
+          <t>a single joined set-cookie header (no getSetCookie) is split into its cookies</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -8715,12 +8715,12 @@
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>applyTexts swaps only the translatable fields and keeps names, prices and photos</t>
+          <t>clears the session on 401</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>applyTexts matches services and references by id and leaves unknown ones untouched</t>
+          <t>a 401 without a stored session does not call onUnauthorized</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>applyTexts keeps line breaks</t>
+          <t>every request names the app origin and leaves the platform cookie store out</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>sends the stored cookie and stores a new set-cookie</t>
+          <t>a 409 with error and missing throws ApiError with code and missing</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>a single joined set-cookie header (no getSetCookie) is split into its cookies</t>
+          <t>a 400 "Invalid input" lists the fields named by its issues</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>clears the session on 401</t>
+          <t>a network failure throws ApiError(0, network)</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>a 401 without a stored session does not call onUnauthorized</t>
+          <t>a server that never answers fails as network after the time limit</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>every request names the app origin and leaves the platform cookie store out</t>
+          <t>saves have no time limit: a slow save that succeeds is not reported as a failure</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>a 409 with error and missing throws ApiError with code and missing</t>
+          <t>updateMe PATCHes the account name</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>a 400 "Invalid input" lists the fields named by its issues</t>
+          <t>upload sends multipart with the cookie and no time limit</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>a network failure throws ApiError(0, network)</t>
+          <t>upload sends the file bytes with its name and type, not a bare { uri } object</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>a server that never answers fails as network after the time limit</t>
+          <t>a file the phone cannot open is "File unreadable", not a network error, and nothing is sent</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>saves have no time limit: a slow save that succeeds is not reported as a failure</t>
+          <t>upload maps a 413 to ApiError "File too large"</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>updateMe PATCHes the account name</t>
+          <t>upload maps a network failure to ApiError network and does not retry</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>upload sends multipart with the cookie and no time limit</t>
+          <t>a store that cannot be read (Keystore failure) sends the request without a cookie</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>upload sends the file bytes with its name and type, not a bare { uri } object</t>
+          <t>a cookie that cannot be saved does not fail a request the server already carried out</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>a file the phone cannot open is "File unreadable", not a network error, and nothing is sent</t>
+          <t>a malformed Set-Cookie line without "=" is skipped</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>upload maps a 413 to ApiError "File too large"</t>
+          <t>updateMe sends the one-field name as first and last name, split at the last space</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>upload maps a network failure to ApiError network and does not retry</t>
+          <t>prices follow the website rules in German and English</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>a store that cannot be read (Keystore failure) sends the request without a cookie</t>
+          <t>distance shows km, remote or nothing</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>a cookie that cannot be saved does not fail a request the server already carried out</t>
+          <t>search path leaves out empty filters and trims text</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
@@ -9282,12 +9282,12 @@
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>a malformed Set-Cookie line without "=" is skipped</t>
+          <t>photoSrc loads only absolute http(s) URLs, never a server-relative /api path</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>updateMe sends the one-field name as first and last name, split at the last space</t>
+          <t>a failed check after the upload deletes the uploaded file and reports the original error</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
@@ -9336,12 +9336,12 @@
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>loading -&gt; signed in -&gt; signed out</t>
+          <t>a successful submit deletes nothing</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>an unverified email never counts as signed in: sign-in sends a code and asks for it</t>
+          <t>a failing clean-up does not hide the original error</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth-layout.test.ts</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>a server that refuses unverified sign-ins (EMAIL_NOT_VERIFIED) also leads to the code screen</t>
+          <t>logged-out landing route is login</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -9417,12 +9417,12 @@
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth-layout.test.ts</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>sign-up creates the account and sends the code; the right code signs in and saves the account name</t>
+          <t>no test files inside src/app (each file there becomes a screen)</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
@@ -9439,17 +9439,17 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Serial create</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>serial-create.test.ts</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>a wrong code throws and keeps signed out</t>
+          <t>choosing twice before the create returns creates once, then updates</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -9466,17 +9466,17 @@
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Serial create</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>serial-create.test.ts</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>a failed login rejects and keeps signed out; a server error on load means signed out</t>
+          <t>an existing id is only updated</t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
@@ -9493,17 +9493,17 @@
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>a network error on load sets offline (not signed out); retry recovers</t>
+          <t>two quick changes become one request with the last value</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
@@ -9520,17 +9520,17 @@
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>onUnauthorized from the API client signs the user out</t>
+          <t>flush saves immediately and nothing is sent twice</t>
         </is>
       </c>
       <c r="D332" s="4" t="inlineStr">
@@ -9547,17 +9547,17 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>switching the language also saves it for emails, but only while signed in</t>
+          <t>a rejected save marks error and retry resends the same value</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
@@ -9574,17 +9574,17 @@
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>verify finishes the sign-up: names and address, then the picture, then the record is cleared; returns the tick</t>
+          <t>a change typed while a save is in flight is sent after it, in order</t>
         </is>
       </c>
       <c r="D334" s="4" t="inlineStr">
@@ -9601,17 +9601,17 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>a failed upload keeps the record; loadSession retries it once and clears it</t>
+          <t>dispose sends a pending change so nothing typed is lost</t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>loadSession without a record or while signed out does not finish a sign-up</t>
+          <t>loading -&gt; signed in -&gt; signed out</t>
         </is>
       </c>
       <c r="D336" s="4" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>a record for another email is dropped and applies nothing</t>
+          <t>an unverified email never counts as signed in: sign-in sends a code and asks for it</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="C338" s="4" t="inlineStr">
         <is>
-          <t>a failed PATCH keeps the full record</t>
+          <t>a server that refuses unverified sign-ins (EMAIL_NOT_VERIFIED) also leads to the code screen</t>
         </is>
       </c>
       <c r="D338" s="4" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>after the PATCH succeeded, a failed upload keeps only email, tick and picture; the retry does not PATCH again</t>
+          <t>sign-up creates the account and sends the code; the right code signs in and saves the account name</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C340" s="4" t="inlineStr">
         <is>
-          <t>a picture whose cached file is gone is dropped and the record cleared</t>
+          <t>a wrong code throws and keeps signed out</t>
         </is>
       </c>
       <c r="D340" s="4" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>sign-up keeps the record for the code step; a failed sign-up leaves none</t>
+          <t>a failed login rejects and keeps signed out; a server error on load means signed out</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>finishing a sign-up reloads /me so the home nudge sees the new picture; nothing to finish, nothing to reload</t>
+          <t>a network error on load sets offline (not signed out); retry recovers</t>
         </is>
       </c>
       <c r="D342" s="4" t="inlineStr">
@@ -9817,17 +9817,17 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>Picture nudge</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>picture-nudge.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>the dismissed-nudge key is per user, so a second account on the device still sees it</t>
+          <t>onUnauthorized from the API client signs the user out</t>
         </is>
       </c>
       <c r="D343" s="4" t="inlineStr">
@@ -9844,17 +9844,17 @@
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B344" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>two quick changes become one request with the last value</t>
+          <t>switching the language also saves it for emails, but only while signed in</t>
         </is>
       </c>
       <c r="D344" s="4" t="inlineStr">
@@ -9871,17 +9871,17 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C345" s="4" t="inlineStr">
         <is>
-          <t>flush saves immediately and nothing is sent twice</t>
+          <t>verify finishes the sign-up: names and address, then the picture, then the record is cleared; returns the tick</t>
         </is>
       </c>
       <c r="D345" s="4" t="inlineStr">
@@ -9898,17 +9898,17 @@
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B346" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C346" s="4" t="inlineStr">
         <is>
-          <t>a rejected save marks error and retry resends the same value</t>
+          <t>a failed upload keeps the record; loadSession retries it once and clears it</t>
         </is>
       </c>
       <c r="D346" s="4" t="inlineStr">
@@ -9925,17 +9925,17 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>a change typed while a save is in flight is sent after it, in order</t>
+          <t>loadSession without a record or while signed out does not finish a sign-up</t>
         </is>
       </c>
       <c r="D347" s="4" t="inlineStr">
@@ -9952,17 +9952,17 @@
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B348" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C348" s="4" t="inlineStr">
         <is>
-          <t>dispose sends a pending change so nothing typed is lost</t>
+          <t>a record for another email is dropped and applies nothing</t>
         </is>
       </c>
       <c r="D348" s="4" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>match.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>matches ignores case and accents, and an empty query matches everything</t>
+          <t>a failed PATCH keeps the full record</t>
         </is>
       </c>
       <c r="D349" s="4" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="B350" s="4" t="inlineStr">
         <is>
-          <t>auth-layout.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C350" s="4" t="inlineStr">
         <is>
-          <t>logged-out landing route is login</t>
+          <t>after the PATCH succeeded, a failed upload keeps only email, tick and picture; the retry does not PATCH again</t>
         </is>
       </c>
       <c r="D350" s="4" t="inlineStr">
@@ -10038,12 +10038,12 @@
       </c>
       <c r="B351" s="4" t="inlineStr">
         <is>
-          <t>auth-layout.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C351" s="4" t="inlineStr">
         <is>
-          <t>no test files inside src/app (each file there becomes a screen)</t>
+          <t>a picture whose cached file is gone is dropped and the record cleared</t>
         </is>
       </c>
       <c r="D351" s="4" t="inlineStr">
@@ -10060,17 +10060,17 @@
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>Stale guard</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B352" s="4" t="inlineStr">
         <is>
-          <t>stale-guard.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C352" s="4" t="inlineStr">
         <is>
-          <t>a response older than one already applied is ignored</t>
+          <t>sign-up keeps the record for the code step; a failed sign-up leaves none</t>
         </is>
       </c>
       <c r="D352" s="4" t="inlineStr">
@@ -10087,17 +10087,17 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>Stale guard</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>stale-guard.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>answers arriving in order are all applied</t>
+          <t>finishing a sign-up reloads /me so the home nudge sees the new picture; nothing to finish, nothing to reload</t>
         </is>
       </c>
       <c r="D353" s="4" t="inlineStr">
@@ -10114,17 +10114,17 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>Serial create</t>
+          <t>Use flash</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>serial-create.test.ts</t>
+          <t>use-flash.test.ts</t>
         </is>
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>choosing twice before the create returns creates once, then updates</t>
+          <t>createFlash: on after show, off after the delay, off at once on hide, a second show restarts the delay</t>
         </is>
       </c>
       <c r="D354" s="4" t="inlineStr">
@@ -10141,17 +10141,17 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>Serial create</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>serial-create.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>an existing id is only updated</t>
+          <t>no rows when no service needs a document</t>
         </is>
       </c>
       <c r="D355" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>no rows when no service needs a document</t>
+          <t>a babysitting service with nothing uploaded â†’ police-certificate none</t>
         </is>
       </c>
       <c r="D356" s="4" t="inlineStr">
@@ -10205,7 +10205,7 @@
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>a babysitting service with nothing uploaded â†’ police-certificate none</t>
+          <t>the most recently reviewed check decides, like the server</t>
         </is>
       </c>
       <c r="D357" s="4" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="C358" s="4" t="inlineStr">
         <is>
-          <t>the most recently reviewed check decides, like the server</t>
+          <t>a pending check shows pending even after an approval</t>
         </is>
       </c>
       <c r="D358" s="4" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>a pending check shows pending even after an approval</t>
+          <t>a requirement code the app does not know still gets a row, after the known ones</t>
         </is>
       </c>
       <c r="D359" s="4" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>a requirement code the app does not know still gets a row, after the known ones</t>
+          <t>two services needing the same document give one row</t>
         </is>
       </c>
       <c r="D360" s="4" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>two services needing the same document give one row</t>
+          <t>two different categories needing the same document give one row with the latest status</t>
         </is>
       </c>
       <c r="D361" s="4" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>two different categories needing the same document give one row with the latest status</t>
+          <t>a hidden service says a document is needed until it is uploaded, then that it waits for the check</t>
         </is>
       </c>
       <c r="D362" s="4" t="inlineStr">
@@ -10367,7 +10367,7 @@
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>a hidden service says a document is needed until it is uploaded, then that it waits for the check</t>
+          <t>sharing is allowed only while no service waits for a document</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
@@ -10394,7 +10394,7 @@
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>sharing is allowed only while no service waits for a document</t>
+          <t>saving a waiting service keeps Share hidden: the server answer carries waitingFor</t>
         </is>
       </c>
       <c r="D364" s="4" t="inlineStr">
@@ -10411,17 +10411,17 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>profile-tab.test.ts</t>
         </is>
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>saving a waiting service keeps Share hidden: the server answer carries waitingFor</t>
+          <t>the My profile tab shows only for a known provider</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr">
@@ -10438,17 +10438,17 @@
     <row r="366">
       <c r="A366" s="4" t="inlineStr">
         <is>
-          <t>Use me</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="B366" s="4" t="inlineStr">
         <is>
-          <t>use-me.test.ts</t>
+          <t>profile-tab.test.ts</t>
         </is>
       </c>
       <c r="C366" s="4" t="inlineStr">
         <is>
-          <t>a loadMe in flight at sign-out never fills the store for the next account</t>
+          <t>after sign-out the next account does not inherit the provider tab</t>
         </is>
       </c>
       <c r="D366" s="4" t="inlineStr">
@@ -10465,22 +10465,22 @@
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Picture nudge</t>
         </is>
       </c>
       <c r="B367" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>picture-nudge.test.ts</t>
         </is>
       </c>
       <c r="C367" s="4" t="inlineStr">
         <is>
-          <t>ServiceInputSchema rejects three decimals and negative prices</t>
+          <t>the dismissed-nudge key is per user, so a second account on the device still sees it</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E367" s="4" t="inlineStr">
@@ -10492,22 +10492,22 @@
     <row r="368">
       <c r="A368" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B368" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C368" s="4" t="inlineStr">
         <is>
-          <t>ServiceInputSchema needs no price on request</t>
+          <t>applyTexts swaps only the translatable fields and keeps names, prices and photos</t>
         </is>
       </c>
       <c r="D368" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E368" s="4" t="inlineStr">
@@ -10519,22 +10519,22 @@
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B369" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C369" s="4" t="inlineStr">
         <is>
-          <t>AdminListQuerySchema caps pageSize at 100</t>
+          <t>applyTexts matches services and references by id and leaves unknown ones untouched</t>
         </is>
       </c>
       <c r="D369" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E369" s="4" t="inlineStr">
@@ -10546,22 +10546,22 @@
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B370" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C370" s="4" t="inlineStr">
         <is>
-          <t>parse helpers parseBody answers 400 with the issues</t>
+          <t>applyTexts keeps line breaks</t>
         </is>
       </c>
       <c r="D370" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E370" s="4" t="inlineStr">
@@ -10573,22 +10573,22 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>match.test.ts</t>
         </is>
       </c>
       <c r="C371" s="4" t="inlineStr">
         <is>
-          <t>parse helpers parseQuery reads the search params</t>
+          <t>matches ignores case and accents, and an empty query matches everything</t>
         </is>
       </c>
       <c r="D371" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E371" s="4" t="inlineStr">
@@ -10600,22 +10600,22 @@
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Pending signup</t>
         </is>
       </c>
       <c r="B372" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>pending-signup.test.ts</t>
         </is>
       </c>
       <c r="C372" s="4" t="inlineStr">
         <is>
-          <t>list envelopes lists are { docs: [...] }</t>
+          <t>the pending record round-trips and clears</t>
         </is>
       </c>
       <c r="D372" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E372" s="4" t="inlineStr">
@@ -10627,22 +10627,22 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Use me</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>use-me.test.ts</t>
         </is>
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>list envelopes reference year is checked against the current year at parse time</t>
+          <t>a loadMe in flight at sign-out never fills the store for the next account</t>
         </is>
       </c>
       <c r="D373" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E373" s="4" t="inlineStr">
@@ -10654,22 +10654,22 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Stale guard</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>stale-guard.test.ts</t>
         </is>
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>address street, postcode and city are required (no empty or blank parts)</t>
+          <t>a response older than one already applied is ignored</t>
         </is>
       </c>
       <c r="D374" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E374" s="4" t="inlineStr">
@@ -10681,22 +10681,22 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Stale guard</t>
         </is>
       </c>
       <c r="B375" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>stale-guard.test.ts</t>
         </is>
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>service input as the app sends it a category alone is valid (the server fills currency and title)</t>
+          <t>answers arriving in order are all applied</t>
         </is>
       </c>
       <c r="D375" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E375" s="4" t="inlineStr">
@@ -10708,7 +10708,7 @@
     <row r="376">
       <c r="A376" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B376" s="4" t="inlineStr">
@@ -10718,7 +10718,7 @@
       </c>
       <c r="C376" s="4" t="inlineStr">
         <is>
-          <t>catalogue de and en have the same keys</t>
+          <t>ServiceInputSchema rejects three decimals and negative prices</t>
         </is>
       </c>
       <c r="D376" s="4" t="inlineStr">
@@ -10735,7 +10735,7 @@
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B377" s="4" t="inlineStr">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>catalogue no text is empty and no two keys of one namespace carry the same text</t>
+          <t>ServiceInputSchema needs no price on request</t>
         </is>
       </c>
       <c r="D377" s="4" t="inlineStr">
@@ -10762,7 +10762,7 @@
     <row r="378">
       <c r="A378" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B378" s="4" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
-          <t>catalogue no text contains Treuhand, Escrow, garantiert or a competitor name</t>
+          <t>AdminListQuerySchema caps pageSize at 100</t>
         </is>
       </c>
       <c r="D378" s="4" t="inlineStr">
@@ -10789,7 +10789,7 @@
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B379" s="4" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>catalogue the product name is only written in brand.name</t>
+          <t>parse helpers parseBody answers 400 with the issues</t>
         </is>
       </c>
       <c r="D379" s="4" t="inlineStr">
@@ -10816,7 +10816,7 @@
     <row r="380">
       <c r="A380" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B380" s="4" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="C380" s="4" t="inlineStr">
         <is>
-          <t>t replaces placeholders and falls back to the key when missing</t>
+          <t>parse helpers parseQuery reads the search params</t>
         </is>
       </c>
       <c r="D380" s="4" t="inlineStr">
@@ -10843,7 +10843,7 @@
     <row r="381">
       <c r="A381" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B381" s="4" t="inlineStr">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="C381" s="4" t="inlineStr">
         <is>
-          <t>t fills the brand name without a parameter</t>
+          <t>list envelopes lists are { docs: [...] }</t>
         </is>
       </c>
       <c r="D381" s="4" t="inlineStr">
@@ -10870,7 +10870,7 @@
     <row r="382">
       <c r="A382" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B382" s="4" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="C382" s="4" t="inlineStr">
         <is>
-          <t>t knows its languages</t>
+          <t>list envelopes reference year is checked against the current year at parse time</t>
         </is>
       </c>
       <c r="D382" s="4" t="inlineStr">
@@ -10897,7 +10897,7 @@
     <row r="383">
       <c r="A383" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B383" s="4" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>money formats per language</t>
+          <t>address only the postcode is required; blank street and city become null</t>
         </is>
       </c>
       <c r="D383" s="4" t="inlineStr">
@@ -10924,7 +10924,7 @@
     <row r="384">
       <c r="A384" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B384" s="4" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C384" s="4" t="inlineStr">
         <is>
-          <t>money formats price labels from the catalogue</t>
+          <t>service input as the app sends it a category alone is valid (the server fills currency and title)</t>
         </is>
       </c>
       <c r="D384" s="4" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>acceptLang en-GB,en;q=0.9,de;q=0.8 -&gt; en</t>
+          <t>catalogue de and en have the same keys</t>
         </is>
       </c>
       <c r="D385" s="4" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>acceptLang * -&gt; undefined</t>
+          <t>catalogue no text is empty and no two keys of one namespace carry the same text</t>
         </is>
       </c>
       <c r="D386" s="4" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>acceptLang fr-FR -&gt; undefined</t>
+          <t>catalogue no text contains Treuhand, Escrow, garantiert or a competitor name</t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>acceptLang  -&gt; undefined</t>
+          <t>catalogue the product name is only written in brand.name</t>
         </is>
       </c>
       <c r="D388" s="4" t="inlineStr">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>acceptLang undefined -&gt; undefined</t>
+          <t>t replaces placeholders and falls back to the key when missing</t>
         </is>
       </c>
       <c r="D389" s="4" t="inlineStr">
@@ -11086,22 +11086,22 @@
     <row r="390">
       <c r="A390" s="4" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Texts</t>
         </is>
       </c>
       <c r="B390" s="4" t="inlineStr">
         <is>
-          <t>profile-tab.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>the My profile tab shows only for a known provider</t>
+          <t>t fills the brand name without a parameter</t>
         </is>
       </c>
       <c r="D390" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Packages</t>
         </is>
       </c>
       <c r="E390" s="4" t="inlineStr">
@@ -11113,25 +11113,214 @@
     <row r="391">
       <c r="A391" s="4" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Texts</t>
         </is>
       </c>
       <c r="B391" s="4" t="inlineStr">
         <is>
-          <t>profile-tab.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C391" s="4" t="inlineStr">
         <is>
-          <t>after sign-out the next account does not inherit the provider tab</t>
+          <t>t knows its languages</t>
         </is>
       </c>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Packages</t>
         </is>
       </c>
       <c r="E391" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B392" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C392" s="4" t="inlineStr">
+        <is>
+          <t>money formats per language</t>
+        </is>
+      </c>
+      <c r="D392" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E392" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B393" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C393" s="4" t="inlineStr">
+        <is>
+          <t>money formats price labels from the catalogue</t>
+        </is>
+      </c>
+      <c r="D393" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E393" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B394" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C394" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang en-GB,en;q=0.9,de;q=0.8 -&gt; en</t>
+        </is>
+      </c>
+      <c r="D394" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E394" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B395" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C395" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang * -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D395" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E395" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B396" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C396" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang fr-FR -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D396" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E396" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B397" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C397" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang  -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D397" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E397" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B398" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C398" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang undefined -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D398" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E398" s="4" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
@@ -11148,7 +11337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -11197,7 +11386,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Run 27 October on registration-setup.</t>
+          <t>Run 27 October on account-address-saved.</t>
         </is>
       </c>
     </row>
@@ -11219,7 +11408,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Run 27 October.</t>
+          <t>Run 27 October on account-address-saved.</t>
         </is>
       </c>
     </row>
@@ -11241,7 +11430,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>35 files, 257 tests (the root run).</t>
+          <t>35 files, 259 tests (the root run).</t>
         </is>
       </c>
     </row>
@@ -11285,7 +11474,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>257 tests.</t>
+          <t>259 tests.</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11486,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>20 suites.</t>
+          <t>23 suites.</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -11307,7 +11496,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>110 tests.</t>
+          <t>115 tests.</t>
         </is>
       </c>
     </row>
@@ -11902,6 +12091,138 @@
       <c r="D34" s="4" t="inlineStr">
         <is>
           <t>services-references.int.spec.ts (a category alone, one field per save; add and update answer with waitingFor).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Address with only a postcode</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Contract: postcode alone valid, street without postcode invalid, blank street/city become null. Server: stored, returned by GET /me and the admin user page, null clears all four columns, street without postcode is 400.</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts; provider-profile.int.spec.ts; admin-api.int.spec.ts; apps/mobile address-fields.test.ts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Saved confirmation timing</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>The message turns on, off after 3 s, off at once on edit, and restarts on a second show.</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>apps/mobile use-flash.test.ts (fake timers). The screen wiring needs a phone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Offer services helper</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Creates the draft, reloads /me, then navigates; failure does not navigate; double tap runs once; welcome passes through.</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>apps/mobile start-offering.test.ts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Phone: Account Save shows "Saved"</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Saved appears under Save, vanishes after about 3 s or when you edit; a postcode-only address saves.</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Not yet done (phone)</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Phone: Offer services opens the profile page</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Account &gt; Offer services opens the setup page directly (no Home); My profile tab appears.</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Not yet done (phone)</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Phone: Become a provider card</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Card sits under the find-help button, opens the same page; a provider no longer sees the card.</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Not yet done (phone)</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Owner.</t>
         </is>
       </c>
     </row>
@@ -11916,7 +12237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -12740,6 +13061,57 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (owner phone test): address needs only a postcode</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Street and city optional (stored null); a street without a postcode is refused; an address never vanishes when the street is empty; sign-up and Account share one rule and text. Phone check: save a postcode-only address in Account and sign-up.</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Fixed; Not yet done (phone)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (owner phone test): Saved confirmation</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Account shows "Saved" / "Gespeichert" after a successful save, for about 3 s or until the next edit. Phone check: see it appear and go.</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Fixed; Not yet done (phone)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (owner phone test): Offer services and Become a provider</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Both create the draft, reload /me and open the profile page directly (they used to fall back to Home because the tab was hidden). The sign-up tick uses the same helper. Provider card moved under the find-help button, hidden for providers. Phone checks: Offer services opens the profile page directly; the card is under the find-help button and opens the same page; a provider no longer sees the card.</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Fixed; Not yet done (phone)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Reports/Registration-Setup-Test-Report.xlsx
+++ b/Reports/Registration-Setup-Test-Report.xlsx
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTA('Test Results'!C2:C398)</f>
+        <f>COUNTA('Test Results'!C2:C402)</f>
         <v/>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Test Results'!E2:E398,"Passed")</f>
+        <f>COUNTIF('Test Results'!E2:E402,"Passed")</f>
         <v/>
       </c>
     </row>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Test Results'!E2:E398,"Failed")</f>
+        <f>COUNTIF('Test Results'!E2:E402,"Failed")</f>
         <v/>
       </c>
     </row>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF('Test Results'!E2:E398,"Skipped")</f>
+        <f>COUNTIF('Test Results'!E2:E402,"Skipped")</f>
         <v/>
       </c>
     </row>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E398"/>
+  <dimension ref="A1:E402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7603,17 +7603,17 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>Start offering</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>start-offering.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>creates the draft, reloads /me, then opens the profile page, in that order</t>
+          <t>texts come from the shared catalogue, in the chosen language, with placeholders filled</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
@@ -7630,17 +7630,17 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>Start offering</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>start-offering.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>welcome passes through to the page</t>
+          <t>the translate button texts exist in both languages</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
@@ -7657,17 +7657,17 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>Start offering</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>start-offering.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>a failure returns the error text and does not navigate</t>
+          <t>errorText maps the auth server codes to catalogue messages</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -7684,17 +7684,17 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>Start offering</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>start-offering.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>a second call while one runs does nothing extra</t>
+          <t>errorText maps the app API strings</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>texts come from the shared catalogue, in the chosen language, with placeholders filled</t>
+          <t>docText maps known document codes and passes unknown ones through</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
@@ -7738,17 +7738,17 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Share profile</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>share-profile.test.ts</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>the translate button texts exist in both languages</t>
+          <t>the provider page url carries the language only when it is not the default</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
@@ -7765,17 +7765,17 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Share profile</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>share-profile.test.ts</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>errorText maps the auth server codes to catalogue messages</t>
+          <t>shareProfile passes the url and the text in the given language</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
@@ -7792,17 +7792,17 @@
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>errorText maps the app API strings</t>
+          <t>creates the draft, reloads /me, then sets the target, in that order</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
@@ -7819,17 +7819,17 @@
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>docText maps known document codes and passes unknown ones through</t>
+          <t>welcome passes through</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
@@ -7846,17 +7846,17 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>Share profile</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>share-profile.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>the provider page url carries the language only when it is not the default</t>
+          <t>a failure returns the error text and does not navigate</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
@@ -7873,17 +7873,17 @@
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>Share profile</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>share-profile.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>shareProfile passes the url and the text in the given language</t>
+          <t>a second call while one runs does nothing extra</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
@@ -8278,17 +8278,17 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Pending navigation</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>pending-navigation.test.ts</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>preparePhoto keeps the long side at 1600 px</t>
+          <t>set, consume once, then nothing</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
@@ -8305,17 +8305,17 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Pending navigation</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>pending-navigation.test.ts</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>tooLarge is true above 4_434_464 bytes</t>
+          <t>clearPending drops it (sign-out)</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
@@ -8332,17 +8332,17 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Pending navigation</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>pending-navigation.test.ts</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>pickPhoto cancelled is null</t>
+          <t>readyToNavigate: only with a target and a visible profile tab</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
@@ -8364,12 +8364,12 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>pickPhoto a refused permission is denied, not cancelled</t>
+          <t>server errors land on the right field</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>pickDocument offers PDFs and the image types the server accepts, from any file source</t>
+          <t>withItem adds a trimmed new skill or strength once and ignores blanks</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>pickDocument cancelled is null</t>
+          <t>the form-level error shows unless every server error has an inline slot</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -8450,7 +8450,7 @@
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>server errors land on the right field</t>
+          <t>service and reference validation</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>withItem adds a trimmed new skill or strength once and ignores blanks</t>
+          <t>every missing item the publish route can return has de and en text</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>the form-level error shows unless every server error has an inline slot</t>
+          <t>the service body names the category by id and the currency, as the server expects</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>service and reference validation</t>
+          <t>a 400 "Invalid input" marks each named field</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>every missing item the publish route can return has de and en text</t>
+          <t>live means published and not suspended now (the server rule of listServices)</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>the service body names the category by id and the currency, as the server expects</t>
+          <t>preparePhoto keeps the long side at 1600 px</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>a 400 "Invalid input" marks each named field</t>
+          <t>tooLarge is true above 4_434_464 bytes</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
@@ -8634,12 +8634,12 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>live means published and not suspended now (the server rule of listServices)</t>
+          <t>pickPhoto cancelled is null</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>sends the stored cookie and stores a new set-cookie</t>
+          <t>pickPhoto a refused permission is denied, not cancelled</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>a single joined set-cookie header (no getSetCookie) is split into its cookies</t>
+          <t>pickDocument offers PDFs and the image types the server accepts, from any file source</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -8715,12 +8715,12 @@
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>clears the session on 401</t>
+          <t>pickDocument cancelled is null</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>a 401 without a stored session does not call onUnauthorized</t>
+          <t>no rows when no service needs a document</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>every request names the app origin and leaves the platform cookie store out</t>
+          <t>a babysitting service with nothing uploaded â†’ police-certificate none</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
@@ -8796,12 +8796,12 @@
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>a 409 with error and missing throws ApiError with code and missing</t>
+          <t>the most recently reviewed check decides, like the server</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>a 400 "Invalid input" lists the fields named by its issues</t>
+          <t>a pending check shows pending even after an approval</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>a network failure throws ApiError(0, network)</t>
+          <t>a requirement code the app does not know still gets a row, after the known ones</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>a server that never answers fails as network after the time limit</t>
+          <t>two services needing the same document give one row</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>saves have no time limit: a slow save that succeeds is not reported as a failure</t>
+          <t>two different categories needing the same document give one row with the latest status</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>updateMe PATCHes the account name</t>
+          <t>a hidden service says a document is needed until it is uploaded, then that it waits for the check</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>upload sends multipart with the cookie and no time limit</t>
+          <t>sharing is allowed only while no service waits for a document</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>upload sends the file bytes with its name and type, not a bare { uri } object</t>
+          <t>saving a waiting service keeps Share hidden: the server answer carries waitingFor</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
@@ -9007,17 +9007,17 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use flash</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-flash.test.ts</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>a file the phone cannot open is "File unreadable", not a network error, and nothing is sent</t>
+          <t>createFlash: on after show, off after the delay, off at once on hide, a second show restarts the delay</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -9034,17 +9034,17 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use flash</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-flash.test.ts</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>upload maps a 413 to ApiError "File too large"</t>
+          <t>createFlash: show is a no-op after dispose</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>upload maps a network failure to ApiError network and does not retry</t>
+          <t>prices follow the website rules in German and English</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -9093,12 +9093,12 @@
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>a store that cannot be read (Keystore failure) sends the request without a cookie</t>
+          <t>distance shows km, remote or nothing</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>a cookie that cannot be saved does not fail a request the server already carried out</t>
+          <t>search path leaves out empty filters and trims text</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -9147,12 +9147,12 @@
       </c>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>a malformed Set-Cookie line without "=" is skipped</t>
+          <t>photoSrc loads only absolute http(s) URLs, never a server-relative /api path</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>updateMe sends the one-field name as first and last name, split at the last space</t>
+          <t>applyTexts swaps only the translatable fields and keeps names, prices and photos</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>prices follow the website rules in German and English</t>
+          <t>applyTexts matches services and references by id and leaves unknown ones untouched</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>distance shows km, remote or nothing</t>
+          <t>applyTexts keeps line breaks</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>search path leaves out empty filters and trims text</t>
+          <t>sends the stored cookie and stores a new set-cookie</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
@@ -9282,12 +9282,12 @@
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>photoSrc loads only absolute http(s) URLs, never a server-relative /api path</t>
+          <t>a single joined set-cookie header (no getSetCookie) is split into its cookies</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>a failed check after the upload deletes the uploaded file and reports the original error</t>
+          <t>clears the session on 401</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
@@ -9336,12 +9336,12 @@
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>a successful submit deletes nothing</t>
+          <t>a 401 without a stored session does not call onUnauthorized</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>a failing clean-up does not hide the original error</t>
+          <t>every request names the app origin and leaves the platform cookie store out</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>auth-layout.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>logged-out landing route is login</t>
+          <t>a 409 with error and missing throws ApiError with code and missing</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -9417,12 +9417,12 @@
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>auth-layout.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>no test files inside src/app (each file there becomes a screen)</t>
+          <t>a 400 "Invalid input" lists the fields named by its issues</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
@@ -9439,17 +9439,17 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>Serial create</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>serial-create.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>choosing twice before the create returns creates once, then updates</t>
+          <t>a network failure throws ApiError(0, network)</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -9466,17 +9466,17 @@
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>Serial create</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>serial-create.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>an existing id is only updated</t>
+          <t>a server that never answers fails as network after the time limit</t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
@@ -9493,17 +9493,17 @@
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>two quick changes become one request with the last value</t>
+          <t>saves have no time limit: a slow save that succeeds is not reported as a failure</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
@@ -9520,17 +9520,17 @@
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>flush saves immediately and nothing is sent twice</t>
+          <t>updateMe PATCHes the account name</t>
         </is>
       </c>
       <c r="D332" s="4" t="inlineStr">
@@ -9547,17 +9547,17 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>a rejected save marks error and retry resends the same value</t>
+          <t>upload sends multipart with the cookie and no time limit</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
@@ -9574,17 +9574,17 @@
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>a change typed while a save is in flight is sent after it, in order</t>
+          <t>upload sends the file bytes with its name and type, not a bare { uri } object</t>
         </is>
       </c>
       <c r="D334" s="4" t="inlineStr">
@@ -9601,17 +9601,17 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>dispose sends a pending change so nothing typed is lost</t>
+          <t>a file the phone cannot open is "File unreadable", not a network error, and nothing is sent</t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>loading -&gt; signed in -&gt; signed out</t>
+          <t>upload maps a 413 to ApiError "File too large"</t>
         </is>
       </c>
       <c r="D336" s="4" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>an unverified email never counts as signed in: sign-in sends a code and asks for it</t>
+          <t>upload maps a network failure to ApiError network and does not retry</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="B338" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C338" s="4" t="inlineStr">
         <is>
-          <t>a server that refuses unverified sign-ins (EMAIL_NOT_VERIFIED) also leads to the code screen</t>
+          <t>a store that cannot be read (Keystore failure) sends the request without a cookie</t>
         </is>
       </c>
       <c r="D338" s="4" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="B339" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>sign-up creates the account and sends the code; the right code signs in and saves the account name</t>
+          <t>a cookie that cannot be saved does not fail a request the server already carried out</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="B340" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C340" s="4" t="inlineStr">
         <is>
-          <t>a wrong code throws and keeps signed out</t>
+          <t>a malformed Set-Cookie line without "=" is skipped</t>
         </is>
       </c>
       <c r="D340" s="4" t="inlineStr">
@@ -9768,12 +9768,12 @@
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>a failed login rejects and keeps signed out; a server error on load means signed out</t>
+          <t>updateMe sends the one-field name as first and last name, split at the last space</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="B342" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>a network error on load sets offline (not signed out); retry recovers</t>
+          <t>a failed check after the upload deletes the uploaded file and reports the original error</t>
         </is>
       </c>
       <c r="D342" s="4" t="inlineStr">
@@ -9822,12 +9822,12 @@
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>onUnauthorized from the API client signs the user out</t>
+          <t>a successful submit deletes nothing</t>
         </is>
       </c>
       <c r="D343" s="4" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="B344" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>switching the language also saves it for emails, but only while signed in</t>
+          <t>a failing clean-up does not hide the original error</t>
         </is>
       </c>
       <c r="D344" s="4" t="inlineStr">
@@ -9871,17 +9871,17 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C345" s="4" t="inlineStr">
         <is>
-          <t>verify finishes the sign-up: names and address, then the picture, then the record is cleared; returns the tick</t>
+          <t>two quick changes become one request with the last value</t>
         </is>
       </c>
       <c r="D345" s="4" t="inlineStr">
@@ -9898,17 +9898,17 @@
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B346" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C346" s="4" t="inlineStr">
         <is>
-          <t>a failed upload keeps the record; loadSession retries it once and clears it</t>
+          <t>flush saves immediately and nothing is sent twice</t>
         </is>
       </c>
       <c r="D346" s="4" t="inlineStr">
@@ -9925,17 +9925,17 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>loadSession without a record or while signed out does not finish a sign-up</t>
+          <t>a rejected save marks error and retry resends the same value</t>
         </is>
       </c>
       <c r="D347" s="4" t="inlineStr">
@@ -9952,17 +9952,17 @@
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B348" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C348" s="4" t="inlineStr">
         <is>
-          <t>a record for another email is dropped and applies nothing</t>
+          <t>a change typed while a save is in flight is sent after it, in order</t>
         </is>
       </c>
       <c r="D348" s="4" t="inlineStr">
@@ -9979,17 +9979,17 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>a failed PATCH keeps the full record</t>
+          <t>dispose sends a pending change so nothing typed is lost</t>
         </is>
       </c>
       <c r="D349" s="4" t="inlineStr">
@@ -10006,17 +10006,17 @@
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Stale guard</t>
         </is>
       </c>
       <c r="B350" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>stale-guard.test.ts</t>
         </is>
       </c>
       <c r="C350" s="4" t="inlineStr">
         <is>
-          <t>after the PATCH succeeded, a failed upload keeps only email, tick and picture; the retry does not PATCH again</t>
+          <t>a response older than one already applied is ignored</t>
         </is>
       </c>
       <c r="D350" s="4" t="inlineStr">
@@ -10033,17 +10033,17 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Stale guard</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>stale-guard.test.ts</t>
         </is>
       </c>
       <c r="C351" s="4" t="inlineStr">
         <is>
-          <t>a picture whose cached file is gone is dropped and the record cleared</t>
+          <t>answers arriving in order are all applied</t>
         </is>
       </c>
       <c r="D351" s="4" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="C352" s="4" t="inlineStr">
         <is>
-          <t>sign-up keeps the record for the code step; a failed sign-up leaves none</t>
+          <t>loading -&gt; signed in -&gt; signed out</t>
         </is>
       </c>
       <c r="D352" s="4" t="inlineStr">
@@ -10097,7 +10097,7 @@
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>finishing a sign-up reloads /me so the home nudge sees the new picture; nothing to finish, nothing to reload</t>
+          <t>an unverified email never counts as signed in: sign-in sends a code and asks for it</t>
         </is>
       </c>
       <c r="D353" s="4" t="inlineStr">
@@ -10114,17 +10114,17 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>Use flash</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>use-flash.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>createFlash: on after show, off after the delay, off at once on hide, a second show restarts the delay</t>
+          <t>a server that refuses unverified sign-ins (EMAIL_NOT_VERIFIED) also leads to the code screen</t>
         </is>
       </c>
       <c r="D354" s="4" t="inlineStr">
@@ -10146,12 +10146,12 @@
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>no rows when no service needs a document</t>
+          <t>sign-up creates the account and sends the code; the right code signs in and saves the account name</t>
         </is>
       </c>
       <c r="D355" s="4" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="B356" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>a babysitting service with nothing uploaded â†’ police-certificate none</t>
+          <t>a wrong code throws and keeps signed out</t>
         </is>
       </c>
       <c r="D356" s="4" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>the most recently reviewed check decides, like the server</t>
+          <t>a failed login rejects and keeps signed out; a server error on load means signed out</t>
         </is>
       </c>
       <c r="D357" s="4" t="inlineStr">
@@ -10227,12 +10227,12 @@
       </c>
       <c r="B358" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C358" s="4" t="inlineStr">
         <is>
-          <t>a pending check shows pending even after an approval</t>
+          <t>a network error on load sets offline (not signed out); retry recovers</t>
         </is>
       </c>
       <c r="D358" s="4" t="inlineStr">
@@ -10254,12 +10254,12 @@
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>a requirement code the app does not know still gets a row, after the known ones</t>
+          <t>onUnauthorized from the API client signs the user out</t>
         </is>
       </c>
       <c r="D359" s="4" t="inlineStr">
@@ -10281,12 +10281,12 @@
       </c>
       <c r="B360" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>two services needing the same document give one row</t>
+          <t>switching the language also saves it for emails, but only while signed in</t>
         </is>
       </c>
       <c r="D360" s="4" t="inlineStr">
@@ -10308,12 +10308,12 @@
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>two different categories needing the same document give one row with the latest status</t>
+          <t>verify finishes the sign-up: names and address, then the picture, then the record is cleared; returns the tick</t>
         </is>
       </c>
       <c r="D361" s="4" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="B362" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>a hidden service says a document is needed until it is uploaded, then that it waits for the check</t>
+          <t>a failed upload keeps the record; loadSession retries it once and clears it</t>
         </is>
       </c>
       <c r="D362" s="4" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>sharing is allowed only while no service waits for a document</t>
+          <t>loadSession without a record or while signed out does not finish a sign-up</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="B364" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>saving a waiting service keeps Share hidden: the server answer carries waitingFor</t>
+          <t>a record for another email is dropped and applies nothing</t>
         </is>
       </c>
       <c r="D364" s="4" t="inlineStr">
@@ -10411,17 +10411,17 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
-          <t>profile-tab.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>the My profile tab shows only for a known provider</t>
+          <t>a failed PATCH keeps the full record</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr">
@@ -10438,17 +10438,17 @@
     <row r="366">
       <c r="A366" s="4" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B366" s="4" t="inlineStr">
         <is>
-          <t>profile-tab.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C366" s="4" t="inlineStr">
         <is>
-          <t>after sign-out the next account does not inherit the provider tab</t>
+          <t>after the PATCH succeeded, a failed upload keeps only email, tick and picture; the retry does not PATCH again</t>
         </is>
       </c>
       <c r="D366" s="4" t="inlineStr">
@@ -10465,17 +10465,17 @@
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>Picture nudge</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B367" s="4" t="inlineStr">
         <is>
-          <t>picture-nudge.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C367" s="4" t="inlineStr">
         <is>
-          <t>the dismissed-nudge key is per user, so a second account on the device still sees it</t>
+          <t>a picture whose cached file is gone is dropped and the record cleared</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="B368" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C368" s="4" t="inlineStr">
         <is>
-          <t>applyTexts swaps only the translatable fields and keeps names, prices and photos</t>
+          <t>sign-up keeps the record for the code step; a failed sign-up leaves none</t>
         </is>
       </c>
       <c r="D368" s="4" t="inlineStr">
@@ -10524,12 +10524,12 @@
       </c>
       <c r="B369" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C369" s="4" t="inlineStr">
         <is>
-          <t>applyTexts matches services and references by id and leaves unknown ones untouched</t>
+          <t>finishing a sign-up reloads /me so the home nudge sees the new picture; nothing to finish, nothing to reload</t>
         </is>
       </c>
       <c r="D369" s="4" t="inlineStr">
@@ -10546,17 +10546,17 @@
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Pending signup</t>
         </is>
       </c>
       <c r="B370" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>pending-signup.test.ts</t>
         </is>
       </c>
       <c r="C370" s="4" t="inlineStr">
         <is>
-          <t>applyTexts keeps line breaks</t>
+          <t>the pending record round-trips and clears</t>
         </is>
       </c>
       <c r="D370" s="4" t="inlineStr">
@@ -10573,17 +10573,17 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Picture nudge</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
         <is>
-          <t>match.test.ts</t>
+          <t>picture-nudge.test.ts</t>
         </is>
       </c>
       <c r="C371" s="4" t="inlineStr">
         <is>
-          <t>matches ignores case and accents, and an empty query matches everything</t>
+          <t>the dismissed-nudge key is per user, so a second account on the device still sees it</t>
         </is>
       </c>
       <c r="D371" s="4" t="inlineStr">
@@ -10600,17 +10600,17 @@
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>Pending signup</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B372" s="4" t="inlineStr">
         <is>
-          <t>pending-signup.test.ts</t>
+          <t>match.test.ts</t>
         </is>
       </c>
       <c r="C372" s="4" t="inlineStr">
         <is>
-          <t>the pending record round-trips and clears</t>
+          <t>matches ignores case and accents, and an empty query matches everything</t>
         </is>
       </c>
       <c r="D372" s="4" t="inlineStr">
@@ -10627,17 +10627,17 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>Use me</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
         <is>
-          <t>use-me.test.ts</t>
+          <t>profile-tab.test.ts</t>
         </is>
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>a loadMe in flight at sign-out never fills the store for the next account</t>
+          <t>the My profile tab shows only for a known provider</t>
         </is>
       </c>
       <c r="D373" s="4" t="inlineStr">
@@ -10654,17 +10654,17 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>Stale guard</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>stale-guard.test.ts</t>
+          <t>profile-tab.test.ts</t>
         </is>
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>a response older than one already applied is ignored</t>
+          <t>after sign-out the next account does not inherit the provider tab</t>
         </is>
       </c>
       <c r="D374" s="4" t="inlineStr">
@@ -10681,17 +10681,17 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>Stale guard</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B375" s="4" t="inlineStr">
         <is>
-          <t>stale-guard.test.ts</t>
+          <t>auth-layout.test.ts</t>
         </is>
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>answers arriving in order are all applied</t>
+          <t>logged-out landing route is login</t>
         </is>
       </c>
       <c r="D375" s="4" t="inlineStr">
@@ -10708,22 +10708,22 @@
     <row r="376">
       <c r="A376" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B376" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>auth-layout.test.ts</t>
         </is>
       </c>
       <c r="C376" s="4" t="inlineStr">
         <is>
-          <t>ServiceInputSchema rejects three decimals and negative prices</t>
+          <t>no test files inside src/app (each file there becomes a screen)</t>
         </is>
       </c>
       <c r="D376" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E376" s="4" t="inlineStr">
@@ -10735,22 +10735,22 @@
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Serial create</t>
         </is>
       </c>
       <c r="B377" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>serial-create.test.ts</t>
         </is>
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>ServiceInputSchema needs no price on request</t>
+          <t>choosing twice before the create returns creates once, then updates</t>
         </is>
       </c>
       <c r="D377" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E377" s="4" t="inlineStr">
@@ -10762,22 +10762,22 @@
     <row r="378">
       <c r="A378" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Serial create</t>
         </is>
       </c>
       <c r="B378" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>serial-create.test.ts</t>
         </is>
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
-          <t>AdminListQuerySchema caps pageSize at 100</t>
+          <t>an existing id is only updated</t>
         </is>
       </c>
       <c r="D378" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E378" s="4" t="inlineStr">
@@ -10789,22 +10789,22 @@
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Use me</t>
         </is>
       </c>
       <c r="B379" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>use-me.test.ts</t>
         </is>
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>parse helpers parseBody answers 400 with the issues</t>
+          <t>a loadMe in flight at sign-out never fills the store for the next account</t>
         </is>
       </c>
       <c r="D379" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E379" s="4" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="C380" s="4" t="inlineStr">
         <is>
-          <t>parse helpers parseQuery reads the search params</t>
+          <t>ServiceInputSchema rejects three decimals and negative prices</t>
         </is>
       </c>
       <c r="D380" s="4" t="inlineStr">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="C381" s="4" t="inlineStr">
         <is>
-          <t>list envelopes lists are { docs: [...] }</t>
+          <t>ServiceInputSchema needs no price on request</t>
         </is>
       </c>
       <c r="D381" s="4" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="C382" s="4" t="inlineStr">
         <is>
-          <t>list envelopes reference year is checked against the current year at parse time</t>
+          <t>AdminListQuerySchema caps pageSize at 100</t>
         </is>
       </c>
       <c r="D382" s="4" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>address only the postcode is required; blank street and city become null</t>
+          <t>parse helpers parseBody answers 400 with the issues</t>
         </is>
       </c>
       <c r="D383" s="4" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C384" s="4" t="inlineStr">
         <is>
-          <t>service input as the app sends it a category alone is valid (the server fills currency and title)</t>
+          <t>parse helpers parseQuery reads the search params</t>
         </is>
       </c>
       <c r="D384" s="4" t="inlineStr">
@@ -10951,7 +10951,7 @@
     <row r="385">
       <c r="A385" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B385" s="4" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>catalogue de and en have the same keys</t>
+          <t>list envelopes lists are { docs: [...] }</t>
         </is>
       </c>
       <c r="D385" s="4" t="inlineStr">
@@ -10978,7 +10978,7 @@
     <row r="386">
       <c r="A386" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B386" s="4" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>catalogue no text is empty and no two keys of one namespace carry the same text</t>
+          <t>list envelopes reference year is checked against the current year at parse time</t>
         </is>
       </c>
       <c r="D386" s="4" t="inlineStr">
@@ -11005,7 +11005,7 @@
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B387" s="4" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>catalogue no text contains Treuhand, Escrow, garantiert or a competitor name</t>
+          <t>address only the postcode is required; blank street and city become null</t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
@@ -11032,7 +11032,7 @@
     <row r="388">
       <c r="A388" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B388" s="4" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>catalogue the product name is only written in brand.name</t>
+          <t>service input as the app sends it a category alone is valid (the server fills currency and title)</t>
         </is>
       </c>
       <c r="D388" s="4" t="inlineStr">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>t replaces placeholders and falls back to the key when missing</t>
+          <t>catalogue de and en have the same keys</t>
         </is>
       </c>
       <c r="D389" s="4" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>t fills the brand name without a parameter</t>
+          <t>catalogue no text is empty and no two keys of one namespace carry the same text</t>
         </is>
       </c>
       <c r="D390" s="4" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="C391" s="4" t="inlineStr">
         <is>
-          <t>t knows its languages</t>
+          <t>catalogue no text contains Treuhand, Escrow, garantiert or a competitor name</t>
         </is>
       </c>
       <c r="D391" s="4" t="inlineStr">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>money formats per language</t>
+          <t>catalogue the product name is only written in brand.name</t>
         </is>
       </c>
       <c r="D392" s="4" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>money formats price labels from the catalogue</t>
+          <t>t replaces placeholders and falls back to the key when missing</t>
         </is>
       </c>
       <c r="D393" s="4" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="C394" s="4" t="inlineStr">
         <is>
-          <t>acceptLang en-GB,en;q=0.9,de;q=0.8 -&gt; en</t>
+          <t>t fills the brand name without a parameter</t>
         </is>
       </c>
       <c r="D394" s="4" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>acceptLang * -&gt; undefined</t>
+          <t>t knows its languages</t>
         </is>
       </c>
       <c r="D395" s="4" t="inlineStr">
@@ -11258,7 +11258,7 @@
       </c>
       <c r="C396" s="4" t="inlineStr">
         <is>
-          <t>acceptLang fr-FR -&gt; undefined</t>
+          <t>money formats per language</t>
         </is>
       </c>
       <c r="D396" s="4" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>acceptLang  -&gt; undefined</t>
+          <t>money formats price labels from the catalogue</t>
         </is>
       </c>
       <c r="D397" s="4" t="inlineStr">
@@ -11312,15 +11312,123 @@
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
+          <t>acceptLang en-GB,en;q=0.9,de;q=0.8 -&gt; en</t>
+        </is>
+      </c>
+      <c r="D398" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E398" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B399" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C399" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang * -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D399" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E399" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B400" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C400" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang fr-FR -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D400" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E400" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B401" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C401" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang  -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D401" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E401" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B402" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C402" s="4" t="inlineStr">
+        <is>
           <t>acceptLang undefined -&gt; undefined</t>
         </is>
       </c>
-      <c r="D398" s="4" t="inlineStr">
+      <c r="D402" s="4" t="inlineStr">
         <is>
           <t>Packages</t>
         </is>
       </c>
-      <c r="E398" s="4" t="inlineStr">
+      <c r="E402" s="4" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
@@ -11486,7 +11594,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>23 suites.</t>
+          <t>24 suites.</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -11496,7 +11604,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>115 tests.</t>
+          <t>119 tests.</t>
         </is>
       </c>
     </row>
@@ -12146,7 +12254,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Creates the draft, reloads /me, then navigates; failure does not navigate; double tap runs once; welcome passes through.</t>
+          <t>Creates the draft, reloads /me, then hands the target to the tabs layout, which navigates once the tab is visible; failure sets no target; double tap runs once; welcome passes through; sign-out clears the target.</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -12156,7 +12264,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>apps/mobile start-offering.test.ts.</t>
+          <t>apps/mobile start-offering.test.ts; pending-navigation.test.ts. The layout effect itself needs a phone.</t>
         </is>
       </c>
     </row>
@@ -13103,7 +13211,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Both create the draft, reload /me and open the profile page directly (they used to fall back to Home because the tab was hidden). The sign-up tick uses the same helper. Provider card moved under the find-help button, hidden for providers. Phone checks: Offer services opens the profile page directly; the card is under the find-help button and opens the same page; a provider no longer sees the card.</t>
+          <t>Both create the draft, reload /me and open the profile page directly (they used to fall back to Home because the tab was hidden). The sign-up tick uses the same helper. Provider card moved under the find-help button, hidden for providers. Phone checks: Offer services opens the profile page directly; the card is under the find-help button and opens the same page; a provider no longer sees the card. The navigation waits for the tabs layout to show the tab (hand-off through a pending target), not for luck.</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">

--- a/Reports/Registration-Setup-Test-Report.xlsx
+++ b/Reports/Registration-Setup-Test-Report.xlsx
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTA('Test Results'!C2:C402)</f>
+        <f>COUNTA('Test Results'!C2:C408)</f>
         <v/>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Test Results'!E2:E402,"Passed")</f>
+        <f>COUNTIF('Test Results'!E2:E408,"Passed")</f>
         <v/>
       </c>
     </row>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Test Results'!E2:E402,"Failed")</f>
+        <f>COUNTIF('Test Results'!E2:E408,"Failed")</f>
         <v/>
       </c>
     </row>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF('Test Results'!E2:E402,"Skipped")</f>
+        <f>COUNTIF('Test Results'!E2:E408,"Skipped")</f>
         <v/>
       </c>
     </row>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E402"/>
+  <dimension ref="A1:E408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7738,17 +7738,17 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>Share profile</t>
+          <t>Pending navigation</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>share-profile.test.ts</t>
+          <t>pending-navigation.test.ts</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>the provider page url carries the language only when it is not the default</t>
+          <t>set, consume once, then nothing</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
@@ -7765,17 +7765,17 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>Share profile</t>
+          <t>Pending navigation</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>share-profile.test.ts</t>
+          <t>pending-navigation.test.ts</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>shareProfile passes the url and the text in the given language</t>
+          <t>clearPending drops it (sign-out)</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
@@ -7792,17 +7792,17 @@
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>Start offering</t>
+          <t>Pending navigation</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>start-offering.test.ts</t>
+          <t>pending-navigation.test.ts</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>creates the draft, reloads /me, then sets the target, in that order</t>
+          <t>readyToNavigate: only with a target and a visible profile tab</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
@@ -7819,17 +7819,17 @@
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>Start offering</t>
+          <t>Pending navigation</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>start-offering.test.ts</t>
+          <t>pending-navigation.test.ts</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>welcome passes through</t>
+          <t>the layout order: not ready keeps the target, ready consumes it once</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
@@ -7846,17 +7846,17 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>Start offering</t>
+          <t>Share profile</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>start-offering.test.ts</t>
+          <t>share-profile.test.ts</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>a failure returns the error text and does not navigate</t>
+          <t>the provider page url carries the language only when it is not the default</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
@@ -7873,17 +7873,17 @@
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>Start offering</t>
+          <t>Share profile</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>start-offering.test.ts</t>
+          <t>share-profile.test.ts</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>a second call while one runs does nothing extra</t>
+          <t>shareProfile passes the url and the text in the given language</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
@@ -7900,17 +7900,17 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>Address fields</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>address-fields.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>toAddress: empty is null (clears), a postcode alone is enough, street or city without postcode is undefined</t>
+          <t>creates the draft, reloads /me, then sets the target, in that order</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
@@ -7927,17 +7927,17 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>signUp posts email, password and name and stores the session cookie</t>
+          <t>welcome passes through</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
@@ -7954,17 +7954,17 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>signIn posts email and password and returns the user</t>
+          <t>a failure returns the error text and does not navigate</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
@@ -7981,17 +7981,17 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>a refused sign-in throws the server code, which maps to a catalogue message</t>
+          <t>a second call while one runs does nothing extra</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
@@ -8008,17 +8008,17 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>signOut forgets the session at once and tells the server with the old cookie</t>
+          <t>no target when /me says the person is not a provider</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
@@ -8035,17 +8035,17 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>signOut offline still signs out</t>
+          <t>a sign-out during the run leaves no target behind</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
@@ -8062,17 +8062,17 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Address fields</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>address-fields.test.ts</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>session reads get-session with the cookie; no cookie means null without a request</t>
+          <t>toAddress: empty is null (clears), a postcode alone is enough, street or city without postcode is undefined</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>session throws on a network error (the app offers a retry, not the login)</t>
+          <t>server errors land on the right field</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>sendVerificationCode asks for an email-verification code</t>
+          <t>withItem adds a trimmed new skill or strength once and ignores blanks</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>verifyEmail sends the code as otp, stores the new session and returns the user</t>
+          <t>the form-level error shows unless every server error has an inline slot</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>requestPasswordReset asks for a reset code</t>
+          <t>service and reference validation</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
@@ -8202,12 +8202,12 @@
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>resetPassword sends email, code and the new password</t>
+          <t>every missing item the publish route can return has de and en text</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
@@ -8229,12 +8229,12 @@
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>a wrong code throws INVALID_OTP, shown as the code message</t>
+          <t>the service body names the category by id and the currency, as the server expects</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>signUp and signIn start without an old stored session</t>
+          <t>a 400 "Invalid input" marks each named field</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
@@ -8278,17 +8278,17 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>Pending navigation</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>pending-navigation.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>set, consume once, then nothing</t>
+          <t>live means published and not suspended now (the server rule of listServices)</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
@@ -8305,17 +8305,17 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>Pending navigation</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>pending-navigation.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>clearPending drops it (sign-out)</t>
+          <t>preparePhoto keeps the long side at 1600 px</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
@@ -8332,17 +8332,17 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>Pending navigation</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>pending-navigation.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>readyToNavigate: only with a target and a visible profile tab</t>
+          <t>tooLarge is true above 4_434_464 bytes</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
@@ -8364,12 +8364,12 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>server errors land on the right field</t>
+          <t>pickPhoto cancelled is null</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>withItem adds a trimmed new skill or strength once and ignores blanks</t>
+          <t>pickPhoto a refused permission is denied, not cancelled</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>the form-level error shows unless every server error has an inline slot</t>
+          <t>pickDocument offers PDFs and the image types the server accepts, from any file source</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>service and reference validation</t>
+          <t>pickDocument cancelled is null</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
@@ -8472,12 +8472,12 @@
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>every missing item the publish route can return has de and en text</t>
+          <t>prices follow the website rules in German and English</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
@@ -8499,12 +8499,12 @@
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>the service body names the category by id and the currency, as the server expects</t>
+          <t>distance shows km, remote or nothing</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>a 400 "Invalid input" marks each named field</t>
+          <t>search path leaves out empty filters and trims text</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>live means published and not suspended now (the server rule of listServices)</t>
+          <t>photoSrc loads only absolute http(s) URLs, never a server-relative /api path</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>preparePhoto keeps the long side at 1600 px</t>
+          <t>loading -&gt; signed in -&gt; signed out</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>tooLarge is true above 4_434_464 bytes</t>
+          <t>an unverified email never counts as signed in: sign-in sends a code and asks for it</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
@@ -8634,12 +8634,12 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>pickPhoto cancelled is null</t>
+          <t>a server that refuses unverified sign-ins (EMAIL_NOT_VERIFIED) also leads to the code screen</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>pickPhoto a refused permission is denied, not cancelled</t>
+          <t>sign-up creates the account and sends the code; the right code signs in and saves the account name</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>pickDocument offers PDFs and the image types the server accepts, from any file source</t>
+          <t>a wrong code throws and keeps signed out</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -8715,12 +8715,12 @@
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>pickDocument cancelled is null</t>
+          <t>a failed login rejects and keeps signed out; a server error on load means signed out</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>no rows when no service needs a document</t>
+          <t>a network error on load sets offline (not signed out); retry recovers</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>a babysitting service with nothing uploaded â†’ police-certificate none</t>
+          <t>onUnauthorized from the API client signs the user out</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
@@ -8796,12 +8796,12 @@
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>the most recently reviewed check decides, like the server</t>
+          <t>switching the language also saves it for emails, but only while signed in</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>a pending check shows pending even after an approval</t>
+          <t>verify finishes the sign-up: names and address, then the picture, then the record is cleared; returns the tick</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>a requirement code the app does not know still gets a row, after the known ones</t>
+          <t>a failed upload keeps the record; loadSession retries it once and clears it</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>two services needing the same document give one row</t>
+          <t>loadSession without a record or while signed out does not finish a sign-up</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>two different categories needing the same document give one row with the latest status</t>
+          <t>a record for another email is dropped and applies nothing</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>a hidden service says a document is needed until it is uploaded, then that it waits for the check</t>
+          <t>a failed PATCH keeps the full record</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>sharing is allowed only while no service waits for a document</t>
+          <t>a postcode the server calls invalid does not block the names: they are saved without the address</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>saving a waiting service keeps Share hidden: the server answer carries waitingFor</t>
+          <t>after the PATCH succeeded, a failed upload keeps only email, tick and picture; the retry does not PATCH again</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
@@ -9007,17 +9007,17 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>Use flash</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>use-flash.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>createFlash: on after show, off after the delay, off at once on hide, a second show restarts the delay</t>
+          <t>a picture whose cached file is gone is dropped and the record cleared</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -9034,17 +9034,17 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>Use flash</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>use-flash.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>createFlash: show is a no-op after dispose</t>
+          <t>sign-up keeps the record for the code step; a failed sign-up leaves none</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>prices follow the website rules in German and English</t>
+          <t>finishing a sign-up reloads /me so the home nudge sees the new picture; nothing to finish, nothing to reload</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -9093,12 +9093,12 @@
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>distance shows km, remote or nothing</t>
+          <t>signUp posts email, password and name and stores the session cookie</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>search path leaves out empty filters and trims text</t>
+          <t>signIn posts email and password and returns the user</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -9147,12 +9147,12 @@
       </c>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>photoSrc loads only absolute http(s) URLs, never a server-relative /api path</t>
+          <t>a refused sign-in throws the server code, which maps to a catalogue message</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>applyTexts swaps only the translatable fields and keeps names, prices and photos</t>
+          <t>signOut forgets the session at once and tells the server with the old cookie</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>applyTexts matches services and references by id and leaves unknown ones untouched</t>
+          <t>signOut offline still signs out</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>applyTexts keeps line breaks</t>
+          <t>session reads get-session with the cookie; no cookie means null without a request</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>sends the stored cookie and stores a new set-cookie</t>
+          <t>session throws on a network error (the app offers a retry, not the login)</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
@@ -9282,12 +9282,12 @@
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>a single joined set-cookie header (no getSetCookie) is split into its cookies</t>
+          <t>sendVerificationCode asks for an email-verification code</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>clears the session on 401</t>
+          <t>verifyEmail sends the code as otp, stores the new session and returns the user</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
@@ -9336,12 +9336,12 @@
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>a 401 without a stored session does not call onUnauthorized</t>
+          <t>requestPasswordReset asks for a reset code</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>every request names the app origin and leaves the platform cookie store out</t>
+          <t>resetPassword sends email, code and the new password</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>a 409 with error and missing throws ApiError with code and missing</t>
+          <t>a wrong code throws INVALID_OTP, shown as the code message</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -9417,12 +9417,12 @@
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>a 400 "Invalid input" lists the fields named by its issues</t>
+          <t>signUp and signIn start without an old stored session</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>a network failure throws ApiError(0, network)</t>
+          <t>applyTexts swaps only the translatable fields and keeps names, prices and photos</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>a server that never answers fails as network after the time limit</t>
+          <t>applyTexts matches services and references by id and leaves unknown ones untouched</t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>saves have no time limit: a slow save that succeeds is not reported as a failure</t>
+          <t>applyTexts keeps line breaks</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>updateMe PATCHes the account name</t>
+          <t>a failed check after the upload deletes the uploaded file and reports the original error</t>
         </is>
       </c>
       <c r="D332" s="4" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>upload sends multipart with the cookie and no time limit</t>
+          <t>a successful submit deletes nothing</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>upload sends the file bytes with its name and type, not a bare { uri } object</t>
+          <t>a failing clean-up does not hide the original error</t>
         </is>
       </c>
       <c r="D334" s="4" t="inlineStr">
@@ -9601,17 +9601,17 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Pending signup</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>pending-signup.test.ts</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>a file the phone cannot open is "File unreadable", not a network error, and nothing is sent</t>
+          <t>the pending record round-trips and clears</t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
@@ -9628,17 +9628,17 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Serial create</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>serial-create.test.ts</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>upload maps a 413 to ApiError "File too large"</t>
+          <t>choosing twice before the create returns creates once, then updates</t>
         </is>
       </c>
       <c r="D336" s="4" t="inlineStr">
@@ -9655,17 +9655,17 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Serial create</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>serial-create.test.ts</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>upload maps a network failure to ApiError network and does not retry</t>
+          <t>an existing id is only updated</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
@@ -9682,17 +9682,17 @@
     <row r="338">
       <c r="A338" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B338" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C338" s="4" t="inlineStr">
         <is>
-          <t>a store that cannot be read (Keystore failure) sends the request without a cookie</t>
+          <t>two quick changes become one request with the last value</t>
         </is>
       </c>
       <c r="D338" s="4" t="inlineStr">
@@ -9709,17 +9709,17 @@
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B339" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>a cookie that cannot be saved does not fail a request the server already carried out</t>
+          <t>flush saves immediately and nothing is sent twice</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
@@ -9736,17 +9736,17 @@
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B340" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C340" s="4" t="inlineStr">
         <is>
-          <t>a malformed Set-Cookie line without "=" is skipped</t>
+          <t>a rejected save marks error and retry resends the same value</t>
         </is>
       </c>
       <c r="D340" s="4" t="inlineStr">
@@ -9763,17 +9763,17 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>updateMe sends the one-field name as first and last name, split at the last space</t>
+          <t>a change typed while a save is in flight is sent after it, in order</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
@@ -9790,17 +9790,17 @@
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B342" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>a failed check after the upload deletes the uploaded file and reports the original error</t>
+          <t>dispose sends a pending change so nothing typed is lost</t>
         </is>
       </c>
       <c r="D342" s="4" t="inlineStr">
@@ -9822,12 +9822,12 @@
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>a successful submit deletes nothing</t>
+          <t>sends the stored cookie and stores a new set-cookie</t>
         </is>
       </c>
       <c r="D343" s="4" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="B344" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>a failing clean-up does not hide the original error</t>
+          <t>a single joined set-cookie header (no getSetCookie) is split into its cookies</t>
         </is>
       </c>
       <c r="D344" s="4" t="inlineStr">
@@ -9871,17 +9871,17 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C345" s="4" t="inlineStr">
         <is>
-          <t>two quick changes become one request with the last value</t>
+          <t>clears the session on 401</t>
         </is>
       </c>
       <c r="D345" s="4" t="inlineStr">
@@ -9898,17 +9898,17 @@
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B346" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C346" s="4" t="inlineStr">
         <is>
-          <t>flush saves immediately and nothing is sent twice</t>
+          <t>a 401 without a stored session does not call onUnauthorized</t>
         </is>
       </c>
       <c r="D346" s="4" t="inlineStr">
@@ -9925,17 +9925,17 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>a rejected save marks error and retry resends the same value</t>
+          <t>every request names the app origin and leaves the platform cookie store out</t>
         </is>
       </c>
       <c r="D347" s="4" t="inlineStr">
@@ -9952,17 +9952,17 @@
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B348" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C348" s="4" t="inlineStr">
         <is>
-          <t>a change typed while a save is in flight is sent after it, in order</t>
+          <t>a 409 with error and missing throws ApiError with code and missing</t>
         </is>
       </c>
       <c r="D348" s="4" t="inlineStr">
@@ -9979,17 +9979,17 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>dispose sends a pending change so nothing typed is lost</t>
+          <t>a 400 "Invalid input" lists the fields named by its issues</t>
         </is>
       </c>
       <c r="D349" s="4" t="inlineStr">
@@ -10006,17 +10006,17 @@
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>Stale guard</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B350" s="4" t="inlineStr">
         <is>
-          <t>stale-guard.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C350" s="4" t="inlineStr">
         <is>
-          <t>a response older than one already applied is ignored</t>
+          <t>a network failure throws ApiError(0, network)</t>
         </is>
       </c>
       <c r="D350" s="4" t="inlineStr">
@@ -10033,17 +10033,17 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>Stale guard</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
         <is>
-          <t>stale-guard.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C351" s="4" t="inlineStr">
         <is>
-          <t>answers arriving in order are all applied</t>
+          <t>a server that never answers fails as network after the time limit</t>
         </is>
       </c>
       <c r="D351" s="4" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="B352" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C352" s="4" t="inlineStr">
         <is>
-          <t>loading -&gt; signed in -&gt; signed out</t>
+          <t>saves have no time limit: a slow save that succeeds is not reported as a failure</t>
         </is>
       </c>
       <c r="D352" s="4" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>an unverified email never counts as signed in: sign-in sends a code and asks for it</t>
+          <t>updateMe PATCHes the account name</t>
         </is>
       </c>
       <c r="D353" s="4" t="inlineStr">
@@ -10119,12 +10119,12 @@
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>a server that refuses unverified sign-ins (EMAIL_NOT_VERIFIED) also leads to the code screen</t>
+          <t>upload sends multipart with the cookie and no time limit</t>
         </is>
       </c>
       <c r="D354" s="4" t="inlineStr">
@@ -10146,12 +10146,12 @@
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>sign-up creates the account and sends the code; the right code signs in and saves the account name</t>
+          <t>upload sends the file bytes with its name and type, not a bare { uri } object</t>
         </is>
       </c>
       <c r="D355" s="4" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="B356" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>a wrong code throws and keeps signed out</t>
+          <t>a file the phone cannot open is "File unreadable", not a network error, and nothing is sent</t>
         </is>
       </c>
       <c r="D356" s="4" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>a failed login rejects and keeps signed out; a server error on load means signed out</t>
+          <t>upload maps a 413 to ApiError "File too large"</t>
         </is>
       </c>
       <c r="D357" s="4" t="inlineStr">
@@ -10227,12 +10227,12 @@
       </c>
       <c r="B358" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C358" s="4" t="inlineStr">
         <is>
-          <t>a network error on load sets offline (not signed out); retry recovers</t>
+          <t>upload maps a network failure to ApiError network and does not retry</t>
         </is>
       </c>
       <c r="D358" s="4" t="inlineStr">
@@ -10254,12 +10254,12 @@
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>onUnauthorized from the API client signs the user out</t>
+          <t>a store that cannot be read (Keystore failure) sends the request without a cookie</t>
         </is>
       </c>
       <c r="D359" s="4" t="inlineStr">
@@ -10281,12 +10281,12 @@
       </c>
       <c r="B360" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>switching the language also saves it for emails, but only while signed in</t>
+          <t>a cookie that cannot be saved does not fail a request the server already carried out</t>
         </is>
       </c>
       <c r="D360" s="4" t="inlineStr">
@@ -10308,12 +10308,12 @@
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>verify finishes the sign-up: names and address, then the picture, then the record is cleared; returns the tick</t>
+          <t>a malformed Set-Cookie line without "=" is skipped</t>
         </is>
       </c>
       <c r="D361" s="4" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="B362" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>a failed upload keeps the record; loadSession retries it once and clears it</t>
+          <t>updateMe sends the one-field name as first and last name, split at the last space</t>
         </is>
       </c>
       <c r="D362" s="4" t="inlineStr">
@@ -10357,17 +10357,17 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use me</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-me.test.ts</t>
         </is>
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>loadSession without a record or while signed out does not finish a sign-up</t>
+          <t>a loadMe in flight at sign-out never fills the store for the next account</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
@@ -10384,17 +10384,17 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use me</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-me.test.ts</t>
         </is>
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>a record for another email is dropped and applies nothing</t>
+          <t>the newest loadMe wins: an older, slower response never overwrites a newer one</t>
         </is>
       </c>
       <c r="D364" s="4" t="inlineStr">
@@ -10411,17 +10411,17 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use flash</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-flash.test.ts</t>
         </is>
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>a failed PATCH keeps the full record</t>
+          <t>createFlash: on after show, off after the delay, off at once on hide, a second show restarts the delay</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr">
@@ -10438,17 +10438,17 @@
     <row r="366">
       <c r="A366" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use flash</t>
         </is>
       </c>
       <c r="B366" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-flash.test.ts</t>
         </is>
       </c>
       <c r="C366" s="4" t="inlineStr">
         <is>
-          <t>after the PATCH succeeded, a failed upload keeps only email, tick and picture; the retry does not PATCH again</t>
+          <t>createFlash: show is a no-op after dispose</t>
         </is>
       </c>
       <c r="D366" s="4" t="inlineStr">
@@ -10465,17 +10465,17 @@
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use flash</t>
         </is>
       </c>
       <c r="B367" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-flash.test.ts</t>
         </is>
       </c>
       <c r="C367" s="4" t="inlineStr">
         <is>
-          <t>a picture whose cached file is gone is dropped and the record cleared</t>
+          <t>createFlash: a fresh flash after a dispose works again (remount)</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="B368" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>match.test.ts</t>
         </is>
       </c>
       <c r="C368" s="4" t="inlineStr">
         <is>
-          <t>sign-up keeps the record for the code step; a failed sign-up leaves none</t>
+          <t>matches ignores case and accents, and an empty query matches everything</t>
         </is>
       </c>
       <c r="D368" s="4" t="inlineStr">
@@ -10519,17 +10519,17 @@
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Stale guard</t>
         </is>
       </c>
       <c r="B369" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>stale-guard.test.ts</t>
         </is>
       </c>
       <c r="C369" s="4" t="inlineStr">
         <is>
-          <t>finishing a sign-up reloads /me so the home nudge sees the new picture; nothing to finish, nothing to reload</t>
+          <t>a response older than one already applied is ignored</t>
         </is>
       </c>
       <c r="D369" s="4" t="inlineStr">
@@ -10546,17 +10546,17 @@
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
         <is>
-          <t>Pending signup</t>
+          <t>Stale guard</t>
         </is>
       </c>
       <c r="B370" s="4" t="inlineStr">
         <is>
-          <t>pending-signup.test.ts</t>
+          <t>stale-guard.test.ts</t>
         </is>
       </c>
       <c r="C370" s="4" t="inlineStr">
         <is>
-          <t>the pending record round-trips and clears</t>
+          <t>answers arriving in order are all applied</t>
         </is>
       </c>
       <c r="D370" s="4" t="inlineStr">
@@ -10573,17 +10573,17 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>Picture nudge</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
         <is>
-          <t>picture-nudge.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C371" s="4" t="inlineStr">
         <is>
-          <t>the dismissed-nudge key is per user, so a second account on the device still sees it</t>
+          <t>no rows when no service needs a document</t>
         </is>
       </c>
       <c r="D371" s="4" t="inlineStr">
@@ -10605,12 +10605,12 @@
       </c>
       <c r="B372" s="4" t="inlineStr">
         <is>
-          <t>match.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C372" s="4" t="inlineStr">
         <is>
-          <t>matches ignores case and accents, and an empty query matches everything</t>
+          <t>a babysitting service with nothing uploaded â†’ police-certificate none</t>
         </is>
       </c>
       <c r="D372" s="4" t="inlineStr">
@@ -10627,17 +10627,17 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
         <is>
-          <t>profile-tab.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>the My profile tab shows only for a known provider</t>
+          <t>the most recently reviewed check decides, like the server</t>
         </is>
       </c>
       <c r="D373" s="4" t="inlineStr">
@@ -10654,17 +10654,17 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>profile-tab.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>after sign-out the next account does not inherit the provider tab</t>
+          <t>a pending check shows pending even after an approval</t>
         </is>
       </c>
       <c r="D374" s="4" t="inlineStr">
@@ -10686,12 +10686,12 @@
       </c>
       <c r="B375" s="4" t="inlineStr">
         <is>
-          <t>auth-layout.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>logged-out landing route is login</t>
+          <t>a requirement code the app does not know still gets a row, after the known ones</t>
         </is>
       </c>
       <c r="D375" s="4" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="B376" s="4" t="inlineStr">
         <is>
-          <t>auth-layout.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C376" s="4" t="inlineStr">
         <is>
-          <t>no test files inside src/app (each file there becomes a screen)</t>
+          <t>two services needing the same document give one row</t>
         </is>
       </c>
       <c r="D376" s="4" t="inlineStr">
@@ -10735,17 +10735,17 @@
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>Serial create</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B377" s="4" t="inlineStr">
         <is>
-          <t>serial-create.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>choosing twice before the create returns creates once, then updates</t>
+          <t>two different categories needing the same document give one row with the latest status</t>
         </is>
       </c>
       <c r="D377" s="4" t="inlineStr">
@@ -10762,17 +10762,17 @@
     <row r="378">
       <c r="A378" s="4" t="inlineStr">
         <is>
-          <t>Serial create</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B378" s="4" t="inlineStr">
         <is>
-          <t>serial-create.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
-          <t>an existing id is only updated</t>
+          <t>a hidden service says a document is needed until it is uploaded, then that it waits for the check</t>
         </is>
       </c>
       <c r="D378" s="4" t="inlineStr">
@@ -10789,17 +10789,17 @@
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
         <is>
-          <t>Use me</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B379" s="4" t="inlineStr">
         <is>
-          <t>use-me.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>a loadMe in flight at sign-out never fills the store for the next account</t>
+          <t>sharing is allowed only while no service waits for a document</t>
         </is>
       </c>
       <c r="D379" s="4" t="inlineStr">
@@ -10816,22 +10816,22 @@
     <row r="380">
       <c r="A380" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B380" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C380" s="4" t="inlineStr">
         <is>
-          <t>ServiceInputSchema rejects three decimals and negative prices</t>
+          <t>saving a waiting service keeps Share hidden: the server answer carries waitingFor</t>
         </is>
       </c>
       <c r="D380" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E380" s="4" t="inlineStr">
@@ -10843,22 +10843,22 @@
     <row r="381">
       <c r="A381" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="B381" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>profile-tab.test.ts</t>
         </is>
       </c>
       <c r="C381" s="4" t="inlineStr">
         <is>
-          <t>ServiceInputSchema needs no price on request</t>
+          <t>the My profile tab shows only for a known provider</t>
         </is>
       </c>
       <c r="D381" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E381" s="4" t="inlineStr">
@@ -10870,22 +10870,22 @@
     <row r="382">
       <c r="A382" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="B382" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>profile-tab.test.ts</t>
         </is>
       </c>
       <c r="C382" s="4" t="inlineStr">
         <is>
-          <t>AdminListQuerySchema caps pageSize at 100</t>
+          <t>after sign-out the next account does not inherit the provider tab</t>
         </is>
       </c>
       <c r="D382" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E382" s="4" t="inlineStr">
@@ -10897,22 +10897,22 @@
     <row r="383">
       <c r="A383" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Picture nudge</t>
         </is>
       </c>
       <c r="B383" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>picture-nudge.test.ts</t>
         </is>
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>parse helpers parseBody answers 400 with the issues</t>
+          <t>the dismissed-nudge key is per user, so a second account on the device still sees it</t>
         </is>
       </c>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E383" s="4" t="inlineStr">
@@ -10924,22 +10924,22 @@
     <row r="384">
       <c r="A384" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B384" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>auth-layout.test.ts</t>
         </is>
       </c>
       <c r="C384" s="4" t="inlineStr">
         <is>
-          <t>parse helpers parseQuery reads the search params</t>
+          <t>logged-out landing route is login</t>
         </is>
       </c>
       <c r="D384" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E384" s="4" t="inlineStr">
@@ -10951,22 +10951,22 @@
     <row r="385">
       <c r="A385" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B385" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>auth-layout.test.ts</t>
         </is>
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>list envelopes lists are { docs: [...] }</t>
+          <t>no test files inside src/app (each file there becomes a screen)</t>
         </is>
       </c>
       <c r="D385" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E385" s="4" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>list envelopes reference year is checked against the current year at parse time</t>
+          <t>ServiceInputSchema rejects three decimals and negative prices</t>
         </is>
       </c>
       <c r="D386" s="4" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>address only the postcode is required; blank street and city become null</t>
+          <t>ServiceInputSchema needs no price on request</t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>service input as the app sends it a category alone is valid (the server fills currency and title)</t>
+          <t>AdminListQuerySchema caps pageSize at 100</t>
         </is>
       </c>
       <c r="D388" s="4" t="inlineStr">
@@ -11059,7 +11059,7 @@
     <row r="389">
       <c r="A389" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B389" s="4" t="inlineStr">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>catalogue de and en have the same keys</t>
+          <t>parse helpers parseBody answers 400 with the issues</t>
         </is>
       </c>
       <c r="D389" s="4" t="inlineStr">
@@ -11086,7 +11086,7 @@
     <row r="390">
       <c r="A390" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B390" s="4" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>catalogue no text is empty and no two keys of one namespace carry the same text</t>
+          <t>parse helpers parseQuery reads the search params</t>
         </is>
       </c>
       <c r="D390" s="4" t="inlineStr">
@@ -11113,7 +11113,7 @@
     <row r="391">
       <c r="A391" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B391" s="4" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="C391" s="4" t="inlineStr">
         <is>
-          <t>catalogue no text contains Treuhand, Escrow, garantiert or a competitor name</t>
+          <t>list envelopes lists are { docs: [...] }</t>
         </is>
       </c>
       <c r="D391" s="4" t="inlineStr">
@@ -11140,7 +11140,7 @@
     <row r="392">
       <c r="A392" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B392" s="4" t="inlineStr">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>catalogue the product name is only written in brand.name</t>
+          <t>list envelopes reference year is checked against the current year at parse time</t>
         </is>
       </c>
       <c r="D392" s="4" t="inlineStr">
@@ -11167,7 +11167,7 @@
     <row r="393">
       <c r="A393" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B393" s="4" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>t replaces placeholders and falls back to the key when missing</t>
+          <t>address only the postcode is required; blank street and city become null</t>
         </is>
       </c>
       <c r="D393" s="4" t="inlineStr">
@@ -11194,7 +11194,7 @@
     <row r="394">
       <c r="A394" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B394" s="4" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="C394" s="4" t="inlineStr">
         <is>
-          <t>t fills the brand name without a parameter</t>
+          <t>service input as the app sends it a category alone is valid (the server fills currency and title)</t>
         </is>
       </c>
       <c r="D394" s="4" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>t knows its languages</t>
+          <t>catalogue de and en have the same keys</t>
         </is>
       </c>
       <c r="D395" s="4" t="inlineStr">
@@ -11258,7 +11258,7 @@
       </c>
       <c r="C396" s="4" t="inlineStr">
         <is>
-          <t>money formats per language</t>
+          <t>catalogue no text is empty and no two keys of one namespace carry the same text</t>
         </is>
       </c>
       <c r="D396" s="4" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>money formats price labels from the catalogue</t>
+          <t>catalogue no text contains Treuhand, Escrow, garantiert or a competitor name</t>
         </is>
       </c>
       <c r="D397" s="4" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
-          <t>acceptLang en-GB,en;q=0.9,de;q=0.8 -&gt; en</t>
+          <t>catalogue the product name is only written in brand.name</t>
         </is>
       </c>
       <c r="D398" s="4" t="inlineStr">
@@ -11339,7 +11339,7 @@
       </c>
       <c r="C399" s="4" t="inlineStr">
         <is>
-          <t>acceptLang * -&gt; undefined</t>
+          <t>t replaces placeholders and falls back to the key when missing</t>
         </is>
       </c>
       <c r="D399" s="4" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="C400" s="4" t="inlineStr">
         <is>
-          <t>acceptLang fr-FR -&gt; undefined</t>
+          <t>t fills the brand name without a parameter</t>
         </is>
       </c>
       <c r="D400" s="4" t="inlineStr">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>acceptLang  -&gt; undefined</t>
+          <t>t knows its languages</t>
         </is>
       </c>
       <c r="D401" s="4" t="inlineStr">
@@ -11420,15 +11420,177 @@
       </c>
       <c r="C402" s="4" t="inlineStr">
         <is>
+          <t>money formats per language</t>
+        </is>
+      </c>
+      <c r="D402" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E402" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B403" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C403" s="4" t="inlineStr">
+        <is>
+          <t>money formats price labels from the catalogue</t>
+        </is>
+      </c>
+      <c r="D403" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E403" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B404" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C404" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang en-GB,en;q=0.9,de;q=0.8 -&gt; en</t>
+        </is>
+      </c>
+      <c r="D404" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E404" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B405" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C405" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang * -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D405" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E405" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B406" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C406" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang fr-FR -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D406" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E406" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B407" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C407" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang  -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D407" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E407" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B408" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C408" s="4" t="inlineStr">
+        <is>
           <t>acceptLang undefined -&gt; undefined</t>
         </is>
       </c>
-      <c r="D402" s="4" t="inlineStr">
+      <c r="D408" s="4" t="inlineStr">
         <is>
           <t>Packages</t>
         </is>
       </c>
-      <c r="E402" s="4" t="inlineStr">
+      <c r="E408" s="4" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
@@ -11604,7 +11766,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>119 tests.</t>
+          <t>125 tests.</t>
         </is>
       </c>
     </row>
@@ -12345,7 +12507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -13220,6 +13382,23 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (PR review): offering, postcode, saving</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>The newest /me request wins; Offer services needs isProvider true and leaves no target after a sign-out; the layout consumes the target only when the tab is visible; the server checks the postcode format (400 Invalid postcode; a well-formed unlisted one is accepted); a refused sign-up postcode no longer blocks the names; Account fields are locked while saving. Phone check: Offer services reaches the My profile tab route (not the empty app/my-profile stack); a bad postcode shows the new text in Account.</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Fixed; Not yet done (phone)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Reports/Registration-Setup-Test-Report.xlsx
+++ b/Reports/Registration-Setup-Test-Report.xlsx
@@ -454,7 +454,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Full suite on branch registration-setup (after fix wave 2 of the independent review), run 27 October 2026: web integration tests on the local Docker database, app and package unit tests. Features only a phone can confirm are marked Not yet done (phone) in Other Checks.</t>
+          <t>Full suite on branch account-address-saved (fixes from the owner phone test, on top of registration-setup), run 27 October 2026: web integration tests on the local Docker database, app and package unit tests. Features only a phone can confirm are marked Not yet done (phone) in Other Checks.</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTA('Test Results'!C2:C391)</f>
+        <f>COUNTA('Test Results'!C2:C408)</f>
         <v/>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Test Results'!E2:E389,"Passed")</f>
+        <f>COUNTIF('Test Results'!E2:E408,"Passed")</f>
         <v/>
       </c>
     </row>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Test Results'!E2:E389,"Failed")</f>
+        <f>COUNTIF('Test Results'!E2:E408,"Failed")</f>
         <v/>
       </c>
     </row>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF('Test Results'!E2:E389,"Skipped")</f>
+        <f>COUNTIF('Test Results'!E2:E408,"Skipped")</f>
         <v/>
       </c>
     </row>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E391"/>
+  <dimension ref="A1:E408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>suspension and published-again emails go to published profiles only; the cron still clears every ended suspension</t>
+          <t>GET users/[id] returns an address that has only a postcode</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1069,17 +1069,17 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Admin lang</t>
+          <t>Admin back office API</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>admin-lang.int.spec.ts</t>
+          <t>admin-api.int.spec.ts</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>adminLang {"cookie":"en"} -&gt; en</t>
+          <t>suspension and published-again emails go to published profiles only; the cron still clears every ended suspension</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>adminLang {"cookie":"fr"} -&gt; de</t>
+          <t>adminLang {"cookie":"en"} -&gt; en</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>adminLang {"cookie":"xx","acceptLanguage":"en"} -&gt; en</t>
+          <t>adminLang {"cookie":"fr"} -&gt; de</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>adminLang {"acceptLanguage":"en-GB,en;q=0.9,de;q=0.8"} -&gt; en</t>
+          <t>adminLang {"cookie":"xx","acceptLanguage":"en"} -&gt; en</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>adminLang {"acceptLanguage":"fr-FR"} -&gt; de</t>
+          <t>adminLang {"acceptLanguage":"en-GB,en;q=0.9,de;q=0.8"} -&gt; en</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>adminLang {} -&gt; de</t>
+          <t>adminLang {"acceptLanguage":"fr-FR"} -&gt; de</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>adminLangCookie lasts a year for the whole site</t>
+          <t>adminLang {} -&gt; de</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>useAt renders en</t>
+          <t>adminLangCookie lasts a year for the whole site</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>useAt renders de</t>
+          <t>useAt renders en</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>admin layout follows the cookie, then Accept-Language, then German</t>
+          <t>useAt renders de</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1339,17 +1339,17 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Staff roles</t>
+          <t>Admin lang</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>admin-roles.int.spec.ts</t>
+          <t>admin-lang.int.spec.ts</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>a Reviewer cannot do Administrator actions, and nothing changes</t>
+          <t>admin layout follows the cookie, then Accept-Language, then German</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>a Reviewer cannot change or delete an existing category or page</t>
+          <t>a Reviewer cannot do Administrator actions, and nothing changes</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>a Reviewer can read users and documents</t>
+          <t>a Reviewer cannot change or delete an existing category or page</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>a customer with no staff role gets 403 on every admin route; no session gets 401</t>
+          <t>a Reviewer can read users and documents</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>the last Administrator cannot be demoted</t>
+          <t>a customer with no staff role gets 403 on every admin route; no session gets 401</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>every route file under app/api/admin exports handlers built with adminRequest</t>
+          <t>the last Administrator cannot be demoted</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1501,17 +1501,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Security rule check</t>
+          <t>Staff roles</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>app-endpoints-wrapped.int.spec.ts</t>
+          <t>admin-roles.int.spec.ts</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>the owner-connection check catches a bypass (negative fixture)</t>
+          <t>every route file under app/api/admin exports handlers built with adminRequest</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>every route file under app/app-api exports handlers built with appRequest</t>
+          <t>the owner-connection check catches a bypass (negative fixture)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1555,17 +1555,17 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>App request wrapper</t>
+          <t>Security rule check</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>app-request.int.spec.ts</t>
+          <t>app-endpoints-wrapped.int.spec.ts</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>first contact creates the users row</t>
+          <t>every route file under app/app-api exports handlers built with appRequest</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>a forged cookie is 401 and touches nothing</t>
+          <t>first contact creates the users row</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>required auth without a cookie is 401</t>
+          <t>a forged cookie is 401 and touches nothing</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>optional auth without a cookie runs with no user</t>
+          <t>required auth without a cookie is 401</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>an unconfirmed email: 403 where auth is required, signed out where optional; never a users row</t>
+          <t>optional auth without a cookie runs with no user</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>a handler error rolls back and returns 500</t>
+          <t>an unconfirmed email: 403 where auth is required, signed out where optional; never a users row</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>a body over maxBodyBytes is 413 before the handler runs</t>
+          <t>a handler error rolls back and returns 500</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>user A cannot read user B through the wrapper</t>
+          <t>a body over maxBodyBytes is 413 before the handler runs</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>app_user cannot write staff columns of its own row</t>
+          <t>user A cannot read user B through the wrapper</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>first contact with a changed email updates the row</t>
+          <t>app_user cannot write staff columns of its own row</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>a second id with the same email gets 409 and no row is written</t>
+          <t>first contact with a changed email updates the row</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>a thrown 400 Response is returned unchanged</t>
+          <t>a second id with the same email gets 409 and no row is written</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1879,17 +1879,17 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Sign-up and session</t>
+          <t>App request wrapper</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>auth-cookie-flow.int.spec.ts</t>
+          <t>app-request.int.spec.ts</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>auth cookie flow signs up by REST, captures the cookie; /app-api/v1/me knows the session but refuses it until the email is confirmed</t>
+          <t>a thrown 400 Response is returned unchanged</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1906,17 +1906,17 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Categories</t>
+          <t>Sign-up and session</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>categories.int.spec.ts</t>
+          <t>auth-cookie-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>ordered by sort, "other services" always last, names in the requested language, anonymous allowed</t>
+          <t>auth cookie flow signs up by REST, captures the cookie; /app-api/v1/me knows the session but refuses it until the email is confirmed</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>an unknown language is 400</t>
+          <t>ordered by sort, "other services" always last, names in the requested language, anonymous allowed</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1960,17 +1960,17 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Concurrency</t>
+          <t>Categories</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>concurrency.int.spec.ts</t>
+          <t>categories.int.spec.ts</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>12 concurrent searches and 12 concurrent public pages all complete</t>
+          <t>an unknown language is 400</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Cron suspensions</t>
+          <t>Concurrency</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>cron-suspensions.int.spec.ts</t>
+          <t>concurrency.int.spec.ts</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>401 without the right secret, and when CRON_SECRET is unset</t>
+          <t>12 concurrent searches and 12 concurrent public pages all complete</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>ends a past suspension once: both columns cleared, one email; a future one is left alone</t>
+          <t>401 without the right secret, and when CRON_SECRET is unset</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2041,17 +2041,17 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Database migrations</t>
+          <t>Cron suspensions</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>db-migrations.int.spec.ts</t>
+          <t>cron-suspensions.int.spec.ts</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>migrates an empty database and classifies every table</t>
+          <t>ends a past suspension once: both columns cleared, one email; a future one is left alone</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>0008: person fields on users, suspensions by date, drafts allowed, notifications; applyRls succeeds</t>
+          <t>migrates an empty database and classifies every table</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>photos: a profile photo has no provider, a portfolio photo has one, one profile photo per person</t>
+          <t>0008: person fields on users, suspensions by date, drafts allowed, notifications; applyRls succeeds</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>0008 on a database with data: a suspended provider stays hidden, a published one without names or picture goes back to draft</t>
+          <t>photos: a profile photo has no provider, a portfolio photo has one, one profile photo per person</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -2149,17 +2149,17 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Emails</t>
+          <t>Database migrations</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>email.int.spec.ts</t>
+          <t>db-migrations.int.spec.ts</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>approval: one email in the user language with the document name and the deep link</t>
+          <t>0008 on a database with data: a suspended provider stays hidden, a published one without names or picture goes back to draft</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>rejection in German includes the note verbatim, escaped in the HTML</t>
+          <t>approval: one email in the user language with the document name and the deep link</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>without a key it only logs and records, and never throws</t>
+          <t>rejection in German includes the note verbatim, escaped in the HTML</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>outside tests without a key: one log line without recipient or body, and nothing kept in memory</t>
+          <t>without a key it only logs and records, and never throws</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>with a key it calls Resend with the full message; an { error } and a throw are logged, not thrown</t>
+          <t>outside tests without a key: one log line without recipient or body, and nothing kept in memory</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>an unexpected stored language falls back to German</t>
+          <t>with a key it calls Resend with the full message; an { error } and a throw are logged, not thrown</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -2311,17 +2311,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Uploads and document review</t>
+          <t>Emails</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>files-review.int.spec.ts</t>
+          <t>email.int.spec.ts</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>afterCommit: a handler that deletes a photo and then throws rolls back, the object stays</t>
+          <t>an unexpected stored language falls back to German</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>afterCommit: the object is deleted only after the commit</t>
+          <t>afterCommit: a handler that deletes a photo and then throws rolls back, the object stays</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>private_files and documents are isolated (RLS)</t>
+          <t>afterCommit: the object is deleted only after the commit</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>at most 10 unsubmitted uploads per user (409)</t>
+          <t>private_files and documents are isolated (RLS)</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>a decompression bomb and a header followed by garbage are 400; a later upload is accepted</t>
+          <t>at most 10 unsubmitted uploads per user (409)</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>EXIF is stripped from the stored JPEG</t>
+          <t>a decompression bomb and a header followed by garbage are 400; a later upload is accepted</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>alt over 200 characters is 400</t>
+          <t>EXIF is stripped from the stored JPEG</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>an unauthenticated upload is refused before the body is read</t>
+          <t>alt over 200 characters is 400</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>the body is read before the first-contact user row and the transaction exist</t>
+          <t>an unauthenticated upload is refused before the body is read</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>photos of a published provider are public, and unreadable once suspended</t>
+          <t>the body is read before the first-contact user row and the transaction exist</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>replacing the profile photo of a published profile works</t>
+          <t>photos of a published provider are public, and unreadable once suspended</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>deleting the profile photo while publishing never leaves a published profile without a photo</t>
+          <t>replacing the profile photo of a published profile works</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>two simultaneous submits for one requirement give one 201 and one 409</t>
+          <t>deleting the profile photo while publishing never leaves a published profile without a photo</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>the database refuses a second pending check for a requirement</t>
+          <t>two simultaneous submits for one requirement give one 201 and one 409</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>approval (staff SQL) makes a service with required documents offerable</t>
+          <t>the database refuses a second pending check for a requirement</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>the signed link carries X-Amz-Expires=300 and the public URL needs AWS_ENDPOINT</t>
+          <t>approval (staff SQL) makes a service with required documents offerable</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -2743,17 +2743,17 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Uploads</t>
+          <t>Uploads and document review</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>files.int.spec.ts</t>
+          <t>files-review.int.spec.ts</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>a profile photo is re-encoded to JPEG at most 1600 px and returned in contract shape</t>
+          <t>the signed link carries X-Amz-Expires=300 and the public URL needs AWS_ENDPOINT</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>a new profile photo replaces the old one and deletes its object</t>
+          <t>a profile photo is re-encoded to JPEG at most 1600 px and returned in contract shape</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>portfolio is limited to 12 (409), a non-image is 400, a missing kind is 400</t>
+          <t>a new profile photo replaces the old one and deletes its object</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>a portfolio photo needs a profile first (409); anonymous is 401; an oversize body is 413</t>
+          <t>portfolio is limited to 12 (409), a non-image is 400, a missing kind is 400</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>deleting a photo: another user gets 404, the owner 204 and the object and row are gone</t>
+          <t>a portfolio photo needs a profile first (409); anonymous is 401; an oversize body is 413</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>the profile photo of a published profile cannot be deleted (409)</t>
+          <t>deleting a photo: another user gets 404, the owner 204 and the object and row are gone</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>suspended_until is domain-only and photos are isolated</t>
+          <t>the profile photo of a published profile cannot be deleted (409)</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>files: a PDF goes to the private bucket, a non-PDF is 400, another user gets 404, the owner a signed link</t>
+          <t>suspended_until is domain-only and photos are isolated</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>documents also take JPEG, PNG and WEBP photos: re-encoded without metadata, at most 2400 px, stored with their type</t>
+          <t>files: a PDF goes to the private bucket, a non-PDF is 400, another user gets 404, the owner a signed link</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>a GIF and a text file renamed to .pdf are refused as documents</t>
+          <t>documents also take JPEG, PNG and WEBP photos: re-encoded without metadata, at most 2400 px, stored with their type</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>staff open an image document through the same signed link; it is served as an image</t>
+          <t>a GIF and a text file renamed to .pdf are refused as documents</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>a failed file insert removes the uploaded object</t>
+          <t>staff open an image document through the same signed link; it is served as an image</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>verifications: one pending check per requirement (409 removes the second file), bad input is 400</t>
+          <t>a failed file insert removes the uploaded object</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>the profile photo is private to its owner: another user cannot see it and gets 404 on delete; listPhotos puts it first</t>
+          <t>verifications: one pending check per requirement (409 removes the second file), bad input is 400</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -3121,17 +3121,17 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Website home page</t>
+          <t>Uploads</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>home-page.int.spec.ts</t>
+          <t>files.int.spec.ts</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>home page is German by default: headline, categories, store badges without links, no forbidden words</t>
+          <t>the profile photo is private to its owner: another user cannot see it and gets 404 on delete; listPhotos puts it first</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>home page switches to English with ?lang=en and falls back to German for unknown values</t>
+          <t>home page is German by default: headline, categories, store badges without links, no forbidden words</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>home page has per-language metadata with canonical and hreflang for every language</t>
+          <t>home page switches to English with ?lang=en and falls back to German for unknown values</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>site layout metadataBase makes canonical and hreflang absolute on the site url</t>
+          <t>home page has per-language metadata with canonical and hreflang for every language</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>site layout html lang follows the request language; unknown falls back to de</t>
+          <t>site layout metadataBase makes canonical and hreflang absolute on the site url</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>site layout footer links the four legal pages with catalogue labels in both languages</t>
+          <t>site layout html lang follows the request language; unknown falls back to de</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -3283,17 +3283,17 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Website home page</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>notifications.int.spec.ts</t>
+          <t>home-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>live and nothing else pending: "profile is live" email with the link, and one notification</t>
+          <t>site layout footer links the four legal pages with catalogue labels in both languages</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>the link of a German provider has no lang parameter</t>
+          <t>live and nothing else pending: "profile is live" email with the link, and one notification</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>live but another document is still missing: says the category service is visible, no notification</t>
+          <t>the link of a German provider has no lang parameter</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>the approved requirement is not enough for any service: plain approval, no notification</t>
+          <t>live but another document is still missing: says the category service is visible, no notification</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>draft profile: offline text, no notification</t>
+          <t>the approved requirement is not enough for any service: plain approval, no notification</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>suspended profile: suspended text with the date, no notification</t>
+          <t>draft profile: offline text, no notification</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>a requirement that was already approved: plain approval, no notification</t>
+          <t>suspended profile: suspended text with the date, no notification</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>rejection is unchanged</t>
+          <t>a requirement that was already approved: plain approval, no notification</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>GET /me lists the notification; PATCH dismissed hides it; another user gets 404</t>
+          <t>rejection is unchanged</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -3526,17 +3526,17 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>Database connection</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>owner-connection.int.spec.ts</t>
+          <t>notifications.int.spec.ts</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>inside a request transaction the owner connection `db` is a different connection (not app_user)</t>
+          <t>GET /me lists the notification; PATCH dismissed hides it; another user gets 404</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>two interleaved requests keep their own user id and role</t>
+          <t>inside a request transaction the owner connection `db` is a different connection (not app_user)</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -3580,17 +3580,17 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>Legal and info pages</t>
+          <t>Database connection</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>pages.int.spec.ts</t>
+          <t>owner-connection.int.spec.ts</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>pages tables every table is classified (pages and page_texts are public reference tables)</t>
+          <t>two interleaved requests keep their own user id and role</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>pages tables anonymous app requests read pages but cannot write them</t>
+          <t>pages tables every table is classified (pages and page_texts are public reference tables)</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>getPage returns the text in the language, falls back to de, hides drafts and unknown slugs</t>
+          <t>pages tables anonymous app requests read pages but cannot write them</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>getPage publishedPages lists published pages only</t>
+          <t>getPage returns the text in the language, falls back to de, hides drafts and unknown slugs</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>legal page by slug renders the Markdown body in both languages with the de fallback</t>
+          <t>getPage publishedPages lists published pages only</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>legal page by slug 404 for unknown and unpublished slugs</t>
+          <t>legal page by slug renders the Markdown body in both languages with the de fallback</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>legal page by slug metadata: title, canonical and hreflang for every language</t>
+          <t>legal page by slug 404 for unknown and unpublished slugs</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>legal page by slug escapes HTML in a body and drops unsafe links</t>
+          <t>legal page by slug metadata: title, canonical and hreflang for every language</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>renderMarkdown escapes raw html and keeps Markdown</t>
+          <t>legal page by slug escapes HTML in a body and drops unsafe links</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>renderMarkdown external links get rel="nofollow ugc"; protocol-relative and backslash paths are dropped</t>
+          <t>renderMarkdown escapes raw html and keeps Markdown</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -3850,17 +3850,17 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>Postcodes</t>
+          <t>Legal and info pages</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>postcodes.int.spec.ts</t>
+          <t>pages.int.spec.ts</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>imports the German file and looks up 01053 Dresden</t>
+          <t>renderMarkdown external links get rel="nofollow ugc"; protocol-relative and backslash paths are dropped</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>rejects a four-digit German code and an unknown one</t>
+          <t>imports the German file and looks up 01053 Dresden</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Berlin to Munich is about 504 km</t>
+          <t>rejects a four-digit German code and an unknown one</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -3931,17 +3931,17 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>Website provider page</t>
+          <t>Postcodes</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>provider-page.int.spec.ts</t>
+          <t>postcodes.int.spec.ts</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>public provider page German default: public name heading, category, price "ab 80,00 â‚¬", on request, place</t>
+          <t>Berlin to Munich is about 504 km</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>public provider page English with ?lang=en: "from â‚¬80.00"</t>
+          <t>public provider page German default: public name heading, category, price "ab 80,00 â‚¬", on request, place</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>public provider page escapes user content</t>
+          <t>public provider page English with ?lang=en: "from â‚¬80.00"</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>public provider page 404 for a hidden provider (draft) and an unknown slug</t>
+          <t>public provider page escapes user content</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>public provider page metadata: title, description, canonical and hreflang for every language</t>
+          <t>public provider page 404 for a hidden provider (draft) and an unknown slug</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>translate link is shown only when the texts are not in the page language</t>
+          <t>public provider page metadata: title, description, canonical and hreflang for every language</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>translate link ?translate=1 shows the translation with the AI label, noindex, canonical unchanged</t>
+          <t>translate link is shown only when the texts are not in the page language</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>translate link ?translate=1 without a key shows the original texts and the unavailable copy</t>
+          <t>translate link ?translate=1 shows the translation with the AI label, noindex, canonical unchanged</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>translate link translate=1 on texts already in the viewer language: original, no label, no model call</t>
+          <t>translate link ?translate=1 without a key shows the original texts and the unavailable copy</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -4174,17 +4174,17 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>Provider profile</t>
+          <t>Website provider page</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>provider-profile.int.spec.ts</t>
+          <t>provider-page.int.spec.ts</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>GET is null when there is no profile</t>
+          <t>translate link translate=1 on texts already in the viewer language: original, no label, no model call</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>PUT creates (201) and a later PUT edits (200); responses fit the contract</t>
+          <t>GET is null when there is no profile</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>an unknown postcode is 400 and changes nothing</t>
+          <t>PUT creates (201) and a later PUT edits (200); responses fit the contract</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>a partial first save never fails on business rules</t>
+          <t>an unknown postcode is 400 and changes nothing</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>status, slug and suspended in the body are ignored</t>
+          <t>a partial first save never fails on business rules</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>one user's profile is not visible to another</t>
+          <t>status, slug and suspended in the body are ignored</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>an invalid body is 400 with the contract error</t>
+          <t>one user's profile is not visible to another</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>an unconfirmed email gets 403 EMAIL_NOT_VERIFIED from PUT provider-profile and GET /me, and no users row</t>
+          <t>an invalid body is 400 with the contract error</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>PATCH /me checks its body with the contract: 400 Invalid input names the field; a valid patch saves</t>
+          <t>an unconfirmed email gets 403 EMAIL_NOT_VERIFIED from PUT provider-profile and GET /me, and no users row</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>a user without an address still gets a draft (the provider row default country applies)</t>
+          <t>PATCH /me checks its body with the contract: 400 Invalid input names the field; a valid patch saves</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>POST creates a draft with the postcode prefilled; again returns the same id; GET /me is fine</t>
+          <t>an address with only a postcode is stored and returned; a street without a postcode is refused; null clears it</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>missing: the empty draft lists the person-independent items, business adds two, saves shrink it, PUT carries it</t>
+          <t>a user without an address still gets a draft (the provider row default country applies)</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>publish of an incomplete draft is 409 with the list; complete publishes with public name Lena F.</t>
+          <t>POST creates a draft with the postcode prefilled; again returns the same id; GET /me is fine</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>a draft with every nullable field null is invisible in search and the sitemap</t>
+          <t>missing: the empty draft lists the person-independent items, business adds two, saves shrink it, PUT carries it</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>a draft created during a suspension cannot be published</t>
+          <t>publish of an incomplete draft is 409 with the list; complete publishes with public name Lena F.</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>the draft prefills the postcode only when it is a known one</t>
+          <t>a draft with every nullable field null is invisible in search and the sitemap</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>a live profile cannot be emptied by a save: 409 with the missing list, nothing changed</t>
+          <t>a draft created during a suspension cannot be published</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>a provider whose names are missing cannot publish: missing lists name</t>
+          <t>the draft prefills the postcode only when it is a known one</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>the draft's postcode lookup uses the owner's stored country</t>
+          <t>a live profile cannot be emptied by a save: 409 with the missing list, nothing changed</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -4687,17 +4687,17 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>Public provider data</t>
+          <t>Provider profile</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>provider-public.int.spec.ts</t>
+          <t>provider-profile.int.spec.ts</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>a published provider page: contract shape, place, photo urls, only offerable services</t>
+          <t>a provider whose names are missing cannot publish: missing lists name</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -4714,17 +4714,17 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>Public provider data</t>
+          <t>Provider profile</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>provider-public.int.spec.ts</t>
+          <t>provider-profile.int.spec.ts</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>404 when not visible: unknown, draft, or no offerable service</t>
+          <t>the draft's postcode lookup uses the owner's stored country</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>a draft page is a 404 for its own owner too</t>
+          <t>a published provider page: contract shape, place, photo urls, only offerable services</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>unknown language is 400</t>
+          <t>404 when not visible: unknown, draft, or no offerable service</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>anonymous: the page carries the owner's profile photo and the public name, no display name</t>
+          <t>a draft page is a 404 for its own owner too</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -4822,17 +4822,17 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>Translate endpoint</t>
+          <t>Public provider data</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>provider-translation.int.spec.ts</t>
+          <t>provider-public.int.spec.ts</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>returns translated texts in the page shape</t>
+          <t>unknown language is 400</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -4849,17 +4849,17 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>Translate endpoint</t>
+          <t>Public provider data</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>provider-translation.int.spec.ts</t>
+          <t>provider-public.int.spec.ts</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>a draft or suspended provider -&gt; 404, no call</t>
+          <t>anonymous: the page carries the owner's profile photo and the public name, no display name</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>unknown lang -&gt; 400</t>
+          <t>returns translated texts in the page shape</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>service failure -&gt; 503 and nothing stored</t>
+          <t>a draft or suspended provider -&gt; 404, no call</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>a logged-in caller is counted under the user id</t>
+          <t>unknown lang -&gt; 400</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>the provider endpoint reports translatable per viewer language</t>
+          <t>service failure -&gt; 503 and nothing stored</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>accepts no text from the client</t>
+          <t>a logged-in caller is counted under the user id</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>fails closed without a usable secret: 503, no counter row, no model call</t>
+          <t>the provider endpoint reports translatable per viewer language</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -5038,17 +5038,17 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>Site and admin routing</t>
+          <t>Translate endpoint</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>proxy.int.spec.ts</t>
+          <t>provider-translation.int.spec.ts</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>/admin and below go through the auth middleware</t>
+          <t>accepts no text from the client</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
@@ -5065,17 +5065,17 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>Site and admin routing</t>
+          <t>Translate endpoint</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>proxy.int.spec.ts</t>
+          <t>provider-translation.int.spec.ts</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>/administrator or a page slug starting with admin is a site path with x-lang</t>
+          <t>fails closed without a usable secret: 503, no counter row, no model call</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -5092,17 +5092,17 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>Public name</t>
+          <t>Site and admin routing</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>public-name.int.spec.ts</t>
+          <t>proxy.int.spec.ts</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>publicNameFor: business name, else first name and surname initial</t>
+          <t>/admin and below go through the auth middleware</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -5119,17 +5119,17 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>Public name</t>
+          <t>Site and admin routing</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>public-name.int.spec.ts</t>
+          <t>proxy.int.spec.ts</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>slugify transliterates umlauts and strips the rest</t>
+          <t>/administrator or a page slug starting with admin is a site path with x-lang</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>public name and slug are unique and stable</t>
+          <t>publicNameFor: business name, else first name and surname initial</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>an individual without names cannot publish; with names the public name follows</t>
+          <t>slugify transliterates umlauts and strips the rest</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>first contact does not copy the session name: the person sets their own names</t>
+          <t>public name and slug are unique and stable</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>a rename of the person changes the public name of their provider profile</t>
+          <t>an individual without names cannot publish; with names the public name follows</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -5254,17 +5254,17 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>Publish and unpublish</t>
+          <t>Public name</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>publish-flow.int.spec.ts</t>
+          <t>public-name.int.spec.ts</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>the first-time flow: refused until photo and service exist, then published, then unpublished</t>
+          <t>first contact does not copy the session name: the person sets their own names</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -5281,17 +5281,17 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>Publish and unpublish</t>
+          <t>Public name</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>publish-flow.int.spec.ts</t>
+          <t>public-name.int.spec.ts</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>a postcode-less profile is refused until a postcode is saved</t>
+          <t>a rename of the person changes the public name of their provider profile</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>a suspended profile cannot publish (409)</t>
+          <t>the first-time flow: refused until photo and service exist, then published, then unpublished</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>RLS: published and not suspended is public, drafts and suspended are not</t>
+          <t>a postcode-less profile is refused until a postcode is saved</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>RLS: another user cannot change or add to a provider; domain-only columns are closed</t>
+          <t>a suspended profile cannot publish (409)</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>RLS: set_provider_* touch only the caller's own profile</t>
+          <t>RLS: published and not suspended is public, drafts and suspended are not</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>RLS: documents are private and the verdict is staff-only</t>
+          <t>RLS: another user cannot change or add to a provider; domain-only columns are closed</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>offerableServiceIds: services whose required documents are all approved</t>
+          <t>RLS: set_provider_* touch only the caller's own profile</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>a user suspension that has ended no longer blocks publishing; a running one does</t>
+          <t>RLS: documents are private and the verdict is staff-only</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
@@ -5497,17 +5497,17 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>Staff check</t>
+          <t>Publish and unpublish</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>require-staff.int.spec.ts</t>
+          <t>publish-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>an active admin passes</t>
+          <t>offerableServiceIds: services whose required documents are all approved</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -5524,17 +5524,17 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>Staff check</t>
+          <t>Publish and unpublish</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>require-staff.int.spec.ts</t>
+          <t>publish-flow.int.spec.ts</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>a suspended admin gets 403</t>
+          <t>a user suspension that has ended no longer blocks publishing; a running one does</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>an expired suspension no longer blocks</t>
+          <t>an active admin passes</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -5578,17 +5578,17 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>Row-level security</t>
+          <t>Staff check</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>rls-providers.int.spec.ts</t>
+          <t>require-staff.int.spec.ts</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>another user cannot update or delete a service or a reference (rowCount 0, rows unchanged)</t>
+          <t>a suspended admin gets 403</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
@@ -5605,17 +5605,17 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>Row-level security</t>
+          <t>Staff check</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>rls-providers.int.spec.ts</t>
+          <t>require-staff.int.spec.ts</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>another user cannot insert a service or a reference for my provider</t>
+          <t>an expired suspension no longer blocks</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>the owner cannot move a service to another provider</t>
+          <t>another user cannot update or delete a service or a reference (rowCount 0, rows unchanged)</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>offerableServiceIds and missingRequirements are identical through tx and the owner db</t>
+          <t>another user cannot insert a service or a reference for my provider</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>a stranger asking about a draft provider gets empty answers; the owner still gets the full ones</t>
+          <t>the owner cannot move a service to another provider</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>a service with a category alone (no price type yet) is never offerable, not even to its owner</t>
+          <t>offerableServiceIds and missingRequirements are identical through tx and the owner db</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>slugify strips accents</t>
+          <t>a stranger asking about a draft provider gets empty answers; the owner still gets the full ones</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>rls.int.spec.ts</t>
+          <t>rls-providers.int.spec.ts</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>app_user cannot read a private table row of another user</t>
+          <t>a service with a category alone (no price type yet) is never offerable, not even to its owner</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>rls.int.spec.ts</t>
+          <t>rls-providers.int.spec.ts</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>public reference tables are readable by app_user and not writable</t>
+          <t>slugify strips accents</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>a person's picture is private until the owner's provider is published and not suspended</t>
+          <t>app_user cannot read a private table row of another user</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>notifications: the owner reads and marks own rows; another user sees none, cannot insert or change kind</t>
+          <t>public reference tables are readable by app_user and not writable</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
@@ -5875,17 +5875,17 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Row-level security</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>search.int.spec.ts</t>
+          <t>rls.int.spec.ts</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>radius edge and remote providers</t>
+          <t>a person's picture is private until the owner's provider is published and not suspended</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
@@ -5902,17 +5902,17 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Row-level security</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>search.int.spec.ts</t>
+          <t>rls.int.spec.ts</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>a remote provider more than 200 km away is found, without a distance</t>
+          <t>notifications: the owner reads and marks own rows; another user sees none, cannot insert or change kind</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>a draft is invisible to its owner too</t>
+          <t>radius edge and remote providers</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>distance is whole km, at least 1, hidden for remote providers outside the radius</t>
+          <t>a remote provider more than 200 km away is found, without a distance</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>a draft, a suspended or a provider without an offerable service never appears</t>
+          <t>a draft is invisible to its owner too</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>category filter and q (public name and skills, case-insensitive)</t>
+          <t>distance is whole km, at least 1, hidden for remote providers outside the radius</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>bad input is 400: unknown postcode, bad format, unknown country, unknown language, bad page</t>
+          <t>a draft, a suspended or a provider without an offerable service never appears</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>paging: 20 per page and hasMore</t>
+          <t>category filter and q (public name and skills, case-insensitive)</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>anonymous: the card carries the owner's profile photo and the public name, no display name</t>
+          <t>bad input is 400: unknown postcode, bad format, unknown country, unknown language, bad page</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>a provider whose only service has no price type is neither found nor has a public page</t>
+          <t>paging: 20 per page and hasMore</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>a fixed service without a price is not found in its category</t>
+          <t>anonymous: the card carries the owner's profile photo and the public name, no display name</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
@@ -6172,17 +6172,17 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>search.int.spec.ts</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>categories seed is idempotent: 14 categories, both names, babysitting needs a police certificate</t>
+          <t>a provider whose only service has no price type is neither found nor has a public page</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
@@ -6199,17 +6199,17 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>Seeds</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>seeds.int.spec.ts</t>
+          <t>search.int.spec.ts</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>postcode import upserts: a second run leaves the same count</t>
+          <t>a fixed service without a price is not found in its category</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>the dev guard needs the dev branch AND the dev database host</t>
+          <t>categories seed is idempotent: 14 categories, both names, babysitting needs a police certificate</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>loadSeedData reads the git-ignored list or the committed example, and rejects a broken file</t>
+          <t>postcode import upserts: a second run leaves the same count</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>seedTestUsers itself refuses outside dev, before touching anything</t>
+          <t>the dev guard needs the dev branch AND the dev database host</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>builds the test users through the domain: published providers with photo, services, public names, verified; a rerun adds nothing</t>
+          <t>loadSeedData reads the git-ignored list or the committed example, and rejects a broken file</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>a run that crashed after the services (no photo, not published) resumes without adding the services twice</t>
+          <t>seedTestUsers itself refuses outside dev, before touching anything</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>placeholder photos: gives a published profile without a photo one; elsewhere needs the typed yes</t>
+          <t>builds the test users through the domain: published providers with photo, services, public names, verified; a rerun adds nothing</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>neonAuth retries a 429, then succeeds</t>
+          <t>a run that crashed after the services (no photo, not published) resumes without adding the services twice</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>neonAuth signs in when the email already exists</t>
+          <t>placeholder photos: gives a published profile without a photo one; elsewhere needs the typed yes</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>neonAuth surfaces any other sign-up failure without falling back to sign-in</t>
+          <t>neonAuth retries a 429, then succeeds</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
@@ -6469,17 +6469,17 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>Services and references</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>services-references.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>a service needs a profile first (409)</t>
+          <t>neonAuth signs in when the email already exists</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
@@ -6496,17 +6496,17 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>Services and references</t>
+          <t>Seeds</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>services-references.int.spec.ts</t>
+          <t>seeds.int.spec.ts</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>create, list and patch a service; shapes fit the contract</t>
+          <t>neonAuth surfaces any other sign-up failure without falling back to sign-in</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>on-request has no price, even when one is sent</t>
+          <t>a service needs a profile first (409)</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>bad service input: no price, three decimals, unknown category are 400</t>
+          <t>create, list and patch a service; shapes fit the contract</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>a service in a category with required documents waits for approval</t>
+          <t>on-request has no price, even when one is sent</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>user A cannot edit or delete user B's service</t>
+          <t>bad service input: no price, three decimals, unknown category are 400</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>references are capped at 2 (409), can be patched and deleted</t>
+          <t>a service in a category with required documents waits for approval</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>a service with a category alone is saved, not offerable, and a patch accepts the partial shape</t>
+          <t>user A cannot edit or delete user B's service</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>the price type and the price save in either order, each as its own one-field save</t>
+          <t>references are capped at 2 (409), can be patched and deleted</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>a fixed service without a price is not offerable, with a price it is; on-request clears the price</t>
+          <t>a service with a category alone is saved, not offerable, and a patch accepts the partial shape</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>the app sends a category alone, then one field per save: currency defaults to EUR, title to the category name</t>
+          <t>the price type and the price save in either order, each as its own one-field save</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>add and update answer with waitingFor and visibleInSearch, like the list</t>
+          <t>a fixed service without a price is not offerable, with a price it is; on-request clears the price</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
@@ -6793,17 +6793,17 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>Sitemaps</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>sitemaps.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>providers sitemap lists only visible providers</t>
+          <t>the app sends a category alone, then one field per save: currency defaults to EUR, title to the category name</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
@@ -6820,17 +6820,17 @@
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>Sitemaps</t>
+          <t>Services and references</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>sitemaps.int.spec.ts</t>
+          <t>services-references.int.spec.ts</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>pages sitemap lists the home page and published pages only</t>
+          <t>add and update answer with waitingFor and visibleInSearch, like the list</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>robots.txt allows the site, keeps the admin out and points at both sitemaps</t>
+          <t>providers sitemap lists only visible providers</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
@@ -6874,17 +6874,17 @@
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>Smoke test</t>
+          <t>Sitemaps</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>smoke.int.spec.ts</t>
+          <t>sitemaps.int.spec.ts</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>connects to the test database and sees PostGIS</t>
+          <t>pages sitemap lists the home page and published pages only</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
@@ -6901,17 +6901,17 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>Test database guard</t>
+          <t>Sitemaps</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>test-guard.int.spec.ts</t>
+          <t>sitemaps.int.spec.ts</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>the test guard refuses a non-local or non-test URL</t>
+          <t>robots.txt allows the site, keeps the admin out and points at both sitemaps</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
@@ -6928,17 +6928,17 @@
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Smoke test</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>smoke.int.spec.ts</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>translate stores translations and serves the second request from the store without a call</t>
+          <t>connects to the test database and sees PostGIS</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
@@ -6955,17 +6955,17 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>Translate</t>
+          <t>Test database guard</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>translate.int.spec.ts</t>
+          <t>test-guard.int.spec.ts</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>translate an edited text is re-translated, the rest comes from the store</t>
+          <t>the test guard refuses a non-local or non-test URL</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>translate texts already in the target language are returned unchanged without a call</t>
+          <t>translate stores translations and serves the second request from the store without a call</t>
         </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>translate a malformed or incomplete model answer stores nothing and throws TranslationUnavailable</t>
+          <t>translate an edited text is re-translated, the rest comes from the store</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>translate a non-2xx answer throws TranslationUnavailable</t>
+          <t>translate texts already in the target language are returned unchanged without a call</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>translate line breaks survive</t>
+          <t>translate a malformed or incomplete model answer stores nothing and throws TranslationUnavailable</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>translate no key -&gt; TranslationUnavailable without a call</t>
+          <t>translate a non-2xx answer throws TranslationUnavailable</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>translate the 31st AI call within an hour for one client key -&gt; TranslationUnavailable</t>
+          <t>translate line breaks survive</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>translate the limit boundary: the 30th call passes, the 31st is refused</t>
+          <t>translate no key -&gt; TranslationUnavailable without a call</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>translate a timeout -&gt; TranslationUnavailable</t>
+          <t>translate the 31st AI call within an hour for one client key -&gt; TranslationUnavailable</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>translate concurrent translations of the same page store one row per text</t>
+          <t>translate the limit boundary: the 30th call passes, the 31st is refused</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>translate writes through the request transaction and commits with it</t>
+          <t>translate a timeout -&gt; TranslationUnavailable</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>translate the default timeout is 12 seconds</t>
+          <t>translate concurrent translations of the same page store one row per text</t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>translate French and Afrikaans texts are flagged and sent to the model, in either viewer language</t>
+          <t>translate writes through the request transaction and commits with it</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>translate a page the detector cannot classify is translated when long enough, left alone when short</t>
+          <t>translate the default timeout is 12 seconds</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>translate a German profile of short skills and titles needs no translation for de but does for en</t>
+          <t>translate French and Afrikaans texts are flagged and sent to the model, in either viewer language</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>translate a Markdown-fenced answer parses; the request carries max_tokens</t>
+          <t>translate a page the detector cannot classify is translated when long enough, left alone when short</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>translate an empty string from the model stores nothing</t>
+          <t>translate a German profile of short skills and titles needs no translation for de but does for en</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>translate counter rows older than 24 hours are deleted; recent ones stay</t>
+          <t>translate a Markdown-fenced answer parses; the request carries max_tokens</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>translate anonymous client keys are salted hashes, never the raw IP</t>
+          <t>translate an empty string from the model stores nothing</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>translate textsOf picks the translatable fields of a profile</t>
+          <t>translate counter rows older than 24 hours are deleted; recent ones stay</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>translate needsTranslation is false for a page entirely in the viewer language and true for a mixed page</t>
+          <t>translate anonymous client keys are salted hashes, never the raw IP</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>translation tables are insert-only for app_user anonymous callers can insert and read, never update or delete</t>
+          <t>translate textsOf picks the translatable fields of a profile</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
@@ -7549,22 +7549,22 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>server errors land on the right field</t>
+          <t>translate needsTranslation is false for a page entirely in the viewer language and true for a mixed page</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr">
@@ -7576,22 +7576,22 @@
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Translate</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>translate.int.spec.ts</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>withItem adds a trimmed new skill or strength once and ignores blanks</t>
+          <t>translation tables are insert-only for app_user anonymous callers can insert and read, never update or delete</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E260" s="4" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>the form-level error shows unless every server error has an inline slot</t>
+          <t>texts come from the shared catalogue, in the chosen language, with placeholders filled</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>service and reference validation</t>
+          <t>the translate button texts exist in both languages</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>every missing item the publish route can return has de and en text</t>
+          <t>errorText maps the auth server codes to catalogue messages</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>the service body names the category by id and the currency, as the server expects</t>
+          <t>errorText maps the app API strings</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>a 400 "Invalid input" marks each named field</t>
+          <t>docText maps known document codes and passes unknown ones through</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
@@ -7738,17 +7738,17 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Pending navigation</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>profile-form.test.ts</t>
+          <t>pending-navigation.test.ts</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>live means published and not suspended now (the server rule of listServices)</t>
+          <t>set, consume once, then nothing</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
@@ -7765,17 +7765,17 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>Share profile</t>
+          <t>Pending navigation</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>share-profile.test.ts</t>
+          <t>pending-navigation.test.ts</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>the provider page url carries the language only when it is not the default</t>
+          <t>clearPending drops it (sign-out)</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
@@ -7792,17 +7792,17 @@
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>Share profile</t>
+          <t>Pending navigation</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>share-profile.test.ts</t>
+          <t>pending-navigation.test.ts</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>shareProfile passes the url and the text in the given language</t>
+          <t>readyToNavigate: only with a target and a visible profile tab</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
@@ -7819,17 +7819,17 @@
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>Address fields</t>
+          <t>Pending navigation</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>address-fields.test.ts</t>
+          <t>pending-navigation.test.ts</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>toAddress: empty is null (clears), complete is DE, partial is undefined</t>
+          <t>the layout order: not ready keeps the target, ready consumes it once</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
@@ -7846,17 +7846,17 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Share profile</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>share-profile.test.ts</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>texts come from the shared catalogue, in the chosen language, with placeholders filled</t>
+          <t>the provider page url carries the language only when it is not the default</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
@@ -7873,17 +7873,17 @@
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Share profile</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>share-profile.test.ts</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>the translate button texts exist in both languages</t>
+          <t>shareProfile passes the url and the text in the given language</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
@@ -7900,17 +7900,17 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>errorText maps the auth server codes to catalogue messages</t>
+          <t>creates the draft, reloads /me, then sets the target, in that order</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
@@ -7927,17 +7927,17 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>errorText maps the app API strings</t>
+          <t>welcome passes through</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
@@ -7954,17 +7954,17 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>docText maps known document codes and passes unknown ones through</t>
+          <t>a failure returns the error text and does not navigate</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
@@ -7981,17 +7981,17 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>prices follow the website rules in German and English</t>
+          <t>a second call while one runs does nothing extra</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
@@ -8008,17 +8008,17 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>distance shows km, remote or nothing</t>
+          <t>no target when /me says the person is not a provider</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
@@ -8035,17 +8035,17 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Start offering</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>start-offering.test.ts</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>search path leaves out empty filters and trims text</t>
+          <t>a sign-out during the run leaves no target behind</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
@@ -8062,17 +8062,17 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Address fields</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>format.test.ts</t>
+          <t>address-fields.test.ts</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>photoSrc loads only absolute http(s) URLs, never a server-relative /api path</t>
+          <t>toAddress: empty is null (clears), a postcode alone is enough, street or city without postcode is undefined</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>signUp posts email, password and name and stores the session cookie</t>
+          <t>server errors land on the right field</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>signIn posts email and password and returns the user</t>
+          <t>withItem adds a trimmed new skill or strength once and ignores blanks</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>a refused sign-in throws the server code, which maps to a catalogue message</t>
+          <t>the form-level error shows unless every server error has an inline slot</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>signOut forgets the session at once and tells the server with the old cookie</t>
+          <t>service and reference validation</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
@@ -8202,12 +8202,12 @@
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>signOut offline still signs out</t>
+          <t>every missing item the publish route can return has de and en text</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
@@ -8229,12 +8229,12 @@
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>session reads get-session with the cookie; no cookie means null without a request</t>
+          <t>the service body names the category by id and the currency, as the server expects</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>session throws on a network error (the app offers a retry, not the login)</t>
+          <t>a 400 "Invalid input" marks each named field</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>profile-form.test.ts</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>sendVerificationCode asks for an email-verification code</t>
+          <t>live means published and not suspended now (the server rule of listServices)</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>verifyEmail sends the code as otp, stores the new session and returns the user</t>
+          <t>preparePhoto keeps the long side at 1600 px</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>requestPasswordReset asks for a reset code</t>
+          <t>tooLarge is true above 4_434_464 bytes</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
@@ -8364,12 +8364,12 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>resetPassword sends email, code and the new password</t>
+          <t>pickPhoto cancelled is null</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>a wrong code throws INVALID_OTP, shown as the code message</t>
+          <t>pickPhoto a refused permission is denied, not cancelled</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>auth.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>signUp and signIn start without an old stored session</t>
+          <t>pickDocument offers PDFs and the image types the server accepts, from any file source</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>pick.test.ts</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>a failed check after the upload deletes the uploaded file and reports the original error</t>
+          <t>pickDocument cancelled is null</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
@@ -8472,12 +8472,12 @@
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>a successful submit deletes nothing</t>
+          <t>prices follow the website rules in German and English</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
@@ -8499,12 +8499,12 @@
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>my-profile.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>a failing clean-up does not hide the original error</t>
+          <t>distance shows km, remote or nothing</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>preparePhoto keeps the long side at 1600 px</t>
+          <t>search path leaves out empty filters and trims text</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>format.test.ts</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>tooLarge is true above 4_434_464 bytes</t>
+          <t>photoSrc loads only absolute http(s) URLs, never a server-relative /api path</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>pickPhoto cancelled is null</t>
+          <t>loading -&gt; signed in -&gt; signed out</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>pickPhoto a refused permission is denied, not cancelled</t>
+          <t>an unverified email never counts as signed in: sign-in sends a code and asks for it</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
@@ -8634,12 +8634,12 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>pickDocument offers PDFs and the image types the server accepts, from any file source</t>
+          <t>a server that refuses unverified sign-ins (EMAIL_NOT_VERIFIED) also leads to the code screen</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>pick.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>pickDocument cancelled is null</t>
+          <t>sign-up creates the account and sends the code; the right code signs in and saves the account name</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
@@ -8683,17 +8683,17 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>Pending signup</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>pending-signup.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>the pending record round-trips and clears</t>
+          <t>a wrong code throws and keeps signed out</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -8715,12 +8715,12 @@
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>applyTexts swaps only the translatable fields and keeps names, prices and photos</t>
+          <t>a failed login rejects and keeps signed out; a server error on load means signed out</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>applyTexts matches services and references by id and leaves unknown ones untouched</t>
+          <t>a network error on load sets offline (not signed out); retry recovers</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>translation.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>applyTexts keeps line breaks</t>
+          <t>onUnauthorized from the API client signs the user out</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
@@ -8796,12 +8796,12 @@
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>sends the stored cookie and stores a new set-cookie</t>
+          <t>switching the language also saves it for emails, but only while signed in</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>a single joined set-cookie header (no getSetCookie) is split into its cookies</t>
+          <t>verify finishes the sign-up: names and address, then the picture, then the record is cleared; returns the tick</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>clears the session on 401</t>
+          <t>a failed upload keeps the record; loadSession retries it once and clears it</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>a 401 without a stored session does not call onUnauthorized</t>
+          <t>loadSession without a record or while signed out does not finish a sign-up</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>every request names the app origin and leaves the platform cookie store out</t>
+          <t>a record for another email is dropped and applies nothing</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>a 409 with error and missing throws ApiError with code and missing</t>
+          <t>a failed PATCH keeps the full record</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>a 400 "Invalid input" lists the fields named by its issues</t>
+          <t>a postcode the server calls invalid does not block the names: they are saved without the address</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>a network failure throws ApiError(0, network)</t>
+          <t>after the PATCH succeeded, a failed upload keeps only email, tick and picture; the retry does not PATCH again</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
@@ -9012,12 +9012,12 @@
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>a server that never answers fails as network after the time limit</t>
+          <t>a picture whose cached file is gone is dropped and the record cleared</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>saves have no time limit: a slow save that succeeds is not reported as a failure</t>
+          <t>sign-up keeps the record for the code step; a failed sign-up leaves none</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>use-session.test.ts</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>updateMe PATCHes the account name</t>
+          <t>finishing a sign-up reloads /me so the home nudge sees the new picture; nothing to finish, nothing to reload</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -9093,12 +9093,12 @@
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>upload sends multipart with the cookie and no time limit</t>
+          <t>signUp posts email, password and name and stores the session cookie</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>upload sends the file bytes with its name and type, not a bare { uri } object</t>
+          <t>signIn posts email and password and returns the user</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -9147,12 +9147,12 @@
       </c>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>a file the phone cannot open is "File unreadable", not a network error, and nothing is sent</t>
+          <t>a refused sign-in throws the server code, which maps to a catalogue message</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>upload maps a 413 to ApiError "File too large"</t>
+          <t>signOut forgets the session at once and tells the server with the old cookie</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>upload maps a network failure to ApiError network and does not retry</t>
+          <t>signOut offline still signs out</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>a store that cannot be read (Keystore failure) sends the request without a cookie</t>
+          <t>session reads get-session with the cookie; no cookie means null without a request</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>a cookie that cannot be saved does not fail a request the server already carried out</t>
+          <t>session throws on a network error (the app offers a retry, not the login)</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
@@ -9282,12 +9282,12 @@
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>a malformed Set-Cookie line without "=" is skipped</t>
+          <t>sendVerificationCode asks for an email-verification code</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>client.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>updateMe sends the one-field name as first and last name, split at the last space</t>
+          <t>verifyEmail sends the code as otp, stores the new session and returns the user</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
@@ -9336,12 +9336,12 @@
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>loading -&gt; signed in -&gt; signed out</t>
+          <t>requestPasswordReset asks for a reset code</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>an unverified email never counts as signed in: sign-in sends a code and asks for it</t>
+          <t>resetPassword sends email, code and the new password</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>a server that refuses unverified sign-ins (EMAIL_NOT_VERIFIED) also leads to the code screen</t>
+          <t>a wrong code throws INVALID_OTP, shown as the code message</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -9417,12 +9417,12 @@
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>auth.test.ts</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>sign-up creates the account and sends the code; the right code signs in and saves the account name</t>
+          <t>signUp and signIn start without an old stored session</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>a wrong code throws and keeps signed out</t>
+          <t>applyTexts swaps only the translatable fields and keeps names, prices and photos</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>a failed login rejects and keeps signed out; a server error on load means signed out</t>
+          <t>applyTexts matches services and references by id and leaves unknown ones untouched</t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>translation.test.ts</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>a network error on load sets offline (not signed out); retry recovers</t>
+          <t>applyTexts keeps line breaks</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>onUnauthorized from the API client signs the user out</t>
+          <t>a failed check after the upload deletes the uploaded file and reports the original error</t>
         </is>
       </c>
       <c r="D332" s="4" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>switching the language also saves it for emails, but only while signed in</t>
+          <t>a successful submit deletes nothing</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>my-profile.test.ts</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>verify finishes the sign-up: names and address, then the picture, then the record is cleared; returns the tick</t>
+          <t>a failing clean-up does not hide the original error</t>
         </is>
       </c>
       <c r="D334" s="4" t="inlineStr">
@@ -9601,17 +9601,17 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Pending signup</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>pending-signup.test.ts</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>a failed upload keeps the record; loadSession retries it once and clears it</t>
+          <t>the pending record round-trips and clears</t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
@@ -9628,17 +9628,17 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Serial create</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>serial-create.test.ts</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>loadSession without a record or while signed out does not finish a sign-up</t>
+          <t>choosing twice before the create returns creates once, then updates</t>
         </is>
       </c>
       <c r="D336" s="4" t="inlineStr">
@@ -9655,17 +9655,17 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Serial create</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>serial-create.test.ts</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>a record for another email is dropped and applies nothing</t>
+          <t>an existing id is only updated</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
@@ -9682,17 +9682,17 @@
     <row r="338">
       <c r="A338" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B338" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C338" s="4" t="inlineStr">
         <is>
-          <t>a failed PATCH keeps the full record</t>
+          <t>two quick changes become one request with the last value</t>
         </is>
       </c>
       <c r="D338" s="4" t="inlineStr">
@@ -9709,17 +9709,17 @@
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B339" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>after the PATCH succeeded, a failed upload keeps only email, tick and picture; the retry does not PATCH again</t>
+          <t>flush saves immediately and nothing is sent twice</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
@@ -9736,17 +9736,17 @@
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B340" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C340" s="4" t="inlineStr">
         <is>
-          <t>a picture whose cached file is gone is dropped and the record cleared</t>
+          <t>a rejected save marks error and retry resends the same value</t>
         </is>
       </c>
       <c r="D340" s="4" t="inlineStr">
@@ -9763,17 +9763,17 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>sign-up keeps the record for the code step; a failed sign-up leaves none</t>
+          <t>a change typed while a save is in flight is sent after it, in order</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
@@ -9790,17 +9790,17 @@
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use field save</t>
         </is>
       </c>
       <c r="B342" s="4" t="inlineStr">
         <is>
-          <t>use-session.test.ts</t>
+          <t>use-field-save.test.ts</t>
         </is>
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>finishing a sign-up reloads /me so the home nudge sees the new picture; nothing to finish, nothing to reload</t>
+          <t>dispose sends a pending change so nothing typed is lost</t>
         </is>
       </c>
       <c r="D342" s="4" t="inlineStr">
@@ -9817,17 +9817,17 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>Picture nudge</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>picture-nudge.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>the dismissed-nudge key is per user, so a second account on the device still sees it</t>
+          <t>sends the stored cookie and stores a new set-cookie</t>
         </is>
       </c>
       <c r="D343" s="4" t="inlineStr">
@@ -9844,17 +9844,17 @@
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B344" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>two quick changes become one request with the last value</t>
+          <t>a single joined set-cookie header (no getSetCookie) is split into its cookies</t>
         </is>
       </c>
       <c r="D344" s="4" t="inlineStr">
@@ -9871,17 +9871,17 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C345" s="4" t="inlineStr">
         <is>
-          <t>flush saves immediately and nothing is sent twice</t>
+          <t>clears the session on 401</t>
         </is>
       </c>
       <c r="D345" s="4" t="inlineStr">
@@ -9898,17 +9898,17 @@
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B346" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C346" s="4" t="inlineStr">
         <is>
-          <t>a rejected save marks error and retry resends the same value</t>
+          <t>a 401 without a stored session does not call onUnauthorized</t>
         </is>
       </c>
       <c r="D346" s="4" t="inlineStr">
@@ -9925,17 +9925,17 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>a change typed while a save is in flight is sent after it, in order</t>
+          <t>every request names the app origin and leaves the platform cookie store out</t>
         </is>
       </c>
       <c r="D347" s="4" t="inlineStr">
@@ -9952,17 +9952,17 @@
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>Use field save</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B348" s="4" t="inlineStr">
         <is>
-          <t>use-field-save.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C348" s="4" t="inlineStr">
         <is>
-          <t>dispose sends a pending change so nothing typed is lost</t>
+          <t>a 409 with error and missing throws ApiError with code and missing</t>
         </is>
       </c>
       <c r="D348" s="4" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>match.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>matches ignores case and accents, and an empty query matches everything</t>
+          <t>a 400 "Invalid input" lists the fields named by its issues</t>
         </is>
       </c>
       <c r="D349" s="4" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="B350" s="4" t="inlineStr">
         <is>
-          <t>auth-layout.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C350" s="4" t="inlineStr">
         <is>
-          <t>logged-out landing route is login</t>
+          <t>a network failure throws ApiError(0, network)</t>
         </is>
       </c>
       <c r="D350" s="4" t="inlineStr">
@@ -10038,12 +10038,12 @@
       </c>
       <c r="B351" s="4" t="inlineStr">
         <is>
-          <t>auth-layout.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C351" s="4" t="inlineStr">
         <is>
-          <t>no test files inside src/app (each file there becomes a screen)</t>
+          <t>a server that never answers fails as network after the time limit</t>
         </is>
       </c>
       <c r="D351" s="4" t="inlineStr">
@@ -10060,17 +10060,17 @@
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>Stale guard</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B352" s="4" t="inlineStr">
         <is>
-          <t>stale-guard.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C352" s="4" t="inlineStr">
         <is>
-          <t>a response older than one already applied is ignored</t>
+          <t>saves have no time limit: a slow save that succeeds is not reported as a failure</t>
         </is>
       </c>
       <c r="D352" s="4" t="inlineStr">
@@ -10087,17 +10087,17 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>Stale guard</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>stale-guard.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>answers arriving in order are all applied</t>
+          <t>updateMe PATCHes the account name</t>
         </is>
       </c>
       <c r="D353" s="4" t="inlineStr">
@@ -10114,17 +10114,17 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>Serial create</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>serial-create.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>choosing twice before the create returns creates once, then updates</t>
+          <t>upload sends multipart with the cookie and no time limit</t>
         </is>
       </c>
       <c r="D354" s="4" t="inlineStr">
@@ -10141,17 +10141,17 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>Serial create</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>serial-create.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>an existing id is only updated</t>
+          <t>upload sends the file bytes with its name and type, not a bare { uri } object</t>
         </is>
       </c>
       <c r="D355" s="4" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="B356" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>no rows when no service needs a document</t>
+          <t>a file the phone cannot open is "File unreadable", not a network error, and nothing is sent</t>
         </is>
       </c>
       <c r="D356" s="4" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>a babysitting service with nothing uploaded â†’ police-certificate none</t>
+          <t>upload maps a 413 to ApiError "File too large"</t>
         </is>
       </c>
       <c r="D357" s="4" t="inlineStr">
@@ -10227,12 +10227,12 @@
       </c>
       <c r="B358" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C358" s="4" t="inlineStr">
         <is>
-          <t>the most recently reviewed check decides, like the server</t>
+          <t>upload maps a network failure to ApiError network and does not retry</t>
         </is>
       </c>
       <c r="D358" s="4" t="inlineStr">
@@ -10254,12 +10254,12 @@
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>a pending check shows pending even after an approval</t>
+          <t>a store that cannot be read (Keystore failure) sends the request without a cookie</t>
         </is>
       </c>
       <c r="D359" s="4" t="inlineStr">
@@ -10281,12 +10281,12 @@
       </c>
       <c r="B360" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>a requirement code the app does not know still gets a row, after the known ones</t>
+          <t>a cookie that cannot be saved does not fail a request the server already carried out</t>
         </is>
       </c>
       <c r="D360" s="4" t="inlineStr">
@@ -10308,12 +10308,12 @@
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>two services needing the same document give one row</t>
+          <t>a malformed Set-Cookie line without "=" is skipped</t>
         </is>
       </c>
       <c r="D361" s="4" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="B362" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>client.test.ts</t>
         </is>
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>two different categories needing the same document give one row with the latest status</t>
+          <t>updateMe sends the one-field name as first and last name, split at the last space</t>
         </is>
       </c>
       <c r="D362" s="4" t="inlineStr">
@@ -10357,17 +10357,17 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use me</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-me.test.ts</t>
         </is>
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>a hidden service says a document is needed until it is uploaded, then that it waits for the check</t>
+          <t>a loadMe in flight at sign-out never fills the store for the next account</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
@@ -10384,17 +10384,17 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use me</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-me.test.ts</t>
         </is>
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>sharing is allowed only while no service waits for a document</t>
+          <t>the newest loadMe wins: an older, slower response never overwrites a newer one</t>
         </is>
       </c>
       <c r="D364" s="4" t="inlineStr">
@@ -10411,17 +10411,17 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>Phone app</t>
+          <t>Use flash</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
-          <t>documents.test.ts</t>
+          <t>use-flash.test.ts</t>
         </is>
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>saving a waiting service keeps Share hidden: the server answer carries waitingFor</t>
+          <t>createFlash: on after show, off after the delay, off at once on hide, a second show restarts the delay</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr">
@@ -10438,17 +10438,17 @@
     <row r="366">
       <c r="A366" s="4" t="inlineStr">
         <is>
-          <t>Use me</t>
+          <t>Use flash</t>
         </is>
       </c>
       <c r="B366" s="4" t="inlineStr">
         <is>
-          <t>use-me.test.ts</t>
+          <t>use-flash.test.ts</t>
         </is>
       </c>
       <c r="C366" s="4" t="inlineStr">
         <is>
-          <t>a loadMe in flight at sign-out never fills the store for the next account</t>
+          <t>createFlash: show is a no-op after dispose</t>
         </is>
       </c>
       <c r="D366" s="4" t="inlineStr">
@@ -10465,22 +10465,22 @@
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Use flash</t>
         </is>
       </c>
       <c r="B367" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>use-flash.test.ts</t>
         </is>
       </c>
       <c r="C367" s="4" t="inlineStr">
         <is>
-          <t>ServiceInputSchema rejects three decimals and negative prices</t>
+          <t>createFlash: a fresh flash after a dispose works again (remount)</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E367" s="4" t="inlineStr">
@@ -10492,22 +10492,22 @@
     <row r="368">
       <c r="A368" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B368" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>match.test.ts</t>
         </is>
       </c>
       <c r="C368" s="4" t="inlineStr">
         <is>
-          <t>ServiceInputSchema needs no price on request</t>
+          <t>matches ignores case and accents, and an empty query matches everything</t>
         </is>
       </c>
       <c r="D368" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E368" s="4" t="inlineStr">
@@ -10519,22 +10519,22 @@
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Stale guard</t>
         </is>
       </c>
       <c r="B369" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>stale-guard.test.ts</t>
         </is>
       </c>
       <c r="C369" s="4" t="inlineStr">
         <is>
-          <t>AdminListQuerySchema caps pageSize at 100</t>
+          <t>a response older than one already applied is ignored</t>
         </is>
       </c>
       <c r="D369" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E369" s="4" t="inlineStr">
@@ -10546,22 +10546,22 @@
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Stale guard</t>
         </is>
       </c>
       <c r="B370" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>stale-guard.test.ts</t>
         </is>
       </c>
       <c r="C370" s="4" t="inlineStr">
         <is>
-          <t>parse helpers parseBody answers 400 with the issues</t>
+          <t>answers arriving in order are all applied</t>
         </is>
       </c>
       <c r="D370" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E370" s="4" t="inlineStr">
@@ -10573,22 +10573,22 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C371" s="4" t="inlineStr">
         <is>
-          <t>parse helpers parseQuery reads the search params</t>
+          <t>no rows when no service needs a document</t>
         </is>
       </c>
       <c r="D371" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E371" s="4" t="inlineStr">
@@ -10600,22 +10600,22 @@
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B372" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C372" s="4" t="inlineStr">
         <is>
-          <t>list envelopes lists are { docs: [...] }</t>
+          <t>a babysitting service with nothing uploaded â†’ police-certificate none</t>
         </is>
       </c>
       <c r="D372" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E372" s="4" t="inlineStr">
@@ -10627,22 +10627,22 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>list envelopes reference year is checked against the current year at parse time</t>
+          <t>the most recently reviewed check decides, like the server</t>
         </is>
       </c>
       <c r="D373" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E373" s="4" t="inlineStr">
@@ -10654,22 +10654,22 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>address street, postcode and city are required (no empty or blank parts)</t>
+          <t>a pending check shows pending even after an approval</t>
         </is>
       </c>
       <c r="D374" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E374" s="4" t="inlineStr">
@@ -10681,22 +10681,22 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B375" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>service input as the app sends it a category alone is valid (the server fills currency and title)</t>
+          <t>a requirement code the app does not know still gets a row, after the known ones</t>
         </is>
       </c>
       <c r="D375" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E375" s="4" t="inlineStr">
@@ -10708,22 +10708,22 @@
     <row r="376">
       <c r="A376" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B376" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C376" s="4" t="inlineStr">
         <is>
-          <t>catalogue de and en have the same keys</t>
+          <t>two services needing the same document give one row</t>
         </is>
       </c>
       <c r="D376" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E376" s="4" t="inlineStr">
@@ -10735,22 +10735,22 @@
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B377" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>catalogue no text is empty and no two keys of one namespace carry the same text</t>
+          <t>two different categories needing the same document give one row with the latest status</t>
         </is>
       </c>
       <c r="D377" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E377" s="4" t="inlineStr">
@@ -10762,22 +10762,22 @@
     <row r="378">
       <c r="A378" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B378" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
-          <t>catalogue no text contains Treuhand, Escrow, garantiert or a competitor name</t>
+          <t>a hidden service says a document is needed until it is uploaded, then that it waits for the check</t>
         </is>
       </c>
       <c r="D378" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E378" s="4" t="inlineStr">
@@ -10789,22 +10789,22 @@
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B379" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>catalogue the product name is only written in brand.name</t>
+          <t>sharing is allowed only while no service waits for a document</t>
         </is>
       </c>
       <c r="D379" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E379" s="4" t="inlineStr">
@@ -10816,22 +10816,22 @@
     <row r="380">
       <c r="A380" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B380" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>documents.test.ts</t>
         </is>
       </c>
       <c r="C380" s="4" t="inlineStr">
         <is>
-          <t>t replaces placeholders and falls back to the key when missing</t>
+          <t>saving a waiting service keeps Share hidden: the server answer carries waitingFor</t>
         </is>
       </c>
       <c r="D380" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E380" s="4" t="inlineStr">
@@ -10843,22 +10843,22 @@
     <row r="381">
       <c r="A381" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="B381" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>profile-tab.test.ts</t>
         </is>
       </c>
       <c r="C381" s="4" t="inlineStr">
         <is>
-          <t>t fills the brand name without a parameter</t>
+          <t>the My profile tab shows only for a known provider</t>
         </is>
       </c>
       <c r="D381" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E381" s="4" t="inlineStr">
@@ -10870,22 +10870,22 @@
     <row r="382">
       <c r="A382" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="B382" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>profile-tab.test.ts</t>
         </is>
       </c>
       <c r="C382" s="4" t="inlineStr">
         <is>
-          <t>t knows its languages</t>
+          <t>after sign-out the next account does not inherit the provider tab</t>
         </is>
       </c>
       <c r="D382" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E382" s="4" t="inlineStr">
@@ -10897,22 +10897,22 @@
     <row r="383">
       <c r="A383" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Picture nudge</t>
         </is>
       </c>
       <c r="B383" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>picture-nudge.test.ts</t>
         </is>
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>money formats per language</t>
+          <t>the dismissed-nudge key is per user, so a second account on the device still sees it</t>
         </is>
       </c>
       <c r="D383" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E383" s="4" t="inlineStr">
@@ -10924,22 +10924,22 @@
     <row r="384">
       <c r="A384" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B384" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>auth-layout.test.ts</t>
         </is>
       </c>
       <c r="C384" s="4" t="inlineStr">
         <is>
-          <t>money formats price labels from the catalogue</t>
+          <t>logged-out landing route is login</t>
         </is>
       </c>
       <c r="D384" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E384" s="4" t="inlineStr">
@@ -10951,22 +10951,22 @@
     <row r="385">
       <c r="A385" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Phone app</t>
         </is>
       </c>
       <c r="B385" s="4" t="inlineStr">
         <is>
-          <t>index.test.ts</t>
+          <t>auth-layout.test.ts</t>
         </is>
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>acceptLang en-GB,en;q=0.9,de;q=0.8 -&gt; en</t>
+          <t>no test files inside src/app (each file there becomes a screen)</t>
         </is>
       </c>
       <c r="D385" s="4" t="inlineStr">
         <is>
-          <t>Packages</t>
+          <t>App</t>
         </is>
       </c>
       <c r="E385" s="4" t="inlineStr">
@@ -10978,7 +10978,7 @@
     <row r="386">
       <c r="A386" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B386" s="4" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>acceptLang * -&gt; undefined</t>
+          <t>ServiceInputSchema rejects three decimals and negative prices</t>
         </is>
       </c>
       <c r="D386" s="4" t="inlineStr">
@@ -11005,7 +11005,7 @@
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B387" s="4" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>acceptLang fr-FR -&gt; undefined</t>
+          <t>ServiceInputSchema needs no price on request</t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
@@ -11032,7 +11032,7 @@
     <row r="388">
       <c r="A388" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B388" s="4" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>acceptLang  -&gt; undefined</t>
+          <t>AdminListQuerySchema caps pageSize at 100</t>
         </is>
       </c>
       <c r="D388" s="4" t="inlineStr">
@@ -11059,7 +11059,7 @@
     <row r="389">
       <c r="A389" s="4" t="inlineStr">
         <is>
-          <t>Texts</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B389" s="4" t="inlineStr">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>acceptLang undefined -&gt; undefined</t>
+          <t>parse helpers parseBody answers 400 with the issues</t>
         </is>
       </c>
       <c r="D389" s="4" t="inlineStr">
@@ -11086,22 +11086,22 @@
     <row r="390">
       <c r="A390" s="4" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B390" s="4" t="inlineStr">
         <is>
-          <t>profile-tab.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>the My profile tab shows only for a known provider</t>
+          <t>parse helpers parseQuery reads the search params</t>
         </is>
       </c>
       <c r="D390" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Packages</t>
         </is>
       </c>
       <c r="E390" s="4" t="inlineStr">
@@ -11113,25 +11113,484 @@
     <row r="391">
       <c r="A391" s="4" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B391" s="4" t="inlineStr">
         <is>
-          <t>profile-tab.test.ts</t>
+          <t>index.test.ts</t>
         </is>
       </c>
       <c r="C391" s="4" t="inlineStr">
         <is>
-          <t>after sign-out the next account does not inherit the provider tab</t>
+          <t>list envelopes lists are { docs: [...] }</t>
         </is>
       </c>
       <c r="D391" s="4" t="inlineStr">
         <is>
-          <t>App</t>
+          <t>Packages</t>
         </is>
       </c>
       <c r="E391" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="4" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="B392" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C392" s="4" t="inlineStr">
+        <is>
+          <t>list envelopes reference year is checked against the current year at parse time</t>
+        </is>
+      </c>
+      <c r="D392" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E392" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="4" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="B393" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C393" s="4" t="inlineStr">
+        <is>
+          <t>address only the postcode is required; blank street and city become null</t>
+        </is>
+      </c>
+      <c r="D393" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E393" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="4" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="B394" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C394" s="4" t="inlineStr">
+        <is>
+          <t>service input as the app sends it a category alone is valid (the server fills currency and title)</t>
+        </is>
+      </c>
+      <c r="D394" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E394" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B395" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C395" s="4" t="inlineStr">
+        <is>
+          <t>catalogue de and en have the same keys</t>
+        </is>
+      </c>
+      <c r="D395" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E395" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B396" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C396" s="4" t="inlineStr">
+        <is>
+          <t>catalogue no text is empty and no two keys of one namespace carry the same text</t>
+        </is>
+      </c>
+      <c r="D396" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E396" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B397" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C397" s="4" t="inlineStr">
+        <is>
+          <t>catalogue no text contains Treuhand, Escrow, garantiert or a competitor name</t>
+        </is>
+      </c>
+      <c r="D397" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E397" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B398" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C398" s="4" t="inlineStr">
+        <is>
+          <t>catalogue the product name is only written in brand.name</t>
+        </is>
+      </c>
+      <c r="D398" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E398" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B399" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C399" s="4" t="inlineStr">
+        <is>
+          <t>t replaces placeholders and falls back to the key when missing</t>
+        </is>
+      </c>
+      <c r="D399" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E399" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B400" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C400" s="4" t="inlineStr">
+        <is>
+          <t>t fills the brand name without a parameter</t>
+        </is>
+      </c>
+      <c r="D400" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E400" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B401" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C401" s="4" t="inlineStr">
+        <is>
+          <t>t knows its languages</t>
+        </is>
+      </c>
+      <c r="D401" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E401" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B402" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C402" s="4" t="inlineStr">
+        <is>
+          <t>money formats per language</t>
+        </is>
+      </c>
+      <c r="D402" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E402" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B403" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C403" s="4" t="inlineStr">
+        <is>
+          <t>money formats price labels from the catalogue</t>
+        </is>
+      </c>
+      <c r="D403" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E403" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B404" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C404" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang en-GB,en;q=0.9,de;q=0.8 -&gt; en</t>
+        </is>
+      </c>
+      <c r="D404" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E404" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B405" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C405" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang * -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D405" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E405" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B406" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C406" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang fr-FR -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D406" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E406" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B407" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C407" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang  -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D407" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E407" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="4" t="inlineStr">
+        <is>
+          <t>Texts</t>
+        </is>
+      </c>
+      <c r="B408" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts</t>
+        </is>
+      </c>
+      <c r="C408" s="4" t="inlineStr">
+        <is>
+          <t>acceptLang undefined -&gt; undefined</t>
+        </is>
+      </c>
+      <c r="D408" s="4" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="E408" s="4" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
@@ -11148,7 +11607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -11197,7 +11656,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Run 27 October on registration-setup.</t>
+          <t>Run 27 October on account-address-saved.</t>
         </is>
       </c>
     </row>
@@ -11219,7 +11678,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Run 27 October.</t>
+          <t>Run 27 October on account-address-saved.</t>
         </is>
       </c>
     </row>
@@ -11241,7 +11700,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>35 files, 257 tests (the root run).</t>
+          <t>35 files, 259 tests (the root run).</t>
         </is>
       </c>
     </row>
@@ -11285,7 +11744,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>257 tests.</t>
+          <t>259 tests.</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11756,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>20 suites.</t>
+          <t>24 suites.</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -11307,7 +11766,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>110 tests.</t>
+          <t>125 tests.</t>
         </is>
       </c>
     </row>
@@ -11902,6 +12361,138 @@
       <c r="D34" s="4" t="inlineStr">
         <is>
           <t>services-references.int.spec.ts (a category alone, one field per save; add and update answer with waitingFor).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Address with only a postcode</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Contract: postcode alone valid, street without postcode invalid, blank street/city become null. Server: stored, returned by GET /me and the admin user page, null clears all four columns, street without postcode is 400.</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>index.test.ts; provider-profile.int.spec.ts; admin-api.int.spec.ts; apps/mobile address-fields.test.ts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Saved confirmation timing</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>The message turns on, off after 3 s, off at once on edit, and restarts on a second show.</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>apps/mobile use-flash.test.ts (fake timers). The screen wiring needs a phone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Offer services helper</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Creates the draft, reloads /me, then hands the target to the tabs layout, which navigates once the tab is visible; failure sets no target; double tap runs once; welcome passes through; sign-out clears the target.</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>apps/mobile start-offering.test.ts; pending-navigation.test.ts. The layout effect itself needs a phone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Phone: Account Save shows "Saved"</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Saved appears under Save, vanishes after about 3 s or when you edit; a postcode-only address saves.</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Not yet done (phone)</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Phone: Offer services opens the profile page</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Account &gt; Offer services opens the setup page directly (no Home); My profile tab appears.</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Not yet done (phone)</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Phone: Become a provider card</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Card sits under the find-help button, opens the same page; a provider no longer sees the card.</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Not yet done (phone)</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Owner.</t>
         </is>
       </c>
     </row>
@@ -11916,7 +12507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -12740,6 +13331,74 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (owner phone test): address needs only a postcode</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Street and city optional (stored null); a street without a postcode is refused; an address never vanishes when the street is empty; sign-up and Account share one rule and text. Phone check: save a postcode-only address in Account and sign-up.</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Fixed; Not yet done (phone)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (owner phone test): Saved confirmation</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Account shows "Saved" / "Gespeichert" after a successful save, for about 3 s or until the next edit. Phone check: see it appear and go.</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Fixed; Not yet done (phone)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (owner phone test): Offer services and Become a provider</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Both create the draft, reload /me and open the profile page directly (they used to fall back to Home because the tab was hidden). The sign-up tick uses the same helper. Provider card moved under the find-help button, hidden for providers. Phone checks: Offer services opens the profile page directly; the card is under the find-help button and opens the same page; a provider no longer sees the card. The navigation waits for the tabs layout to show the tab (hand-off through a pending target), not for luck.</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Fixed; Not yet done (phone)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Fixed (PR review): offering, postcode, saving</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>The newest /me request wins; Offer services needs isProvider true and leaves no target after a sign-out; the layout consumes the target only when the tab is visible; the server checks the postcode format (400 Invalid postcode; a well-formed unlisted one is accepted); a refused sign-up postcode no longer blocks the names; Account fields are locked while saving. Phone check: Offer services reaches the My profile tab route (not the empty app/my-profile stack); a bad postcode shows the new text in Account.</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Fixed; Not yet done (phone)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
